--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9658AE-7500-4A32-A995-8AE358DAC37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C174A180-FBFB-4399-9FF6-C57E98E06352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8960" yWindow="0" windowWidth="14170" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4999" uniqueCount="960">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -2648,6 +2648,282 @@
   </si>
   <si>
     <t>USURTOT</t>
+  </si>
+  <si>
+    <t>Interest Rate</t>
+  </si>
+  <si>
+    <t>FDTR</t>
+  </si>
+  <si>
+    <t>FDTRDOT</t>
+  </si>
+  <si>
+    <t>Projection</t>
+  </si>
+  <si>
+    <t>Fed Interest Rate Decision</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/interest-rate-decision-168</t>
+  </si>
+  <si>
+    <t>Fed Interest Rate Projection</t>
+  </si>
+  <si>
+    <t>Querterly</t>
+  </si>
+  <si>
+    <t>PAYEMS</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/nonfarm-payrolls-227</t>
+  </si>
+  <si>
+    <t>US Nonfarm Payrolls</t>
+  </si>
+  <si>
+    <t>RSAFS</t>
+  </si>
+  <si>
+    <t>US Retail Sales</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/RSAFS</t>
+  </si>
+  <si>
+    <t>FRED</t>
+  </si>
+  <si>
+    <t>Consumption</t>
+  </si>
+  <si>
+    <t>Sentiment</t>
+  </si>
+  <si>
+    <t>Survey</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>CONCCONF</t>
+  </si>
+  <si>
+    <t>US CB Consumer Confidence</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/cb-consumer-confidence-48</t>
+  </si>
+  <si>
+    <t>Conference Board</t>
+  </si>
+  <si>
+    <t>CONSSENT</t>
+  </si>
+  <si>
+    <t>US Michigan Consumer Sentiment Index</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/michigan-consumer-sentiment-320</t>
+  </si>
+  <si>
+    <t>University of Michigan</t>
+  </si>
+  <si>
+    <t>BEA</t>
+  </si>
+  <si>
+    <t>Core PCE Price Index YoY NSA</t>
+  </si>
+  <si>
+    <t>Core PCE Price Index YoY SA</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/core-pce-price-index-905</t>
+  </si>
+  <si>
+    <t>PCESRVY</t>
+  </si>
+  <si>
+    <t>PCECYOY</t>
+  </si>
+  <si>
+    <t>Inflation</t>
+  </si>
+  <si>
+    <t>CPIYOY</t>
+  </si>
+  <si>
+    <t>US Consumer Price Index</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/cpi-733</t>
+  </si>
+  <si>
+    <t>BOL</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>USGDP</t>
+  </si>
+  <si>
+    <t>GDPCQQQ</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/united-states-gross-domestic-product-(gdp)-qoq-375</t>
+  </si>
+  <si>
+    <t>US Gross Domestic Product QoQ</t>
+  </si>
+  <si>
+    <t>QoQ Rate</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>NAPMPMI</t>
+  </si>
+  <si>
+    <t>NAPMNEWO</t>
+  </si>
+  <si>
+    <t>NAPMNMI</t>
+  </si>
+  <si>
+    <t>NAPMNNO</t>
+  </si>
+  <si>
+    <t>NAPMNSD</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-manufacturing-pmi-173</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-manufacturing-new-orders-index-1483</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-non-manufacturing-pmi-176</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/ism-non-manufacturing-new-orders-1050</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/tenaga-kerja-non-manufaktur-ism-1048</t>
+  </si>
+  <si>
+    <t>ISM</t>
+  </si>
+  <si>
+    <t>ISM Manufacturing Purchasing Managers Index</t>
+  </si>
+  <si>
+    <t>ISM Manufacturing Purchasing Managers New Order Index</t>
+  </si>
+  <si>
+    <t>ISM Non-Manufacturing Purchasing Managers Index</t>
+  </si>
+  <si>
+    <t>ISM Non-Manufacturing Purchasing Managers New Order Index</t>
+  </si>
+  <si>
+    <t>ISM Non-Manufacturing Purchasing Managers Employment Index</t>
+  </si>
+  <si>
+    <t>Manufacture</t>
+  </si>
+  <si>
+    <t>Non Manufacture</t>
+  </si>
+  <si>
+    <t>CNCPIYOY</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>China Consumer Price Index</t>
+  </si>
+  <si>
+    <t>https://cn.investing.com/economic-calendar/chinese-cpi-459</t>
+  </si>
+  <si>
+    <t>CPMINDX</t>
+  </si>
+  <si>
+    <t>CFLP</t>
+  </si>
+  <si>
+    <t>China Manufacturing PMI Index</t>
+  </si>
+  <si>
+    <t>https://cn.investing.com/economic-calendar/chinese-manufacturing-pmi-594</t>
+  </si>
+  <si>
+    <t>TWTREXPY</t>
+  </si>
+  <si>
+    <t>Taiwan Exports YoY Index</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/taiwanese-exports-1118</t>
+  </si>
+  <si>
+    <t>Export</t>
+  </si>
+  <si>
+    <t>Trade</t>
+  </si>
+  <si>
+    <t>CPICEMU</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/european-consumer-price-index-(cpi)-yoy-68</t>
+  </si>
+  <si>
+    <t>European Consumer Price YoY Index</t>
+  </si>
+  <si>
+    <t>EUROSTAT</t>
+  </si>
+  <si>
+    <t>EUAPRRT</t>
+  </si>
+  <si>
+    <t>ECB</t>
+  </si>
+  <si>
+    <t>Europe Central Bank Interest Rate Decision</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/interest-rate-decision-164</t>
+  </si>
+  <si>
+    <t>JPCPIYOY</t>
+  </si>
+  <si>
+    <t>Japan National Consumer Price Index</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/national-cpi-992</t>
+  </si>
+  <si>
+    <t>BOJ</t>
+  </si>
+  <si>
+    <t>BOJDTR</t>
+  </si>
+  <si>
+    <t>Japan Interest Rate Decision</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/interest-rate-decision-165</t>
   </si>
 </sst>
 </file>
@@ -2706,7 +2982,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2984,23 +3260,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O473"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O495"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" customWidth="1"/>
-    <col min="10" max="10" width="35.44140625" customWidth="1"/>
-    <col min="11" max="13" width="12.88671875" customWidth="1"/>
-    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" customWidth="1"/>
+    <col min="11" max="13" width="12.90625" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3047,7 +3323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>450</v>
       </c>
@@ -3079,7 +3355,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>450</v>
       </c>
@@ -3111,7 +3387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>450</v>
       </c>
@@ -3143,7 +3419,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>450</v>
       </c>
@@ -3175,7 +3451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>450</v>
       </c>
@@ -3207,7 +3483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>450</v>
       </c>
@@ -3236,7 +3512,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -3256,7 +3532,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>450</v>
       </c>
@@ -3276,7 +3552,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>450</v>
       </c>
@@ -3296,7 +3572,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>450</v>
       </c>
@@ -3316,7 +3592,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>450</v>
       </c>
@@ -3336,7 +3612,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>450</v>
       </c>
@@ -3356,7 +3632,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>450</v>
       </c>
@@ -3376,7 +3652,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>450</v>
       </c>
@@ -3396,7 +3672,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>450</v>
       </c>
@@ -3416,7 +3692,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>450</v>
       </c>
@@ -3436,7 +3712,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>450</v>
       </c>
@@ -3456,7 +3732,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>450</v>
       </c>
@@ -3476,7 +3752,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>450</v>
       </c>
@@ -3496,7 +3772,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>450</v>
       </c>
@@ -3516,7 +3792,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>450</v>
       </c>
@@ -3536,7 +3812,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>450</v>
       </c>
@@ -3556,7 +3832,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>450</v>
       </c>
@@ -3576,7 +3852,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>450</v>
       </c>
@@ -3596,7 +3872,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>450</v>
       </c>
@@ -3616,7 +3892,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>450</v>
       </c>
@@ -3636,7 +3912,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>450</v>
       </c>
@@ -3656,7 +3932,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>450</v>
       </c>
@@ -3676,7 +3952,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>450</v>
       </c>
@@ -3696,7 +3972,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>450</v>
       </c>
@@ -3716,7 +3992,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>450</v>
       </c>
@@ -3736,7 +4012,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>450</v>
       </c>
@@ -3759,7 +4035,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>450</v>
       </c>
@@ -3782,7 +4058,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>450</v>
       </c>
@@ -3805,7 +4081,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>450</v>
       </c>
@@ -3828,7 +4104,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>450</v>
       </c>
@@ -3848,7 +4124,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>450</v>
       </c>
@@ -3868,7 +4144,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>450</v>
       </c>
@@ -3888,7 +4164,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>450</v>
       </c>
@@ -3908,7 +4184,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>450</v>
       </c>
@@ -3928,7 +4204,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>450</v>
       </c>
@@ -3948,7 +4224,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>450</v>
       </c>
@@ -3971,7 +4247,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>450</v>
       </c>
@@ -3994,7 +4270,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>450</v>
       </c>
@@ -4017,7 +4293,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>450</v>
       </c>
@@ -4040,7 +4316,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>450</v>
       </c>
@@ -4063,7 +4339,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>450</v>
       </c>
@@ -4086,7 +4362,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>450</v>
       </c>
@@ -4109,7 +4385,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>450</v>
       </c>
@@ -4129,7 +4405,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>450</v>
       </c>
@@ -4152,7 +4428,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>450</v>
       </c>
@@ -4172,7 +4448,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>450</v>
       </c>
@@ -4192,7 +4468,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>450</v>
       </c>
@@ -4212,7 +4488,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>450</v>
       </c>
@@ -4232,7 +4508,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>450</v>
       </c>
@@ -4252,7 +4528,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>450</v>
       </c>
@@ -4272,7 +4548,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>450</v>
       </c>
@@ -4292,7 +4568,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>450</v>
       </c>
@@ -4312,7 +4588,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>450</v>
       </c>
@@ -4326,7 +4602,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>141</v>
       </c>
@@ -4358,7 +4634,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>141</v>
       </c>
@@ -4390,7 +4666,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>141</v>
       </c>
@@ -4422,7 +4698,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>141</v>
       </c>
@@ -4454,7 +4730,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>141</v>
       </c>
@@ -4486,7 +4762,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>141</v>
       </c>
@@ -4518,7 +4794,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>141</v>
       </c>
@@ -4550,7 +4826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>141</v>
       </c>
@@ -4585,7 +4861,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>141</v>
       </c>
@@ -4617,7 +4893,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>141</v>
       </c>
@@ -4652,7 +4928,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>141</v>
       </c>
@@ -4687,7 +4963,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>141</v>
       </c>
@@ -4722,7 +4998,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>141</v>
       </c>
@@ -4754,7 +5030,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>141</v>
       </c>
@@ -4789,7 +5065,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>141</v>
       </c>
@@ -4824,7 +5100,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>141</v>
       </c>
@@ -4856,7 +5132,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>141</v>
       </c>
@@ -4891,7 +5167,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>141</v>
       </c>
@@ -4926,7 +5202,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>141</v>
       </c>
@@ -4958,7 +5234,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>141</v>
       </c>
@@ -4990,7 +5266,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>141</v>
       </c>
@@ -5022,7 +5298,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>141</v>
       </c>
@@ -5054,7 +5330,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>141</v>
       </c>
@@ -5086,7 +5362,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>141</v>
       </c>
@@ -5118,7 +5394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>141</v>
       </c>
@@ -5150,7 +5426,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>141</v>
       </c>
@@ -5182,7 +5458,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>141</v>
       </c>
@@ -5214,7 +5490,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>141</v>
       </c>
@@ -5246,7 +5522,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>141</v>
       </c>
@@ -5278,7 +5554,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>141</v>
       </c>
@@ -5310,7 +5586,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>141</v>
       </c>
@@ -5345,7 +5621,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>141</v>
       </c>
@@ -5377,7 +5653,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>141</v>
       </c>
@@ -5409,7 +5685,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>141</v>
       </c>
@@ -5444,7 +5720,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>141</v>
       </c>
@@ -5479,7 +5755,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>141</v>
       </c>
@@ -5511,7 +5787,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>141</v>
       </c>
@@ -5543,7 +5819,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>141</v>
       </c>
@@ -5575,7 +5851,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>141</v>
       </c>
@@ -5607,7 +5883,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="100" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>141</v>
       </c>
@@ -5639,7 +5915,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>141</v>
       </c>
@@ -5671,7 +5947,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="102" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>141</v>
       </c>
@@ -5703,7 +5979,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>141</v>
       </c>
@@ -5735,7 +6011,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="104" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>141</v>
       </c>
@@ -5767,7 +6043,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="105" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>141</v>
       </c>
@@ -5799,7 +6075,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="106" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>141</v>
       </c>
@@ -5831,7 +6107,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="107" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>141</v>
       </c>
@@ -5863,7 +6139,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="108" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>141</v>
       </c>
@@ -5895,7 +6171,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="109" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>141</v>
       </c>
@@ -5927,7 +6203,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="110" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>141</v>
       </c>
@@ -5959,7 +6235,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="111" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>141</v>
       </c>
@@ -5991,7 +6267,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="112" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>141</v>
       </c>
@@ -6023,7 +6299,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="113" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>141</v>
       </c>
@@ -6055,7 +6331,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>141</v>
       </c>
@@ -6087,7 +6363,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="115" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>141</v>
       </c>
@@ -6119,7 +6395,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="116" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>141</v>
       </c>
@@ -6151,7 +6427,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>141</v>
       </c>
@@ -6183,7 +6459,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>141</v>
       </c>
@@ -6215,7 +6491,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="119" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>141</v>
       </c>
@@ -6247,7 +6523,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="120" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>141</v>
       </c>
@@ -6279,7 +6555,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="121" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>141</v>
       </c>
@@ -6311,7 +6587,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="122" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>141</v>
       </c>
@@ -6343,7 +6619,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="123" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>141</v>
       </c>
@@ -6369,7 +6645,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="124" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>141</v>
       </c>
@@ -6395,7 +6671,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>141</v>
       </c>
@@ -6421,7 +6697,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="126" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>141</v>
       </c>
@@ -6447,7 +6723,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="127" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>141</v>
       </c>
@@ -6479,7 +6755,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>141</v>
       </c>
@@ -6505,7 +6781,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>141</v>
       </c>
@@ -6531,7 +6807,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>141</v>
       </c>
@@ -6557,7 +6833,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>141</v>
       </c>
@@ -6592,7 +6868,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>141</v>
       </c>
@@ -6627,7 +6903,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>141</v>
       </c>
@@ -6662,7 +6938,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>141</v>
       </c>
@@ -6697,7 +6973,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>141</v>
       </c>
@@ -6732,7 +7008,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>141</v>
       </c>
@@ -6767,7 +7043,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>141</v>
       </c>
@@ -6802,7 +7078,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>141</v>
       </c>
@@ -6837,7 +7113,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>141</v>
       </c>
@@ -6872,7 +7148,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -6907,7 +7183,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>141</v>
       </c>
@@ -6942,7 +7218,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>141</v>
       </c>
@@ -6977,7 +7253,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>141</v>
       </c>
@@ -7012,7 +7288,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>141</v>
       </c>
@@ -7047,7 +7323,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>141</v>
       </c>
@@ -7082,7 +7358,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
         <v>141</v>
       </c>
@@ -7117,7 +7393,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>141</v>
       </c>
@@ -7152,7 +7428,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>141</v>
       </c>
@@ -7187,7 +7463,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
         <v>141</v>
       </c>
@@ -7222,7 +7498,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
         <v>141</v>
       </c>
@@ -7257,7 +7533,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
         <v>141</v>
       </c>
@@ -7292,7 +7568,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>141</v>
       </c>
@@ -7330,7 +7606,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
         <v>141</v>
       </c>
@@ -7365,7 +7641,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
         <v>141</v>
       </c>
@@ -7400,7 +7676,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
         <v>141</v>
       </c>
@@ -7435,7 +7711,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
         <v>141</v>
       </c>
@@ -7470,7 +7746,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
         <v>141</v>
       </c>
@@ -7505,7 +7781,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
         <v>141</v>
       </c>
@@ -7543,7 +7819,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
         <v>141</v>
       </c>
@@ -7578,7 +7854,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
         <v>141</v>
       </c>
@@ -7613,7 +7889,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
         <v>141</v>
       </c>
@@ -7648,7 +7924,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
         <v>141</v>
       </c>
@@ -7683,7 +7959,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B163" t="s">
         <v>141</v>
       </c>
@@ -7718,7 +7994,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>141</v>
       </c>
@@ -7753,7 +8029,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
         <v>141</v>
       </c>
@@ -7788,7 +8064,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>141</v>
       </c>
@@ -7823,7 +8099,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
         <v>141</v>
       </c>
@@ -7861,7 +8137,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B168" t="s">
         <v>141</v>
       </c>
@@ -7896,7 +8172,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
         <v>141</v>
       </c>
@@ -7931,7 +8207,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
         <v>141</v>
       </c>
@@ -7966,7 +8242,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>141</v>
       </c>
@@ -8001,7 +8277,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
         <v>141</v>
       </c>
@@ -8036,7 +8312,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>141</v>
       </c>
@@ -8071,7 +8347,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
         <v>141</v>
       </c>
@@ -8106,7 +8382,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>141</v>
       </c>
@@ -8141,7 +8417,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
         <v>141</v>
       </c>
@@ -8176,7 +8452,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>141</v>
       </c>
@@ -8211,7 +8487,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>141</v>
       </c>
@@ -8246,7 +8522,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>141</v>
       </c>
@@ -8281,7 +8557,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>141</v>
       </c>
@@ -8316,7 +8592,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>141</v>
       </c>
@@ -8351,7 +8627,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="182" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>141</v>
       </c>
@@ -8386,7 +8662,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>141</v>
       </c>
@@ -8421,7 +8697,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>141</v>
       </c>
@@ -8456,7 +8732,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>141</v>
       </c>
@@ -8491,7 +8767,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>141</v>
       </c>
@@ -8526,7 +8802,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>141</v>
       </c>
@@ -8561,7 +8837,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>141</v>
       </c>
@@ -8596,7 +8872,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="189" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>141</v>
       </c>
@@ -8628,7 +8904,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>141</v>
       </c>
@@ -8660,7 +8936,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>141</v>
       </c>
@@ -8692,7 +8968,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="192" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>141</v>
       </c>
@@ -8724,7 +9000,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="193" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>141</v>
       </c>
@@ -8756,7 +9032,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="194" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
         <v>141</v>
       </c>
@@ -8788,7 +9064,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="195" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
         <v>141</v>
       </c>
@@ -8820,7 +9096,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="196" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>141</v>
       </c>
@@ -8852,7 +9128,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
         <v>141</v>
       </c>
@@ -8884,7 +9160,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="198" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>141</v>
       </c>
@@ -8916,7 +9192,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="199" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
         <v>141</v>
       </c>
@@ -8954,7 +9230,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="200" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
         <v>141</v>
       </c>
@@ -8992,7 +9268,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
         <v>141</v>
       </c>
@@ -9030,7 +9306,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>141</v>
       </c>
@@ -9068,7 +9344,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="203" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
         <v>141</v>
       </c>
@@ -9106,7 +9382,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="204" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
         <v>141</v>
       </c>
@@ -9144,7 +9420,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="205" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
         <v>141</v>
       </c>
@@ -9182,7 +9458,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
         <v>141</v>
       </c>
@@ -9220,7 +9496,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
         <v>141</v>
       </c>
@@ -9258,7 +9534,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="208" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>141</v>
       </c>
@@ -9296,7 +9572,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="209" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
         <v>141</v>
       </c>
@@ -9334,7 +9610,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="210" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>141</v>
       </c>
@@ -9372,7 +9648,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="211" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>141</v>
       </c>
@@ -9410,7 +9686,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="212" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
         <v>141</v>
       </c>
@@ -9448,7 +9724,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="213" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
         <v>141</v>
       </c>
@@ -9486,7 +9762,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="214" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
         <v>141</v>
       </c>
@@ -9521,7 +9797,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="215" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
         <v>141</v>
       </c>
@@ -9556,7 +9832,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="216" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
         <v>141</v>
       </c>
@@ -9591,7 +9867,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="217" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>141</v>
       </c>
@@ -9626,7 +9902,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="218" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>141</v>
       </c>
@@ -9661,7 +9937,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="219" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B219" t="s">
         <v>141</v>
       </c>
@@ -9696,7 +9972,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="220" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
         <v>141</v>
       </c>
@@ -9731,7 +10007,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="221" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B221" t="s">
         <v>141</v>
       </c>
@@ -9766,7 +10042,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="222" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B222" t="s">
         <v>141</v>
       </c>
@@ -9804,7 +10080,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="223" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
         <v>424</v>
       </c>
@@ -9845,7 +10121,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="224" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B224" t="s">
         <v>424</v>
       </c>
@@ -9883,7 +10159,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B225" t="s">
         <v>424</v>
       </c>
@@ -9921,7 +10197,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="226" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>424</v>
       </c>
@@ -9959,7 +10235,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="227" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>424</v>
       </c>
@@ -9997,7 +10273,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="228" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>424</v>
       </c>
@@ -10035,7 +10311,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="229" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>424</v>
       </c>
@@ -10073,7 +10349,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="230" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
         <v>424</v>
       </c>
@@ -10111,7 +10387,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="231" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B231" t="s">
         <v>424</v>
       </c>
@@ -10149,7 +10425,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="232" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>424</v>
       </c>
@@ -10187,7 +10463,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="233" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>424</v>
       </c>
@@ -10225,7 +10501,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="234" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>449</v>
       </c>
@@ -10257,7 +10533,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
         <v>463</v>
       </c>
@@ -10295,7 +10571,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="236" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B236" t="s">
         <v>463</v>
       </c>
@@ -10333,7 +10609,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="237" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B237" t="s">
         <v>463</v>
       </c>
@@ -10371,7 +10647,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="238" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B238" t="s">
         <v>477</v>
       </c>
@@ -10403,7 +10679,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="239" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>477</v>
       </c>
@@ -10435,7 +10711,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="240" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
         <v>477</v>
       </c>
@@ -10467,7 +10743,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="241" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
         <v>477</v>
       </c>
@@ -10499,7 +10775,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="242" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
         <v>477</v>
       </c>
@@ -10537,7 +10813,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="243" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
         <v>477</v>
       </c>
@@ -10575,7 +10851,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="244" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B244" t="s">
         <v>477</v>
       </c>
@@ -10613,7 +10889,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="245" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B245" t="s">
         <v>477</v>
       </c>
@@ -10651,7 +10927,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="246" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B246" t="s">
         <v>477</v>
       </c>
@@ -10689,7 +10965,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="247" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B247" t="s">
         <v>477</v>
       </c>
@@ -10727,7 +11003,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
         <v>477</v>
       </c>
@@ -10765,7 +11041,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="249" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B249" t="s">
         <v>477</v>
       </c>
@@ -10803,7 +11079,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B250" t="s">
         <v>477</v>
       </c>
@@ -10841,7 +11117,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="251" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
         <v>477</v>
       </c>
@@ -10879,7 +11155,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="252" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B252" t="s">
         <v>477</v>
       </c>
@@ -10917,7 +11193,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="253" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
         <v>477</v>
       </c>
@@ -10955,7 +11231,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="254" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B254" t="s">
         <v>477</v>
       </c>
@@ -10993,7 +11269,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="255" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>477</v>
       </c>
@@ -11031,7 +11307,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="256" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B256" t="s">
         <v>477</v>
       </c>
@@ -11069,7 +11345,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="257" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>477</v>
       </c>
@@ -11107,7 +11383,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="258" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
         <v>477</v>
       </c>
@@ -11145,7 +11421,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="259" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B259" t="s">
         <v>477</v>
       </c>
@@ -11183,7 +11459,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="260" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
         <v>477</v>
       </c>
@@ -11221,7 +11497,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="261" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B261" t="s">
         <v>477</v>
       </c>
@@ -11259,7 +11535,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="262" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
         <v>477</v>
       </c>
@@ -11297,7 +11573,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="263" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B263" t="s">
         <v>477</v>
       </c>
@@ -11335,7 +11611,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="264" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B264" t="s">
         <v>477</v>
       </c>
@@ -11373,7 +11649,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="265" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B265" t="s">
         <v>477</v>
       </c>
@@ -11411,7 +11687,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="266" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B266" t="s">
         <v>477</v>
       </c>
@@ -11449,7 +11725,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="267" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
         <v>477</v>
       </c>
@@ -11487,7 +11763,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="268" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
         <v>477</v>
       </c>
@@ -11525,7 +11801,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="269" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B269" t="s">
         <v>477</v>
       </c>
@@ -11563,7 +11839,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="270" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
         <v>477</v>
       </c>
@@ -11601,7 +11877,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="271" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
         <v>477</v>
       </c>
@@ -11639,7 +11915,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="272" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
         <v>477</v>
       </c>
@@ -11677,7 +11953,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="273" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
         <v>477</v>
       </c>
@@ -11715,7 +11991,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="274" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B274" t="s">
         <v>477</v>
       </c>
@@ -11750,7 +12026,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="275" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B275" t="s">
         <v>477</v>
       </c>
@@ -11785,7 +12061,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="276" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B276" t="s">
         <v>477</v>
       </c>
@@ -11820,7 +12096,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="277" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B277" t="s">
         <v>477</v>
       </c>
@@ -11855,7 +12131,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="278" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B278" t="s">
         <v>477</v>
       </c>
@@ -11890,7 +12166,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="279" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B279" t="s">
         <v>477</v>
       </c>
@@ -11925,7 +12201,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="280" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B280" t="s">
         <v>477</v>
       </c>
@@ -11960,7 +12236,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="281" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B281" t="s">
         <v>477</v>
       </c>
@@ -11995,7 +12271,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="282" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B282" t="s">
         <v>477</v>
       </c>
@@ -12030,7 +12306,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="283" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B283" t="s">
         <v>477</v>
       </c>
@@ -12065,7 +12341,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="284" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B284" t="s">
         <v>477</v>
       </c>
@@ -12100,7 +12376,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="285" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B285" t="s">
         <v>477</v>
       </c>
@@ -12135,7 +12411,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="286" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
         <v>477</v>
       </c>
@@ -12170,7 +12446,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="287" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B287" t="s">
         <v>477</v>
       </c>
@@ -12205,7 +12481,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="288" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B288" t="s">
         <v>477</v>
       </c>
@@ -12240,7 +12516,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="289" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B289" t="s">
         <v>477</v>
       </c>
@@ -12275,7 +12551,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="290" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B290" t="s">
         <v>477</v>
       </c>
@@ -12310,7 +12586,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="291" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B291" t="s">
         <v>477</v>
       </c>
@@ -12345,7 +12621,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="292" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B292" t="s">
         <v>477</v>
       </c>
@@ -12380,7 +12656,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="293" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B293" t="s">
         <v>477</v>
       </c>
@@ -12415,7 +12691,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="294" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B294" t="s">
         <v>477</v>
       </c>
@@ -12450,7 +12726,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="295" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B295" t="s">
         <v>477</v>
       </c>
@@ -12485,7 +12761,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="296" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B296" t="s">
         <v>477</v>
       </c>
@@ -12520,7 +12796,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="297" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B297" t="s">
         <v>477</v>
       </c>
@@ -12555,7 +12831,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="298" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B298" t="s">
         <v>477</v>
       </c>
@@ -12590,7 +12866,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="299" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B299" t="s">
         <v>477</v>
       </c>
@@ -12625,7 +12901,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="300" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B300" t="s">
         <v>477</v>
       </c>
@@ -12660,7 +12936,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="301" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B301" t="s">
         <v>477</v>
       </c>
@@ -12695,7 +12971,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="302" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B302" t="s">
         <v>477</v>
       </c>
@@ -12730,7 +13006,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="303" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B303" t="s">
         <v>477</v>
       </c>
@@ -12765,7 +13041,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="304" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B304" t="s">
         <v>477</v>
       </c>
@@ -12800,7 +13076,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="305" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B305" t="s">
         <v>477</v>
       </c>
@@ -12835,7 +13111,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="306" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B306" t="s">
         <v>477</v>
       </c>
@@ -12870,7 +13146,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="307" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B307" t="s">
         <v>477</v>
       </c>
@@ -12905,7 +13181,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="308" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B308" t="s">
         <v>477</v>
       </c>
@@ -12940,7 +13216,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="309" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B309" t="s">
         <v>477</v>
       </c>
@@ -12975,7 +13251,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="310" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B310" t="s">
         <v>477</v>
       </c>
@@ -13010,7 +13286,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="311" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B311" t="s">
         <v>477</v>
       </c>
@@ -13045,7 +13321,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="312" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B312" t="s">
         <v>477</v>
       </c>
@@ -13077,7 +13353,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="313" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B313" t="s">
         <v>477</v>
       </c>
@@ -13109,7 +13385,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="314" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B314" t="s">
         <v>477</v>
       </c>
@@ -13141,7 +13417,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="315" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B315" t="s">
         <v>477</v>
       </c>
@@ -13173,7 +13449,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="316" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B316" t="s">
         <v>477</v>
       </c>
@@ -13205,7 +13481,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="317" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B317" t="s">
         <v>477</v>
       </c>
@@ -13237,7 +13513,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B318" t="s">
         <v>477</v>
       </c>
@@ -13269,7 +13545,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B319" t="s">
         <v>477</v>
       </c>
@@ -13301,7 +13577,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="320" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B320" t="s">
         <v>477</v>
       </c>
@@ -13333,7 +13609,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="321" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B321" t="s">
         <v>477</v>
       </c>
@@ -13365,7 +13641,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="322" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B322" t="s">
         <v>477</v>
       </c>
@@ -13397,7 +13673,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="323" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B323" t="s">
         <v>477</v>
       </c>
@@ -13429,7 +13705,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="324" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B324" t="s">
         <v>477</v>
       </c>
@@ -13461,7 +13737,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="325" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B325" t="s">
         <v>477</v>
       </c>
@@ -13493,7 +13769,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="326" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B326" t="s">
         <v>477</v>
       </c>
@@ -13525,7 +13801,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="327" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B327" t="s">
         <v>477</v>
       </c>
@@ -13557,7 +13833,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="328" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B328" t="s">
         <v>477</v>
       </c>
@@ -13589,7 +13865,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="329" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B329" t="s">
         <v>477</v>
       </c>
@@ -13621,7 +13897,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="330" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B330" t="s">
         <v>477</v>
       </c>
@@ -13653,7 +13929,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="331" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B331" t="s">
         <v>477</v>
       </c>
@@ -13685,7 +13961,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="332" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B332" t="s">
         <v>477</v>
       </c>
@@ -13717,7 +13993,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="333" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B333" t="s">
         <v>477</v>
       </c>
@@ -13749,7 +14025,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="334" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B334" t="s">
         <v>477</v>
       </c>
@@ -13781,7 +14057,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="335" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B335" t="s">
         <v>477</v>
       </c>
@@ -13813,7 +14089,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="336" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B336" t="s">
         <v>477</v>
       </c>
@@ -13845,7 +14121,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="337" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B337" t="s">
         <v>477</v>
       </c>
@@ -13877,7 +14153,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="338" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B338" t="s">
         <v>477</v>
       </c>
@@ -13909,7 +14185,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="339" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B339" t="s">
         <v>477</v>
       </c>
@@ -13941,7 +14217,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="340" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B340" t="s">
         <v>477</v>
       </c>
@@ -13973,7 +14249,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="341" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B341" t="s">
         <v>477</v>
       </c>
@@ -14005,7 +14281,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="342" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B342" t="s">
         <v>477</v>
       </c>
@@ -14037,7 +14313,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="343" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B343" t="s">
         <v>477</v>
       </c>
@@ -14069,7 +14345,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="344" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B344" t="s">
         <v>477</v>
       </c>
@@ -14101,7 +14377,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="345" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B345" t="s">
         <v>477</v>
       </c>
@@ -14133,7 +14409,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="346" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B346" t="s">
         <v>477</v>
       </c>
@@ -14165,7 +14441,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="347" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B347" t="s">
         <v>477</v>
       </c>
@@ -14197,7 +14473,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="348" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B348" t="s">
         <v>477</v>
       </c>
@@ -14229,7 +14505,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="349" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B349" t="s">
         <v>477</v>
       </c>
@@ -14261,7 +14537,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="350" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B350" t="s">
         <v>477</v>
       </c>
@@ -14293,7 +14569,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="351" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B351" t="s">
         <v>477</v>
       </c>
@@ -14325,7 +14601,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="352" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B352" t="s">
         <v>477</v>
       </c>
@@ -14357,7 +14633,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="353" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B353" t="s">
         <v>477</v>
       </c>
@@ -14389,7 +14665,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="354" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B354" t="s">
         <v>477</v>
       </c>
@@ -14421,7 +14697,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="355" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B355" t="s">
         <v>477</v>
       </c>
@@ -14453,7 +14729,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="356" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B356" t="s">
         <v>477</v>
       </c>
@@ -14485,7 +14761,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="357" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B357" t="s">
         <v>477</v>
       </c>
@@ -14517,7 +14793,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="358" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B358" t="s">
         <v>477</v>
       </c>
@@ -14549,7 +14825,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="359" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B359" t="s">
         <v>477</v>
       </c>
@@ -14581,7 +14857,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="360" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B360" t="s">
         <v>477</v>
       </c>
@@ -14613,7 +14889,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="361" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B361" t="s">
         <v>477</v>
       </c>
@@ -14645,7 +14921,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="362" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B362" t="s">
         <v>477</v>
       </c>
@@ -14677,7 +14953,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="363" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B363" t="s">
         <v>477</v>
       </c>
@@ -14709,7 +14985,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="364" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B364" t="s">
         <v>477</v>
       </c>
@@ -14741,7 +15017,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="365" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B365" t="s">
         <v>477</v>
       </c>
@@ -14773,7 +15049,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="366" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B366" t="s">
         <v>477</v>
       </c>
@@ -14805,7 +15081,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="367" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B367" t="s">
         <v>477</v>
       </c>
@@ -14837,7 +15113,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="368" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B368" t="s">
         <v>477</v>
       </c>
@@ -14869,7 +15145,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="369" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B369" t="s">
         <v>477</v>
       </c>
@@ -14901,7 +15177,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="370" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B370" t="s">
         <v>477</v>
       </c>
@@ -14933,7 +15209,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="371" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B371" t="s">
         <v>477</v>
       </c>
@@ -14968,7 +15244,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="372" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B372" t="s">
         <v>477</v>
       </c>
@@ -15003,7 +15279,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="373" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B373" t="s">
         <v>477</v>
       </c>
@@ -15038,7 +15314,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="374" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B374" t="s">
         <v>477</v>
       </c>
@@ -15073,7 +15349,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="375" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B375" t="s">
         <v>477</v>
       </c>
@@ -15108,7 +15384,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="376" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B376" t="s">
         <v>477</v>
       </c>
@@ -15143,7 +15419,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="377" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B377" t="s">
         <v>477</v>
       </c>
@@ -15178,7 +15454,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="378" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B378" t="s">
         <v>477</v>
       </c>
@@ -15213,7 +15489,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="379" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B379" t="s">
         <v>477</v>
       </c>
@@ -15248,7 +15524,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="380" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B380" t="s">
         <v>477</v>
       </c>
@@ -15283,7 +15559,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="381" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B381" t="s">
         <v>477</v>
       </c>
@@ -15318,7 +15594,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="382" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B382" t="s">
         <v>477</v>
       </c>
@@ -15353,7 +15629,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="383" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B383" t="s">
         <v>477</v>
       </c>
@@ -15388,7 +15664,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="384" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B384" t="s">
         <v>477</v>
       </c>
@@ -15423,7 +15699,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="385" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B385" t="s">
         <v>477</v>
       </c>
@@ -15455,7 +15731,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="386" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B386" t="s">
         <v>477</v>
       </c>
@@ -15487,7 +15763,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="387" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B387" t="s">
         <v>477</v>
       </c>
@@ -15519,7 +15795,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="388" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B388" t="s">
         <v>477</v>
       </c>
@@ -15551,7 +15827,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="389" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B389" t="s">
         <v>477</v>
       </c>
@@ -15583,7 +15859,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="390" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B390" t="s">
         <v>477</v>
       </c>
@@ -15615,7 +15891,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="391" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B391" t="s">
         <v>477</v>
       </c>
@@ -15647,7 +15923,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="392" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B392" t="s">
         <v>477</v>
       </c>
@@ -15679,7 +15955,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="393" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B393" t="s">
         <v>477</v>
       </c>
@@ -15711,7 +15987,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="394" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B394" t="s">
         <v>477</v>
       </c>
@@ -15743,7 +16019,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="395" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B395" t="s">
         <v>477</v>
       </c>
@@ -15775,7 +16051,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="396" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B396" t="s">
         <v>477</v>
       </c>
@@ -15807,7 +16083,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="397" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B397" t="s">
         <v>477</v>
       </c>
@@ -15839,7 +16115,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="398" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B398" t="s">
         <v>477</v>
       </c>
@@ -15871,7 +16147,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="399" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B399" t="s">
         <v>477</v>
       </c>
@@ -15903,7 +16179,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="400" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B400" t="s">
         <v>477</v>
       </c>
@@ -15935,7 +16211,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="401" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B401" t="s">
         <v>477</v>
       </c>
@@ -15967,7 +16243,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="402" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B402" t="s">
         <v>477</v>
       </c>
@@ -15999,7 +16275,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="403" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B403" t="s">
         <v>477</v>
       </c>
@@ -16031,7 +16307,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="404" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B404" t="s">
         <v>477</v>
       </c>
@@ -16063,7 +16339,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="405" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B405" t="s">
         <v>477</v>
       </c>
@@ -16095,7 +16371,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="406" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B406" t="s">
         <v>477</v>
       </c>
@@ -16127,7 +16403,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="407" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B407" t="s">
         <v>477</v>
       </c>
@@ -16159,7 +16435,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="408" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B408" t="s">
         <v>477</v>
       </c>
@@ -16191,7 +16467,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="409" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B409" t="s">
         <v>477</v>
       </c>
@@ -16223,7 +16499,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="410" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B410" t="s">
         <v>477</v>
       </c>
@@ -16255,7 +16531,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="411" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B411" t="s">
         <v>477</v>
       </c>
@@ -16287,7 +16563,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="412" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B412" t="s">
         <v>477</v>
       </c>
@@ -16319,7 +16595,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="413" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B413" t="s">
         <v>477</v>
       </c>
@@ -16351,7 +16627,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="414" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B414" t="s">
         <v>477</v>
       </c>
@@ -16383,7 +16659,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="415" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B415" t="s">
         <v>477</v>
       </c>
@@ -16415,7 +16691,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="416" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B416" t="s">
         <v>477</v>
       </c>
@@ -16447,7 +16723,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="417" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B417" t="s">
         <v>477</v>
       </c>
@@ -16479,7 +16755,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="418" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B418" t="s">
         <v>477</v>
       </c>
@@ -16511,7 +16787,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="419" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B419" t="s">
         <v>477</v>
       </c>
@@ -16543,7 +16819,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="420" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B420" t="s">
         <v>477</v>
       </c>
@@ -16575,7 +16851,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="421" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B421" t="s">
         <v>477</v>
       </c>
@@ -16607,7 +16883,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="422" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B422" t="s">
         <v>477</v>
       </c>
@@ -16639,7 +16915,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="423" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B423" t="s">
         <v>477</v>
       </c>
@@ -16671,7 +16947,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="424" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B424" t="s">
         <v>477</v>
       </c>
@@ -16703,7 +16979,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="425" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B425" t="s">
         <v>477</v>
       </c>
@@ -16735,7 +17011,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="426" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B426" t="s">
         <v>477</v>
       </c>
@@ -16767,7 +17043,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="427" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B427" t="s">
         <v>477</v>
       </c>
@@ -16799,7 +17075,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="428" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B428" t="s">
         <v>477</v>
       </c>
@@ -16831,7 +17107,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="429" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B429" t="s">
         <v>477</v>
       </c>
@@ -16863,7 +17139,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="430" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B430" t="s">
         <v>477</v>
       </c>
@@ -16895,7 +17171,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="431" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B431" t="s">
         <v>477</v>
       </c>
@@ -16921,7 +17197,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="432" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B432" t="s">
         <v>477</v>
       </c>
@@ -16947,7 +17223,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="433" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B433" t="s">
         <v>477</v>
       </c>
@@ -16973,7 +17249,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="434" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B434" t="s">
         <v>477</v>
       </c>
@@ -16999,7 +17275,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="435" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B435" t="s">
         <v>477</v>
       </c>
@@ -17025,7 +17301,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="436" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B436" t="s">
         <v>477</v>
       </c>
@@ -17051,7 +17327,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="437" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B437" t="s">
         <v>477</v>
       </c>
@@ -17077,7 +17353,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="438" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B438" t="s">
         <v>477</v>
       </c>
@@ -17103,7 +17379,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="439" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B439" t="s">
         <v>477</v>
       </c>
@@ -17129,7 +17405,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="440" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B440" t="s">
         <v>477</v>
       </c>
@@ -17155,7 +17431,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="441" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B441" t="s">
         <v>477</v>
       </c>
@@ -17181,7 +17457,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="442" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B442" t="s">
         <v>477</v>
       </c>
@@ -17207,7 +17483,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="443" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B443" t="s">
         <v>477</v>
       </c>
@@ -17233,7 +17509,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="444" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B444" t="s">
         <v>477</v>
       </c>
@@ -17259,7 +17535,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="445" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B445" t="s">
         <v>477</v>
       </c>
@@ -17285,7 +17561,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="446" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B446" t="s">
         <v>477</v>
       </c>
@@ -17311,7 +17587,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="447" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B447" t="s">
         <v>477</v>
       </c>
@@ -17337,7 +17613,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="448" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B448" t="s">
         <v>477</v>
       </c>
@@ -17369,7 +17645,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="449" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B449" t="s">
         <v>477</v>
       </c>
@@ -17401,7 +17677,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="450" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B450" t="s">
         <v>477</v>
       </c>
@@ -17433,7 +17709,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="451" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B451" t="s">
         <v>477</v>
       </c>
@@ -17465,7 +17741,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="452" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B452" t="s">
         <v>477</v>
       </c>
@@ -17497,7 +17773,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="453" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B453" t="s">
         <v>477</v>
       </c>
@@ -17529,7 +17805,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="454" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B454" t="s">
         <v>477</v>
       </c>
@@ -17561,7 +17837,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="455" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B455" t="s">
         <v>477</v>
       </c>
@@ -17593,7 +17869,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="456" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B456" t="s">
         <v>477</v>
       </c>
@@ -17625,7 +17901,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="457" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B457" t="s">
         <v>477</v>
       </c>
@@ -17651,7 +17927,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="458" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B458" t="s">
         <v>477</v>
       </c>
@@ -17677,7 +17953,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="459" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B459" t="s">
         <v>477</v>
       </c>
@@ -17703,7 +17979,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="460" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B460" t="s">
         <v>477</v>
       </c>
@@ -17729,7 +18005,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="461" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B461" t="s">
         <v>477</v>
       </c>
@@ -17755,7 +18031,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="462" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B462" t="s">
         <v>477</v>
       </c>
@@ -17781,7 +18057,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="463" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B463" t="s">
         <v>477</v>
       </c>
@@ -17807,7 +18083,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="464" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B464" t="s">
         <v>477</v>
       </c>
@@ -17833,7 +18109,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="465" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B465" t="s">
         <v>477</v>
       </c>
@@ -17859,7 +18135,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="466" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B466" t="s">
         <v>477</v>
       </c>
@@ -17885,7 +18161,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="467" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B467" t="s">
         <v>477</v>
       </c>
@@ -17923,7 +18199,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="468" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B468" t="s">
         <v>477</v>
       </c>
@@ -17958,7 +18234,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="469" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B469" t="s">
         <v>477</v>
       </c>
@@ -17993,7 +18269,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="470" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B470" t="s">
         <v>477</v>
       </c>
@@ -18028,7 +18304,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="471" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B471" t="s">
         <v>477</v>
       </c>
@@ -18063,7 +18339,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="472" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B472" t="s">
         <v>858</v>
       </c>
@@ -18098,7 +18374,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="473" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B473" t="s">
         <v>858</v>
       </c>
@@ -18131,6 +18407,860 @@
       </c>
       <c r="O473" t="s">
         <v>866</v>
+      </c>
+    </row>
+    <row r="474" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B474" t="s">
+        <v>858</v>
+      </c>
+      <c r="C474" t="s">
+        <v>868</v>
+      </c>
+      <c r="E474" t="s">
+        <v>140</v>
+      </c>
+      <c r="F474" t="s">
+        <v>869</v>
+      </c>
+      <c r="G474" t="s">
+        <v>869</v>
+      </c>
+      <c r="H474" t="s">
+        <v>461</v>
+      </c>
+      <c r="I474" t="s">
+        <v>839</v>
+      </c>
+      <c r="J474" t="s">
+        <v>872</v>
+      </c>
+      <c r="L474" t="s">
+        <v>873</v>
+      </c>
+      <c r="M474" t="s">
+        <v>457</v>
+      </c>
+      <c r="N474" t="s">
+        <v>467</v>
+      </c>
+      <c r="O474" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="475" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B475" t="s">
+        <v>858</v>
+      </c>
+      <c r="C475" t="s">
+        <v>868</v>
+      </c>
+      <c r="D475" t="s">
+        <v>871</v>
+      </c>
+      <c r="E475" t="s">
+        <v>140</v>
+      </c>
+      <c r="F475" t="s">
+        <v>870</v>
+      </c>
+      <c r="H475" t="s">
+        <v>461</v>
+      </c>
+      <c r="I475" t="s">
+        <v>839</v>
+      </c>
+      <c r="J475" t="s">
+        <v>875</v>
+      </c>
+      <c r="L475" t="s">
+        <v>768</v>
+      </c>
+      <c r="M475" t="s">
+        <v>876</v>
+      </c>
+      <c r="N475" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="476" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B476" t="s">
+        <v>858</v>
+      </c>
+      <c r="C476" t="s">
+        <v>859</v>
+      </c>
+      <c r="E476" t="s">
+        <v>140</v>
+      </c>
+      <c r="F476" t="s">
+        <v>877</v>
+      </c>
+      <c r="G476" t="s">
+        <v>877</v>
+      </c>
+      <c r="H476" t="s">
+        <v>906</v>
+      </c>
+      <c r="I476" t="s">
+        <v>839</v>
+      </c>
+      <c r="J476" t="s">
+        <v>879</v>
+      </c>
+      <c r="L476" t="s">
+        <v>861</v>
+      </c>
+      <c r="M476" t="s">
+        <v>457</v>
+      </c>
+      <c r="N476" t="s">
+        <v>467</v>
+      </c>
+      <c r="O476" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="477" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B477" t="s">
+        <v>858</v>
+      </c>
+      <c r="C477" t="s">
+        <v>884</v>
+      </c>
+      <c r="D477" t="s">
+        <v>887</v>
+      </c>
+      <c r="E477" t="s">
+        <v>140</v>
+      </c>
+      <c r="F477" t="s">
+        <v>880</v>
+      </c>
+      <c r="G477" t="s">
+        <v>880</v>
+      </c>
+      <c r="H477" t="s">
+        <v>883</v>
+      </c>
+      <c r="I477" t="s">
+        <v>839</v>
+      </c>
+      <c r="J477" t="s">
+        <v>881</v>
+      </c>
+      <c r="L477" t="s">
+        <v>768</v>
+      </c>
+      <c r="M477" t="s">
+        <v>457</v>
+      </c>
+      <c r="N477" t="s">
+        <v>883</v>
+      </c>
+      <c r="O477" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="478" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B478" t="s">
+        <v>858</v>
+      </c>
+      <c r="C478" t="s">
+        <v>885</v>
+      </c>
+      <c r="D478" t="s">
+        <v>886</v>
+      </c>
+      <c r="E478" t="s">
+        <v>140</v>
+      </c>
+      <c r="F478" t="s">
+        <v>888</v>
+      </c>
+      <c r="G478" t="s">
+        <v>888</v>
+      </c>
+      <c r="H478" t="s">
+        <v>891</v>
+      </c>
+      <c r="I478" t="s">
+        <v>839</v>
+      </c>
+      <c r="J478" t="s">
+        <v>889</v>
+      </c>
+      <c r="L478" t="s">
+        <v>768</v>
+      </c>
+      <c r="M478" t="s">
+        <v>457</v>
+      </c>
+      <c r="N478" t="s">
+        <v>467</v>
+      </c>
+      <c r="O478" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="479" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B479" t="s">
+        <v>858</v>
+      </c>
+      <c r="C479" t="s">
+        <v>885</v>
+      </c>
+      <c r="D479" t="s">
+        <v>886</v>
+      </c>
+      <c r="E479" t="s">
+        <v>140</v>
+      </c>
+      <c r="F479" t="s">
+        <v>892</v>
+      </c>
+      <c r="G479" t="s">
+        <v>892</v>
+      </c>
+      <c r="H479" t="s">
+        <v>895</v>
+      </c>
+      <c r="I479" t="s">
+        <v>839</v>
+      </c>
+      <c r="J479" t="s">
+        <v>893</v>
+      </c>
+      <c r="L479" t="s">
+        <v>768</v>
+      </c>
+      <c r="M479" t="s">
+        <v>457</v>
+      </c>
+      <c r="N479" t="s">
+        <v>467</v>
+      </c>
+      <c r="O479" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="480" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B480" t="s">
+        <v>858</v>
+      </c>
+      <c r="C480" t="s">
+        <v>902</v>
+      </c>
+      <c r="E480" t="s">
+        <v>140</v>
+      </c>
+      <c r="F480" t="s">
+        <v>900</v>
+      </c>
+      <c r="G480" t="s">
+        <v>900</v>
+      </c>
+      <c r="H480" t="s">
+        <v>896</v>
+      </c>
+      <c r="I480" t="s">
+        <v>839</v>
+      </c>
+      <c r="J480" t="s">
+        <v>897</v>
+      </c>
+      <c r="L480" t="s">
+        <v>865</v>
+      </c>
+      <c r="M480" t="s">
+        <v>457</v>
+      </c>
+      <c r="N480" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="481" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B481" t="s">
+        <v>858</v>
+      </c>
+      <c r="C481" t="s">
+        <v>902</v>
+      </c>
+      <c r="E481" t="s">
+        <v>140</v>
+      </c>
+      <c r="F481" t="s">
+        <v>901</v>
+      </c>
+      <c r="G481" t="s">
+        <v>901</v>
+      </c>
+      <c r="H481" t="s">
+        <v>896</v>
+      </c>
+      <c r="I481" t="s">
+        <v>839</v>
+      </c>
+      <c r="J481" t="s">
+        <v>898</v>
+      </c>
+      <c r="L481" t="s">
+        <v>865</v>
+      </c>
+      <c r="M481" t="s">
+        <v>457</v>
+      </c>
+      <c r="N481" t="s">
+        <v>467</v>
+      </c>
+      <c r="O481" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="482" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B482" t="s">
+        <v>858</v>
+      </c>
+      <c r="C482" t="s">
+        <v>902</v>
+      </c>
+      <c r="E482" t="s">
+        <v>140</v>
+      </c>
+      <c r="F482" t="s">
+        <v>903</v>
+      </c>
+      <c r="G482" t="s">
+        <v>903</v>
+      </c>
+      <c r="H482" t="s">
+        <v>906</v>
+      </c>
+      <c r="I482" t="s">
+        <v>839</v>
+      </c>
+      <c r="J482" t="s">
+        <v>904</v>
+      </c>
+      <c r="L482" t="s">
+        <v>865</v>
+      </c>
+      <c r="M482" t="s">
+        <v>457</v>
+      </c>
+      <c r="N482" t="s">
+        <v>467</v>
+      </c>
+      <c r="O482" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="483" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B483" t="s">
+        <v>858</v>
+      </c>
+      <c r="C483" t="s">
+        <v>907</v>
+      </c>
+      <c r="E483" t="s">
+        <v>140</v>
+      </c>
+      <c r="F483" t="s">
+        <v>908</v>
+      </c>
+      <c r="G483" t="s">
+        <v>909</v>
+      </c>
+      <c r="H483" t="s">
+        <v>896</v>
+      </c>
+      <c r="I483" t="s">
+        <v>839</v>
+      </c>
+      <c r="J483" t="s">
+        <v>911</v>
+      </c>
+      <c r="L483" t="s">
+        <v>912</v>
+      </c>
+      <c r="M483" t="s">
+        <v>876</v>
+      </c>
+      <c r="N483" t="s">
+        <v>467</v>
+      </c>
+      <c r="O483" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="484" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B484" t="s">
+        <v>858</v>
+      </c>
+      <c r="C484" t="s">
+        <v>913</v>
+      </c>
+      <c r="D484" t="s">
+        <v>930</v>
+      </c>
+      <c r="E484" t="s">
+        <v>140</v>
+      </c>
+      <c r="F484" t="s">
+        <v>914</v>
+      </c>
+      <c r="G484" t="s">
+        <v>914</v>
+      </c>
+      <c r="H484" t="s">
+        <v>924</v>
+      </c>
+      <c r="I484" t="s">
+        <v>839</v>
+      </c>
+      <c r="J484" t="s">
+        <v>925</v>
+      </c>
+      <c r="L484" t="s">
+        <v>768</v>
+      </c>
+      <c r="M484" t="s">
+        <v>457</v>
+      </c>
+      <c r="N484" t="s">
+        <v>467</v>
+      </c>
+      <c r="O484" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="485" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B485" t="s">
+        <v>858</v>
+      </c>
+      <c r="C485" t="s">
+        <v>913</v>
+      </c>
+      <c r="D485" t="s">
+        <v>930</v>
+      </c>
+      <c r="E485" t="s">
+        <v>140</v>
+      </c>
+      <c r="F485" t="s">
+        <v>915</v>
+      </c>
+      <c r="G485" t="s">
+        <v>915</v>
+      </c>
+      <c r="H485" t="s">
+        <v>924</v>
+      </c>
+      <c r="I485" t="s">
+        <v>839</v>
+      </c>
+      <c r="J485" t="s">
+        <v>926</v>
+      </c>
+      <c r="L485" t="s">
+        <v>768</v>
+      </c>
+      <c r="M485" t="s">
+        <v>457</v>
+      </c>
+      <c r="N485" t="s">
+        <v>467</v>
+      </c>
+      <c r="O485" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="486" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B486" t="s">
+        <v>858</v>
+      </c>
+      <c r="C486" t="s">
+        <v>913</v>
+      </c>
+      <c r="D486" t="s">
+        <v>931</v>
+      </c>
+      <c r="E486" t="s">
+        <v>140</v>
+      </c>
+      <c r="F486" t="s">
+        <v>916</v>
+      </c>
+      <c r="G486" t="s">
+        <v>916</v>
+      </c>
+      <c r="H486" t="s">
+        <v>924</v>
+      </c>
+      <c r="I486" t="s">
+        <v>839</v>
+      </c>
+      <c r="J486" t="s">
+        <v>927</v>
+      </c>
+      <c r="L486" t="s">
+        <v>768</v>
+      </c>
+      <c r="M486" t="s">
+        <v>457</v>
+      </c>
+      <c r="N486" t="s">
+        <v>467</v>
+      </c>
+      <c r="O486" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="487" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B487" t="s">
+        <v>858</v>
+      </c>
+      <c r="C487" t="s">
+        <v>913</v>
+      </c>
+      <c r="D487" t="s">
+        <v>931</v>
+      </c>
+      <c r="E487" t="s">
+        <v>140</v>
+      </c>
+      <c r="F487" t="s">
+        <v>917</v>
+      </c>
+      <c r="G487" t="s">
+        <v>917</v>
+      </c>
+      <c r="H487" t="s">
+        <v>924</v>
+      </c>
+      <c r="I487" t="s">
+        <v>839</v>
+      </c>
+      <c r="J487" t="s">
+        <v>928</v>
+      </c>
+      <c r="L487" t="s">
+        <v>768</v>
+      </c>
+      <c r="M487" t="s">
+        <v>457</v>
+      </c>
+      <c r="N487" t="s">
+        <v>467</v>
+      </c>
+      <c r="O487" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="488" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B488" t="s">
+        <v>858</v>
+      </c>
+      <c r="C488" t="s">
+        <v>913</v>
+      </c>
+      <c r="D488" t="s">
+        <v>931</v>
+      </c>
+      <c r="E488" t="s">
+        <v>140</v>
+      </c>
+      <c r="F488" t="s">
+        <v>918</v>
+      </c>
+      <c r="G488" t="s">
+        <v>918</v>
+      </c>
+      <c r="H488" t="s">
+        <v>924</v>
+      </c>
+      <c r="I488" t="s">
+        <v>839</v>
+      </c>
+      <c r="J488" t="s">
+        <v>929</v>
+      </c>
+      <c r="L488" t="s">
+        <v>768</v>
+      </c>
+      <c r="M488" t="s">
+        <v>457</v>
+      </c>
+      <c r="N488" t="s">
+        <v>467</v>
+      </c>
+      <c r="O488" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="489" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B489" t="s">
+        <v>858</v>
+      </c>
+      <c r="C489" t="s">
+        <v>902</v>
+      </c>
+      <c r="E489" t="s">
+        <v>140</v>
+      </c>
+      <c r="F489" t="s">
+        <v>932</v>
+      </c>
+      <c r="G489" t="s">
+        <v>932</v>
+      </c>
+      <c r="H489" t="s">
+        <v>933</v>
+      </c>
+      <c r="I489" t="s">
+        <v>300</v>
+      </c>
+      <c r="J489" t="s">
+        <v>934</v>
+      </c>
+      <c r="L489" t="s">
+        <v>865</v>
+      </c>
+      <c r="M489" t="s">
+        <v>457</v>
+      </c>
+      <c r="N489" t="s">
+        <v>467</v>
+      </c>
+      <c r="O489" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="490" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B490" t="s">
+        <v>858</v>
+      </c>
+      <c r="C490" t="s">
+        <v>913</v>
+      </c>
+      <c r="D490" t="s">
+        <v>930</v>
+      </c>
+      <c r="E490" t="s">
+        <v>140</v>
+      </c>
+      <c r="F490" t="s">
+        <v>936</v>
+      </c>
+      <c r="G490" t="s">
+        <v>936</v>
+      </c>
+      <c r="H490" t="s">
+        <v>937</v>
+      </c>
+      <c r="I490" t="s">
+        <v>300</v>
+      </c>
+      <c r="J490" t="s">
+        <v>938</v>
+      </c>
+      <c r="L490" t="s">
+        <v>865</v>
+      </c>
+      <c r="M490" t="s">
+        <v>457</v>
+      </c>
+      <c r="N490" t="s">
+        <v>467</v>
+      </c>
+      <c r="O490" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="491" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B491" t="s">
+        <v>858</v>
+      </c>
+      <c r="C491" t="s">
+        <v>944</v>
+      </c>
+      <c r="D491" t="s">
+        <v>943</v>
+      </c>
+      <c r="E491" t="s">
+        <v>140</v>
+      </c>
+      <c r="F491" t="s">
+        <v>940</v>
+      </c>
+      <c r="G491" t="s">
+        <v>940</v>
+      </c>
+      <c r="I491" t="s">
+        <v>843</v>
+      </c>
+      <c r="J491" t="s">
+        <v>941</v>
+      </c>
+      <c r="L491" t="s">
+        <v>865</v>
+      </c>
+      <c r="M491" t="s">
+        <v>457</v>
+      </c>
+      <c r="N491" t="s">
+        <v>467</v>
+      </c>
+      <c r="O491" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="492" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B492" t="s">
+        <v>858</v>
+      </c>
+      <c r="C492" t="s">
+        <v>902</v>
+      </c>
+      <c r="E492" t="s">
+        <v>140</v>
+      </c>
+      <c r="F492" t="s">
+        <v>945</v>
+      </c>
+      <c r="G492" t="s">
+        <v>945</v>
+      </c>
+      <c r="H492" t="s">
+        <v>948</v>
+      </c>
+      <c r="I492" t="s">
+        <v>146</v>
+      </c>
+      <c r="J492" t="s">
+        <v>947</v>
+      </c>
+      <c r="L492" t="s">
+        <v>865</v>
+      </c>
+      <c r="M492" t="s">
+        <v>457</v>
+      </c>
+      <c r="N492" t="s">
+        <v>467</v>
+      </c>
+      <c r="O492" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="493" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B493" t="s">
+        <v>858</v>
+      </c>
+      <c r="C493" t="s">
+        <v>868</v>
+      </c>
+      <c r="E493" t="s">
+        <v>140</v>
+      </c>
+      <c r="F493" t="s">
+        <v>949</v>
+      </c>
+      <c r="G493" t="s">
+        <v>949</v>
+      </c>
+      <c r="H493" t="s">
+        <v>950</v>
+      </c>
+      <c r="I493" t="s">
+        <v>146</v>
+      </c>
+      <c r="J493" t="s">
+        <v>951</v>
+      </c>
+      <c r="L493" t="s">
+        <v>873</v>
+      </c>
+      <c r="M493" t="s">
+        <v>457</v>
+      </c>
+      <c r="N493" t="s">
+        <v>467</v>
+      </c>
+      <c r="O493" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="494" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B494" t="s">
+        <v>858</v>
+      </c>
+      <c r="C494" t="s">
+        <v>902</v>
+      </c>
+      <c r="E494" t="s">
+        <v>140</v>
+      </c>
+      <c r="F494" t="s">
+        <v>953</v>
+      </c>
+      <c r="G494" t="s">
+        <v>953</v>
+      </c>
+      <c r="I494" t="s">
+        <v>145</v>
+      </c>
+      <c r="J494" t="s">
+        <v>954</v>
+      </c>
+      <c r="L494" t="s">
+        <v>865</v>
+      </c>
+      <c r="M494" t="s">
+        <v>457</v>
+      </c>
+      <c r="N494" t="s">
+        <v>467</v>
+      </c>
+      <c r="O494" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="495" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B495" t="s">
+        <v>858</v>
+      </c>
+      <c r="C495" t="s">
+        <v>868</v>
+      </c>
+      <c r="E495" t="s">
+        <v>140</v>
+      </c>
+      <c r="F495" t="s">
+        <v>957</v>
+      </c>
+      <c r="G495" t="s">
+        <v>957</v>
+      </c>
+      <c r="H495" t="s">
+        <v>956</v>
+      </c>
+      <c r="I495" t="s">
+        <v>145</v>
+      </c>
+      <c r="J495" t="s">
+        <v>958</v>
+      </c>
+      <c r="L495" t="s">
+        <v>873</v>
+      </c>
+      <c r="M495" t="s">
+        <v>457</v>
+      </c>
+      <c r="N495" t="s">
+        <v>467</v>
+      </c>
+      <c r="O495" t="s">
+        <v>959</v>
       </c>
     </row>
   </sheetData>

--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C174A180-FBFB-4399-9FF6-C57E98E06352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE52FE1-9181-4252-A572-0AA5B352E672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8960" yWindow="0" windowWidth="14170" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4999" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5516" uniqueCount="1100">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -2719,9 +2719,6 @@
     <t>https://www.investing.com/economic-calendar/cb-consumer-confidence-48</t>
   </si>
   <si>
-    <t>Conference Board</t>
-  </si>
-  <si>
     <t>CONSSENT</t>
   </si>
   <si>
@@ -2924,13 +2921,436 @@
   </si>
   <si>
     <t>https://kr.investing.com/economic-calendar/interest-rate-decision-165</t>
+  </si>
+  <si>
+    <t>KOEXTOTY</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-export-growth-1316</t>
+  </si>
+  <si>
+    <t>South Korea Export YoY Index</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>NFCI</t>
+  </si>
+  <si>
+    <t>ANFCI</t>
+  </si>
+  <si>
+    <t>NFCIRISK</t>
+  </si>
+  <si>
+    <t>NFCICRDT</t>
+  </si>
+  <si>
+    <t>NFCILVRG</t>
+  </si>
+  <si>
+    <t>NFCINFLV</t>
+  </si>
+  <si>
+    <t>https://www.chicagofed.org/research/data/nfci/current-data</t>
+  </si>
+  <si>
+    <t>CHICAGOFED</t>
+  </si>
+  <si>
+    <t>National Financial Conditions Index</t>
+  </si>
+  <si>
+    <t>Adjusted National Financial Conditions Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Financial Conditions Risk Index </t>
+  </si>
+  <si>
+    <t>National Financial Conditions Credit Index</t>
+  </si>
+  <si>
+    <t>National Financial Conditions Leverage Index</t>
+  </si>
+  <si>
+    <t>National Financial Conditions Non financial Leverage Index</t>
+  </si>
+  <si>
+    <t>OFR</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Index</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>liability</t>
+  </si>
+  <si>
+    <t>FSI</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Credit Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Equity Valuation Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Funding Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Safe Assets Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Volatility Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress United States Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Emerging Market Index</t>
+  </si>
+  <si>
+    <t>OFR Financial Stress Other Advanced Economics Index</t>
+  </si>
+  <si>
+    <t>https://www.financialresearch.gov/financial-stress-index/regions/</t>
+  </si>
+  <si>
+    <t>https://www.financialresearch.gov/financial-stress-index/</t>
+  </si>
+  <si>
+    <t>FSICRDT</t>
+  </si>
+  <si>
+    <t>FSIEQVL</t>
+  </si>
+  <si>
+    <t>FSIFUND</t>
+  </si>
+  <si>
+    <t>FSISFAS</t>
+  </si>
+  <si>
+    <t>FSIVOL</t>
+  </si>
+  <si>
+    <t>FSIUSA</t>
+  </si>
+  <si>
+    <t>FSIEM</t>
+  </si>
+  <si>
+    <t>FSIEX</t>
+  </si>
+  <si>
+    <t>Financial Condition</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>SPX50010</t>
+  </si>
+  <si>
+    <t>SPX50015</t>
+  </si>
+  <si>
+    <t>SPX50020</t>
+  </si>
+  <si>
+    <t>SPX50025</t>
+  </si>
+  <si>
+    <t>SPX50030</t>
+  </si>
+  <si>
+    <t>SPX50035</t>
+  </si>
+  <si>
+    <t>SPX50040</t>
+  </si>
+  <si>
+    <t>SPX50045</t>
+  </si>
+  <si>
+    <t>SPX50050</t>
+  </si>
+  <si>
+    <t>SPX50055</t>
+  </si>
+  <si>
+    <t>SPX50060</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Energy Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Materials Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Industrials Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Consumer Discretionary Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Consumer Staples Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Health Care Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Financials Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Information Technology Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Communication Services Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Utilities Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Real Estate Index</t>
+  </si>
+  <si>
+    <t>YAHOO</t>
+  </si>
+  <si>
+    <t>^GSPE</t>
+  </si>
+  <si>
+    <t>^SP500-15</t>
+  </si>
+  <si>
+    <t>^SP500-20</t>
+  </si>
+  <si>
+    <t>^SP500-25</t>
+  </si>
+  <si>
+    <t>^SP500-30</t>
+  </si>
+  <si>
+    <t>^SP500-35</t>
+  </si>
+  <si>
+    <t>^SP500-40</t>
+  </si>
+  <si>
+    <t>^SP500-45</t>
+  </si>
+  <si>
+    <t>^SP500-50</t>
+  </si>
+  <si>
+    <t>^SP500-55</t>
+  </si>
+  <si>
+    <t>^SP500-60</t>
+  </si>
+  <si>
+    <t>SPX500101020</t>
+  </si>
+  <si>
+    <t>SPX500201010</t>
+  </si>
+  <si>
+    <t>SPX150015104010</t>
+  </si>
+  <si>
+    <t>SPX50010102030</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Oil, Gas &amp; Consumable Fuels Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Aerospace &amp; Defense Index</t>
+  </si>
+  <si>
+    <t>S&amp;P1500 Aluminum Index</t>
+  </si>
+  <si>
+    <t>S&amp;P500 Oil &amp; Gas Exploration &amp; Production Index</t>
+  </si>
+  <si>
+    <t>MARKETWATCH</t>
+  </si>
+  <si>
+    <t>VIX</t>
+  </si>
+  <si>
+    <t>VVIX</t>
+  </si>
+  <si>
+    <t>GAMMA</t>
+  </si>
+  <si>
+    <t>SKEW</t>
+  </si>
+  <si>
+    <t>VXN</t>
+  </si>
+  <si>
+    <t>NKVI</t>
+  </si>
+  <si>
+    <t>VHSI</t>
+  </si>
+  <si>
+    <t>VKOSPI</t>
+  </si>
+  <si>
+    <t>MOVE</t>
+  </si>
+  <si>
+    <t>GVZ</t>
+  </si>
+  <si>
+    <t>VXGDX</t>
+  </si>
+  <si>
+    <t>VXEEM</t>
+  </si>
+  <si>
+    <t>VXSLV</t>
+  </si>
+  <si>
+    <t>OVX</t>
+  </si>
+  <si>
+    <t>BITVX</t>
+  </si>
+  <si>
+    <t>TRADINGVIEW</t>
+  </si>
+  <si>
+    <t>CBOE Realized Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE VIX Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE SKEW Index</t>
+  </si>
+  <si>
+    <t>CBOE NASDAQ100 Volatility Index</t>
+  </si>
+  <si>
+    <t>OSE</t>
+  </si>
+  <si>
+    <t>COBE</t>
+  </si>
+  <si>
+    <t>HIS</t>
+  </si>
+  <si>
+    <t>HSI Volatility Index</t>
+  </si>
+  <si>
+    <t>KRX Volatility Index</t>
+  </si>
+  <si>
+    <t>KRX</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>CBOE Emerging Markets ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>ICE BofAML MOVE Index</t>
+  </si>
+  <si>
+    <t>ICE</t>
+  </si>
+  <si>
+    <t>Gold Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Gold Miners ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Silver ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Crude Oil Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Bitcoin ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>Bond</t>
+  </si>
+  <si>
+    <t>Crypto</t>
+  </si>
+  <si>
+    <t>VSTOXX</t>
+  </si>
+  <si>
+    <t>V2TX</t>
+  </si>
+  <si>
+    <t>STOXX</t>
+  </si>
+  <si>
+    <t>EUROSTOXX 50 Volatility Index</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/indices/stoxx-50-volatility-vstoxx-eur</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/indices/nikkei-volatility-historical-data</t>
+  </si>
+  <si>
+    <t>NIKKEI Average Volatility Index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2951,6 +3371,12 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2982,7 +3408,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3260,23 +3686,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O495"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O542"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" customWidth="1"/>
-    <col min="11" max="13" width="12.90625" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+    <col min="10" max="10" width="40.5546875" customWidth="1"/>
+    <col min="11" max="13" width="12.88671875" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3323,7 +3749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>450</v>
       </c>
@@ -3355,7 +3781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>450</v>
       </c>
@@ -3387,7 +3813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>450</v>
       </c>
@@ -3419,7 +3845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>450</v>
       </c>
@@ -3451,7 +3877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>450</v>
       </c>
@@ -3483,7 +3909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>450</v>
       </c>
@@ -3512,7 +3938,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -3532,7 +3958,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>450</v>
       </c>
@@ -3552,7 +3978,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>450</v>
       </c>
@@ -3572,7 +3998,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>450</v>
       </c>
@@ -3592,7 +4018,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>450</v>
       </c>
@@ -3612,7 +4038,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>450</v>
       </c>
@@ -3632,7 +4058,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>450</v>
       </c>
@@ -3652,7 +4078,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>450</v>
       </c>
@@ -3672,7 +4098,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>450</v>
       </c>
@@ -3692,7 +4118,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>450</v>
       </c>
@@ -3712,7 +4138,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>450</v>
       </c>
@@ -3732,7 +4158,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>450</v>
       </c>
@@ -3752,7 +4178,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>450</v>
       </c>
@@ -3772,7 +4198,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>450</v>
       </c>
@@ -3792,7 +4218,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>450</v>
       </c>
@@ -3812,7 +4238,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>450</v>
       </c>
@@ -3832,7 +4258,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>450</v>
       </c>
@@ -3852,7 +4278,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>450</v>
       </c>
@@ -3872,7 +4298,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>450</v>
       </c>
@@ -3892,7 +4318,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>450</v>
       </c>
@@ -3912,7 +4338,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>450</v>
       </c>
@@ -3932,7 +4358,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>450</v>
       </c>
@@ -3952,7 +4378,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>450</v>
       </c>
@@ -3972,7 +4398,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>450</v>
       </c>
@@ -3992,7 +4418,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>450</v>
       </c>
@@ -4012,7 +4438,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>450</v>
       </c>
@@ -4035,7 +4461,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>450</v>
       </c>
@@ -4058,7 +4484,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>450</v>
       </c>
@@ -4081,7 +4507,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>450</v>
       </c>
@@ -4104,7 +4530,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>450</v>
       </c>
@@ -4124,7 +4550,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>450</v>
       </c>
@@ -4144,7 +4570,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>450</v>
       </c>
@@ -4164,7 +4590,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>450</v>
       </c>
@@ -4184,7 +4610,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>450</v>
       </c>
@@ -4204,7 +4630,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>450</v>
       </c>
@@ -4224,7 +4650,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>450</v>
       </c>
@@ -4247,7 +4673,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>450</v>
       </c>
@@ -4270,7 +4696,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>450</v>
       </c>
@@ -4293,7 +4719,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>450</v>
       </c>
@@ -4316,7 +4742,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>450</v>
       </c>
@@ -4339,7 +4765,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>450</v>
       </c>
@@ -4362,7 +4788,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>450</v>
       </c>
@@ -4385,7 +4811,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>450</v>
       </c>
@@ -4405,7 +4831,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>450</v>
       </c>
@@ -4428,7 +4854,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>450</v>
       </c>
@@ -4448,7 +4874,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>450</v>
       </c>
@@ -4468,7 +4894,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>450</v>
       </c>
@@ -4488,7 +4914,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>450</v>
       </c>
@@ -4508,7 +4934,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>450</v>
       </c>
@@ -4528,7 +4954,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>450</v>
       </c>
@@ -4548,7 +4974,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>450</v>
       </c>
@@ -4568,7 +4994,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>450</v>
       </c>
@@ -4588,7 +5014,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>450</v>
       </c>
@@ -4602,7 +5028,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>141</v>
       </c>
@@ -4634,7 +5060,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>141</v>
       </c>
@@ -4666,7 +5092,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>141</v>
       </c>
@@ -4698,7 +5124,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>141</v>
       </c>
@@ -4730,7 +5156,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>141</v>
       </c>
@@ -4762,7 +5188,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>141</v>
       </c>
@@ -4794,7 +5220,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>141</v>
       </c>
@@ -4826,7 +5252,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>141</v>
       </c>
@@ -4861,7 +5287,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>141</v>
       </c>
@@ -4893,7 +5319,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>141</v>
       </c>
@@ -4928,7 +5354,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>141</v>
       </c>
@@ -4963,7 +5389,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>141</v>
       </c>
@@ -4998,7 +5424,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>141</v>
       </c>
@@ -5030,7 +5456,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>141</v>
       </c>
@@ -5065,7 +5491,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>141</v>
       </c>
@@ -5100,7 +5526,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>141</v>
       </c>
@@ -5132,7 +5558,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>141</v>
       </c>
@@ -5167,7 +5593,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>141</v>
       </c>
@@ -5202,7 +5628,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>141</v>
       </c>
@@ -5234,7 +5660,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>141</v>
       </c>
@@ -5266,7 +5692,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>141</v>
       </c>
@@ -5298,7 +5724,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>141</v>
       </c>
@@ -5330,7 +5756,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>141</v>
       </c>
@@ -5362,7 +5788,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>141</v>
       </c>
@@ -5394,7 +5820,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>141</v>
       </c>
@@ -5426,7 +5852,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>141</v>
       </c>
@@ -5458,7 +5884,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>141</v>
       </c>
@@ -5490,7 +5916,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>141</v>
       </c>
@@ -5522,7 +5948,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>141</v>
       </c>
@@ -5554,7 +5980,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>141</v>
       </c>
@@ -5586,7 +6012,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>141</v>
       </c>
@@ -5621,7 +6047,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>141</v>
       </c>
@@ -5653,7 +6079,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>141</v>
       </c>
@@ -5685,7 +6111,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>141</v>
       </c>
@@ -5720,7 +6146,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>141</v>
       </c>
@@ -5755,7 +6181,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>141</v>
       </c>
@@ -5787,7 +6213,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>141</v>
       </c>
@@ -5819,7 +6245,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>141</v>
       </c>
@@ -5851,7 +6277,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>141</v>
       </c>
@@ -5883,7 +6309,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="100" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>141</v>
       </c>
@@ -5915,7 +6341,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>141</v>
       </c>
@@ -5947,7 +6373,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="102" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>141</v>
       </c>
@@ -5979,7 +6405,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>141</v>
       </c>
@@ -6011,7 +6437,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="104" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>141</v>
       </c>
@@ -6043,7 +6469,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="105" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>141</v>
       </c>
@@ -6075,7 +6501,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="106" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>141</v>
       </c>
@@ -6107,7 +6533,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="107" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>141</v>
       </c>
@@ -6139,7 +6565,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="108" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>141</v>
       </c>
@@ -6171,7 +6597,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="109" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>141</v>
       </c>
@@ -6203,7 +6629,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="110" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>141</v>
       </c>
@@ -6235,7 +6661,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="111" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>141</v>
       </c>
@@ -6267,7 +6693,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="112" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>141</v>
       </c>
@@ -6299,7 +6725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="113" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>141</v>
       </c>
@@ -6331,7 +6757,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>141</v>
       </c>
@@ -6363,7 +6789,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="115" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>141</v>
       </c>
@@ -6395,7 +6821,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="116" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>141</v>
       </c>
@@ -6427,7 +6853,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>141</v>
       </c>
@@ -6459,7 +6885,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>141</v>
       </c>
@@ -6491,7 +6917,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="119" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>141</v>
       </c>
@@ -6523,7 +6949,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="120" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>141</v>
       </c>
@@ -6555,7 +6981,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="121" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>141</v>
       </c>
@@ -6587,7 +7013,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="122" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>141</v>
       </c>
@@ -6619,7 +7045,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="123" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>141</v>
       </c>
@@ -6645,7 +7071,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="124" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>141</v>
       </c>
@@ -6671,7 +7097,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="125" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>141</v>
       </c>
@@ -6697,7 +7123,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="126" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>141</v>
       </c>
@@ -6723,7 +7149,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="127" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>141</v>
       </c>
@@ -6755,7 +7181,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>141</v>
       </c>
@@ -6781,7 +7207,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>141</v>
       </c>
@@ -6807,7 +7233,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>141</v>
       </c>
@@ -6833,7 +7259,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>141</v>
       </c>
@@ -6868,7 +7294,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>141</v>
       </c>
@@ -6903,7 +7329,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>141</v>
       </c>
@@ -6938,7 +7364,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>141</v>
       </c>
@@ -6973,7 +7399,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>141</v>
       </c>
@@ -7008,7 +7434,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>141</v>
       </c>
@@ -7043,7 +7469,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>141</v>
       </c>
@@ -7078,7 +7504,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>141</v>
       </c>
@@ -7113,7 +7539,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>141</v>
       </c>
@@ -7148,7 +7574,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -7183,7 +7609,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>141</v>
       </c>
@@ -7218,7 +7644,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>141</v>
       </c>
@@ -7253,7 +7679,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>141</v>
       </c>
@@ -7288,7 +7714,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>141</v>
       </c>
@@ -7323,7 +7749,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>141</v>
       </c>
@@ -7358,7 +7784,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>141</v>
       </c>
@@ -7393,7 +7819,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>141</v>
       </c>
@@ -7428,7 +7854,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>141</v>
       </c>
@@ -7463,7 +7889,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>141</v>
       </c>
@@ -7498,7 +7924,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>141</v>
       </c>
@@ -7533,7 +7959,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>141</v>
       </c>
@@ -7568,7 +7994,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>141</v>
       </c>
@@ -7606,7 +8032,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>141</v>
       </c>
@@ -7641,7 +8067,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>141</v>
       </c>
@@ -7676,7 +8102,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>141</v>
       </c>
@@ -7711,7 +8137,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>141</v>
       </c>
@@ -7746,7 +8172,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>141</v>
       </c>
@@ -7781,7 +8207,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>141</v>
       </c>
@@ -7819,7 +8245,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>141</v>
       </c>
@@ -7854,7 +8280,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>141</v>
       </c>
@@ -7889,7 +8315,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>141</v>
       </c>
@@ -7924,7 +8350,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>141</v>
       </c>
@@ -7959,7 +8385,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>141</v>
       </c>
@@ -7994,7 +8420,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>141</v>
       </c>
@@ -8029,7 +8455,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>141</v>
       </c>
@@ -8064,7 +8490,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>141</v>
       </c>
@@ -8099,7 +8525,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>141</v>
       </c>
@@ -8137,7 +8563,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>141</v>
       </c>
@@ -8172,7 +8598,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>141</v>
       </c>
@@ -8207,7 +8633,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>141</v>
       </c>
@@ -8242,7 +8668,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>141</v>
       </c>
@@ -8277,7 +8703,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>141</v>
       </c>
@@ -8312,7 +8738,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>141</v>
       </c>
@@ -8347,7 +8773,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>141</v>
       </c>
@@ -8382,7 +8808,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>141</v>
       </c>
@@ -8417,7 +8843,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>141</v>
       </c>
@@ -8452,7 +8878,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>141</v>
       </c>
@@ -8487,7 +8913,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>141</v>
       </c>
@@ -8522,7 +8948,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>141</v>
       </c>
@@ -8557,7 +8983,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>141</v>
       </c>
@@ -8592,7 +9018,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>141</v>
       </c>
@@ -8627,7 +9053,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="182" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>141</v>
       </c>
@@ -8662,7 +9088,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>141</v>
       </c>
@@ -8697,7 +9123,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>141</v>
       </c>
@@ -8732,7 +9158,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>141</v>
       </c>
@@ -8767,7 +9193,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>141</v>
       </c>
@@ -8802,7 +9228,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>141</v>
       </c>
@@ -8837,7 +9263,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>141</v>
       </c>
@@ -8872,7 +9298,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="189" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>141</v>
       </c>
@@ -8904,7 +9330,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>141</v>
       </c>
@@ -8936,7 +9362,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>141</v>
       </c>
@@ -8968,7 +9394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="192" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>141</v>
       </c>
@@ -9000,7 +9426,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="193" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>141</v>
       </c>
@@ -9032,7 +9458,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="194" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>141</v>
       </c>
@@ -9064,7 +9490,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="195" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>141</v>
       </c>
@@ -9096,7 +9522,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="196" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>141</v>
       </c>
@@ -9128,7 +9554,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>141</v>
       </c>
@@ -9160,7 +9586,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="198" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>141</v>
       </c>
@@ -9192,7 +9618,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="199" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>141</v>
       </c>
@@ -9230,7 +9656,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="200" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>141</v>
       </c>
@@ -9268,7 +9694,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="201" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>141</v>
       </c>
@@ -9306,7 +9732,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="202" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>141</v>
       </c>
@@ -9344,7 +9770,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="203" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>141</v>
       </c>
@@ -9382,7 +9808,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="204" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>141</v>
       </c>
@@ -9420,7 +9846,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="205" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>141</v>
       </c>
@@ -9458,7 +9884,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="206" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>141</v>
       </c>
@@ -9496,7 +9922,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="207" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>141</v>
       </c>
@@ -9534,7 +9960,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="208" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>141</v>
       </c>
@@ -9572,7 +9998,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="209" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>141</v>
       </c>
@@ -9610,7 +10036,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="210" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>141</v>
       </c>
@@ -9648,7 +10074,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="211" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>141</v>
       </c>
@@ -9686,7 +10112,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="212" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>141</v>
       </c>
@@ -9724,7 +10150,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="213" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>141</v>
       </c>
@@ -9762,7 +10188,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="214" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>141</v>
       </c>
@@ -9797,7 +10223,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="215" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>141</v>
       </c>
@@ -9832,7 +10258,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="216" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>141</v>
       </c>
@@ -9867,7 +10293,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="217" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>141</v>
       </c>
@@ -9902,7 +10328,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="218" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>141</v>
       </c>
@@ -9937,7 +10363,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="219" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>141</v>
       </c>
@@ -9972,7 +10398,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="220" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>141</v>
       </c>
@@ -10007,7 +10433,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="221" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>141</v>
       </c>
@@ -10042,7 +10468,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="222" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>141</v>
       </c>
@@ -10080,7 +10506,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="223" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>424</v>
       </c>
@@ -10121,7 +10547,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="224" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>424</v>
       </c>
@@ -10159,7 +10585,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>424</v>
       </c>
@@ -10197,7 +10623,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="226" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>424</v>
       </c>
@@ -10235,7 +10661,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="227" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>424</v>
       </c>
@@ -10273,7 +10699,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="228" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>424</v>
       </c>
@@ -10311,7 +10737,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="229" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>424</v>
       </c>
@@ -10349,7 +10775,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="230" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>424</v>
       </c>
@@ -10387,7 +10813,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="231" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>424</v>
       </c>
@@ -10425,7 +10851,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="232" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>424</v>
       </c>
@@ -10463,7 +10889,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="233" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>424</v>
       </c>
@@ -10501,7 +10927,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="234" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>449</v>
       </c>
@@ -10533,7 +10959,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>463</v>
       </c>
@@ -10571,7 +10997,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="236" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>463</v>
       </c>
@@ -10609,7 +11035,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="237" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>463</v>
       </c>
@@ -10647,7 +11073,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="238" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>477</v>
       </c>
@@ -10679,7 +11105,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="239" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>477</v>
       </c>
@@ -10711,7 +11137,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="240" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>477</v>
       </c>
@@ -10743,7 +11169,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="241" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>477</v>
       </c>
@@ -10775,7 +11201,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="242" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>477</v>
       </c>
@@ -10813,7 +11239,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="243" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>477</v>
       </c>
@@ -10851,7 +11277,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="244" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>477</v>
       </c>
@@ -10889,7 +11315,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="245" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B245" t="s">
         <v>477</v>
       </c>
@@ -10927,7 +11353,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="246" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B246" t="s">
         <v>477</v>
       </c>
@@ -10965,7 +11391,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="247" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B247" t="s">
         <v>477</v>
       </c>
@@ -11003,7 +11429,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B248" t="s">
         <v>477</v>
       </c>
@@ -11041,7 +11467,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="249" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B249" t="s">
         <v>477</v>
       </c>
@@ -11079,7 +11505,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B250" t="s">
         <v>477</v>
       </c>
@@ -11117,7 +11543,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="251" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>477</v>
       </c>
@@ -11155,7 +11581,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="252" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B252" t="s">
         <v>477</v>
       </c>
@@ -11193,7 +11619,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="253" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B253" t="s">
         <v>477</v>
       </c>
@@ -11231,7 +11657,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="254" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>477</v>
       </c>
@@ -11269,7 +11695,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="255" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>477</v>
       </c>
@@ -11307,7 +11733,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="256" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>477</v>
       </c>
@@ -11345,7 +11771,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="257" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>477</v>
       </c>
@@ -11383,7 +11809,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="258" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>477</v>
       </c>
@@ -11421,7 +11847,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="259" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B259" t="s">
         <v>477</v>
       </c>
@@ -11459,7 +11885,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="260" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B260" t="s">
         <v>477</v>
       </c>
@@ -11497,7 +11923,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="261" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B261" t="s">
         <v>477</v>
       </c>
@@ -11535,7 +11961,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="262" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B262" t="s">
         <v>477</v>
       </c>
@@ -11573,7 +11999,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="263" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B263" t="s">
         <v>477</v>
       </c>
@@ -11611,7 +12037,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="264" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>477</v>
       </c>
@@ -11649,7 +12075,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="265" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>477</v>
       </c>
@@ -11687,7 +12113,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="266" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>477</v>
       </c>
@@ -11725,7 +12151,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="267" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>477</v>
       </c>
@@ -11763,7 +12189,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="268" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>477</v>
       </c>
@@ -11801,7 +12227,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="269" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>477</v>
       </c>
@@ -11839,7 +12265,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="270" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>477</v>
       </c>
@@ -11877,7 +12303,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="271" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>477</v>
       </c>
@@ -11915,7 +12341,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="272" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>477</v>
       </c>
@@ -11953,7 +12379,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="273" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>477</v>
       </c>
@@ -11991,7 +12417,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="274" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>477</v>
       </c>
@@ -12026,7 +12452,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="275" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>477</v>
       </c>
@@ -12061,7 +12487,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="276" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>477</v>
       </c>
@@ -12096,7 +12522,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="277" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>477</v>
       </c>
@@ -12131,7 +12557,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="278" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>477</v>
       </c>
@@ -12166,7 +12592,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="279" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B279" t="s">
         <v>477</v>
       </c>
@@ -12201,7 +12627,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="280" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B280" t="s">
         <v>477</v>
       </c>
@@ -12236,7 +12662,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="281" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B281" t="s">
         <v>477</v>
       </c>
@@ -12271,7 +12697,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="282" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B282" t="s">
         <v>477</v>
       </c>
@@ -12306,7 +12732,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="283" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B283" t="s">
         <v>477</v>
       </c>
@@ -12341,7 +12767,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="284" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B284" t="s">
         <v>477</v>
       </c>
@@ -12376,7 +12802,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="285" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B285" t="s">
         <v>477</v>
       </c>
@@ -12411,7 +12837,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="286" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B286" t="s">
         <v>477</v>
       </c>
@@ -12446,7 +12872,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="287" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B287" t="s">
         <v>477</v>
       </c>
@@ -12481,7 +12907,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="288" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B288" t="s">
         <v>477</v>
       </c>
@@ -12516,7 +12942,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="289" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B289" t="s">
         <v>477</v>
       </c>
@@ -12551,7 +12977,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="290" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B290" t="s">
         <v>477</v>
       </c>
@@ -12586,7 +13012,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="291" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B291" t="s">
         <v>477</v>
       </c>
@@ -12621,7 +13047,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="292" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B292" t="s">
         <v>477</v>
       </c>
@@ -12656,7 +13082,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="293" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B293" t="s">
         <v>477</v>
       </c>
@@ -12691,7 +13117,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="294" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B294" t="s">
         <v>477</v>
       </c>
@@ -12726,7 +13152,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="295" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B295" t="s">
         <v>477</v>
       </c>
@@ -12761,7 +13187,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="296" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B296" t="s">
         <v>477</v>
       </c>
@@ -12796,7 +13222,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="297" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B297" t="s">
         <v>477</v>
       </c>
@@ -12831,7 +13257,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="298" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B298" t="s">
         <v>477</v>
       </c>
@@ -12866,7 +13292,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="299" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B299" t="s">
         <v>477</v>
       </c>
@@ -12901,7 +13327,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="300" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B300" t="s">
         <v>477</v>
       </c>
@@ -12936,7 +13362,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="301" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B301" t="s">
         <v>477</v>
       </c>
@@ -12971,7 +13397,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="302" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B302" t="s">
         <v>477</v>
       </c>
@@ -13006,7 +13432,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="303" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B303" t="s">
         <v>477</v>
       </c>
@@ -13041,7 +13467,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="304" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B304" t="s">
         <v>477</v>
       </c>
@@ -13076,7 +13502,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="305" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B305" t="s">
         <v>477</v>
       </c>
@@ -13111,7 +13537,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="306" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B306" t="s">
         <v>477</v>
       </c>
@@ -13146,7 +13572,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="307" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>477</v>
       </c>
@@ -13181,7 +13607,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="308" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>477</v>
       </c>
@@ -13216,7 +13642,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="309" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>477</v>
       </c>
@@ -13251,7 +13677,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="310" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>477</v>
       </c>
@@ -13286,7 +13712,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="311" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>477</v>
       </c>
@@ -13321,7 +13747,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="312" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>477</v>
       </c>
@@ -13353,7 +13779,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="313" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>477</v>
       </c>
@@ -13385,7 +13811,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="314" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>477</v>
       </c>
@@ -13417,7 +13843,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="315" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>477</v>
       </c>
@@ -13449,7 +13875,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="316" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>477</v>
       </c>
@@ -13481,7 +13907,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="317" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>477</v>
       </c>
@@ -13513,7 +13939,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>477</v>
       </c>
@@ -13545,7 +13971,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B319" t="s">
         <v>477</v>
       </c>
@@ -13577,7 +14003,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="320" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B320" t="s">
         <v>477</v>
       </c>
@@ -13609,7 +14035,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="321" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B321" t="s">
         <v>477</v>
       </c>
@@ -13641,7 +14067,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="322" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B322" t="s">
         <v>477</v>
       </c>
@@ -13673,7 +14099,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="323" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B323" t="s">
         <v>477</v>
       </c>
@@ -13705,7 +14131,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="324" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B324" t="s">
         <v>477</v>
       </c>
@@ -13737,7 +14163,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="325" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B325" t="s">
         <v>477</v>
       </c>
@@ -13769,7 +14195,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="326" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B326" t="s">
         <v>477</v>
       </c>
@@ -13801,7 +14227,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="327" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B327" t="s">
         <v>477</v>
       </c>
@@ -13833,7 +14259,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="328" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B328" t="s">
         <v>477</v>
       </c>
@@ -13865,7 +14291,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="329" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B329" t="s">
         <v>477</v>
       </c>
@@ -13897,7 +14323,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="330" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B330" t="s">
         <v>477</v>
       </c>
@@ -13929,7 +14355,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="331" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>477</v>
       </c>
@@ -13961,7 +14387,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="332" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>477</v>
       </c>
@@ -13993,7 +14419,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="333" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>477</v>
       </c>
@@ -14025,7 +14451,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="334" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>477</v>
       </c>
@@ -14057,7 +14483,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="335" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>477</v>
       </c>
@@ -14089,7 +14515,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="336" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>477</v>
       </c>
@@ -14121,7 +14547,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="337" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>477</v>
       </c>
@@ -14153,7 +14579,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="338" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>477</v>
       </c>
@@ -14185,7 +14611,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="339" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B339" t="s">
         <v>477</v>
       </c>
@@ -14217,7 +14643,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="340" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B340" t="s">
         <v>477</v>
       </c>
@@ -14249,7 +14675,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="341" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B341" t="s">
         <v>477</v>
       </c>
@@ -14281,7 +14707,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="342" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B342" t="s">
         <v>477</v>
       </c>
@@ -14313,7 +14739,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="343" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B343" t="s">
         <v>477</v>
       </c>
@@ -14345,7 +14771,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="344" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B344" t="s">
         <v>477</v>
       </c>
@@ -14377,7 +14803,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="345" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>477</v>
       </c>
@@ -14409,7 +14835,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="346" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>477</v>
       </c>
@@ -14441,7 +14867,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="347" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B347" t="s">
         <v>477</v>
       </c>
@@ -14473,7 +14899,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="348" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B348" t="s">
         <v>477</v>
       </c>
@@ -14505,7 +14931,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="349" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B349" t="s">
         <v>477</v>
       </c>
@@ -14537,7 +14963,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="350" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B350" t="s">
         <v>477</v>
       </c>
@@ -14569,7 +14995,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="351" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B351" t="s">
         <v>477</v>
       </c>
@@ -14601,7 +15027,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="352" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B352" t="s">
         <v>477</v>
       </c>
@@ -14633,7 +15059,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="353" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B353" t="s">
         <v>477</v>
       </c>
@@ -14665,7 +15091,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="354" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B354" t="s">
         <v>477</v>
       </c>
@@ -14697,7 +15123,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="355" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B355" t="s">
         <v>477</v>
       </c>
@@ -14729,7 +15155,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="356" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B356" t="s">
         <v>477</v>
       </c>
@@ -14761,7 +15187,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="357" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B357" t="s">
         <v>477</v>
       </c>
@@ -14793,7 +15219,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="358" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B358" t="s">
         <v>477</v>
       </c>
@@ -14825,7 +15251,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="359" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B359" t="s">
         <v>477</v>
       </c>
@@ -14857,7 +15283,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="360" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B360" t="s">
         <v>477</v>
       </c>
@@ -14889,7 +15315,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="361" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B361" t="s">
         <v>477</v>
       </c>
@@ -14921,7 +15347,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="362" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B362" t="s">
         <v>477</v>
       </c>
@@ -14953,7 +15379,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="363" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B363" t="s">
         <v>477</v>
       </c>
@@ -14985,7 +15411,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="364" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B364" t="s">
         <v>477</v>
       </c>
@@ -15017,7 +15443,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="365" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B365" t="s">
         <v>477</v>
       </c>
@@ -15049,7 +15475,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="366" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B366" t="s">
         <v>477</v>
       </c>
@@ -15081,7 +15507,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="367" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B367" t="s">
         <v>477</v>
       </c>
@@ -15113,7 +15539,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="368" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B368" t="s">
         <v>477</v>
       </c>
@@ -15145,7 +15571,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="369" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B369" t="s">
         <v>477</v>
       </c>
@@ -15177,7 +15603,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="370" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B370" t="s">
         <v>477</v>
       </c>
@@ -15209,7 +15635,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="371" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B371" t="s">
         <v>477</v>
       </c>
@@ -15244,7 +15670,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="372" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B372" t="s">
         <v>477</v>
       </c>
@@ -15279,7 +15705,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="373" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B373" t="s">
         <v>477</v>
       </c>
@@ -15314,7 +15740,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="374" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B374" t="s">
         <v>477</v>
       </c>
@@ -15349,7 +15775,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="375" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B375" t="s">
         <v>477</v>
       </c>
@@ -15384,7 +15810,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="376" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B376" t="s">
         <v>477</v>
       </c>
@@ -15419,7 +15845,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="377" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B377" t="s">
         <v>477</v>
       </c>
@@ -15454,7 +15880,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="378" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B378" t="s">
         <v>477</v>
       </c>
@@ -15489,7 +15915,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="379" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B379" t="s">
         <v>477</v>
       </c>
@@ -15524,7 +15950,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="380" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B380" t="s">
         <v>477</v>
       </c>
@@ -15559,7 +15985,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="381" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B381" t="s">
         <v>477</v>
       </c>
@@ -15594,7 +16020,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="382" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B382" t="s">
         <v>477</v>
       </c>
@@ -15629,7 +16055,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="383" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B383" t="s">
         <v>477</v>
       </c>
@@ -15664,7 +16090,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="384" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B384" t="s">
         <v>477</v>
       </c>
@@ -15699,7 +16125,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="385" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B385" t="s">
         <v>477</v>
       </c>
@@ -15731,7 +16157,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="386" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B386" t="s">
         <v>477</v>
       </c>
@@ -15763,7 +16189,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="387" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B387" t="s">
         <v>477</v>
       </c>
@@ -15795,7 +16221,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="388" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B388" t="s">
         <v>477</v>
       </c>
@@ -15827,7 +16253,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="389" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>477</v>
       </c>
@@ -15859,7 +16285,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="390" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>477</v>
       </c>
@@ -15891,7 +16317,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="391" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>477</v>
       </c>
@@ -15923,7 +16349,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="392" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>477</v>
       </c>
@@ -15955,7 +16381,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="393" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>477</v>
       </c>
@@ -15987,7 +16413,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="394" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>477</v>
       </c>
@@ -16019,7 +16445,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="395" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>477</v>
       </c>
@@ -16051,7 +16477,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="396" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>477</v>
       </c>
@@ -16083,7 +16509,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="397" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>477</v>
       </c>
@@ -16115,7 +16541,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="398" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>477</v>
       </c>
@@ -16147,7 +16573,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="399" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>477</v>
       </c>
@@ -16179,7 +16605,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="400" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>477</v>
       </c>
@@ -16211,7 +16637,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="401" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B401" t="s">
         <v>477</v>
       </c>
@@ -16243,7 +16669,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="402" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B402" t="s">
         <v>477</v>
       </c>
@@ -16275,7 +16701,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="403" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B403" t="s">
         <v>477</v>
       </c>
@@ -16307,7 +16733,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="404" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B404" t="s">
         <v>477</v>
       </c>
@@ -16339,7 +16765,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="405" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B405" t="s">
         <v>477</v>
       </c>
@@ -16371,7 +16797,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="406" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B406" t="s">
         <v>477</v>
       </c>
@@ -16403,7 +16829,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="407" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B407" t="s">
         <v>477</v>
       </c>
@@ -16435,7 +16861,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="408" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B408" t="s">
         <v>477</v>
       </c>
@@ -16467,7 +16893,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="409" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B409" t="s">
         <v>477</v>
       </c>
@@ -16499,7 +16925,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="410" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B410" t="s">
         <v>477</v>
       </c>
@@ -16531,7 +16957,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="411" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>477</v>
       </c>
@@ -16563,7 +16989,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="412" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>477</v>
       </c>
@@ -16595,7 +17021,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="413" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>477</v>
       </c>
@@ -16627,7 +17053,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="414" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>477</v>
       </c>
@@ -16659,7 +17085,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="415" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>477</v>
       </c>
@@ -16691,7 +17117,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="416" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>477</v>
       </c>
@@ -16723,7 +17149,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="417" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>477</v>
       </c>
@@ -16755,7 +17181,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="418" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B418" t="s">
         <v>477</v>
       </c>
@@ -16787,7 +17213,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="419" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B419" t="s">
         <v>477</v>
       </c>
@@ -16819,7 +17245,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="420" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B420" t="s">
         <v>477</v>
       </c>
@@ -16851,7 +17277,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="421" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B421" t="s">
         <v>477</v>
       </c>
@@ -16883,7 +17309,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="422" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B422" t="s">
         <v>477</v>
       </c>
@@ -16915,7 +17341,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="423" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B423" t="s">
         <v>477</v>
       </c>
@@ -16947,7 +17373,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="424" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B424" t="s">
         <v>477</v>
       </c>
@@ -16979,7 +17405,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="425" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B425" t="s">
         <v>477</v>
       </c>
@@ -17011,7 +17437,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="426" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B426" t="s">
         <v>477</v>
       </c>
@@ -17043,7 +17469,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="427" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B427" t="s">
         <v>477</v>
       </c>
@@ -17075,7 +17501,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="428" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B428" t="s">
         <v>477</v>
       </c>
@@ -17107,7 +17533,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="429" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B429" t="s">
         <v>477</v>
       </c>
@@ -17139,7 +17565,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="430" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B430" t="s">
         <v>477</v>
       </c>
@@ -17171,7 +17597,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="431" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B431" t="s">
         <v>477</v>
       </c>
@@ -17197,7 +17623,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="432" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B432" t="s">
         <v>477</v>
       </c>
@@ -17223,7 +17649,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="433" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B433" t="s">
         <v>477</v>
       </c>
@@ -17249,7 +17675,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="434" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B434" t="s">
         <v>477</v>
       </c>
@@ -17275,7 +17701,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="435" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B435" t="s">
         <v>477</v>
       </c>
@@ -17301,7 +17727,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="436" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B436" t="s">
         <v>477</v>
       </c>
@@ -17327,7 +17753,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="437" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B437" t="s">
         <v>477</v>
       </c>
@@ -17353,7 +17779,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="438" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B438" t="s">
         <v>477</v>
       </c>
@@ -17379,7 +17805,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="439" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B439" t="s">
         <v>477</v>
       </c>
@@ -17405,7 +17831,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="440" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B440" t="s">
         <v>477</v>
       </c>
@@ -17431,7 +17857,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="441" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B441" t="s">
         <v>477</v>
       </c>
@@ -17457,7 +17883,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="442" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B442" t="s">
         <v>477</v>
       </c>
@@ -17483,7 +17909,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="443" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B443" t="s">
         <v>477</v>
       </c>
@@ -17509,7 +17935,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="444" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B444" t="s">
         <v>477</v>
       </c>
@@ -17535,7 +17961,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="445" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B445" t="s">
         <v>477</v>
       </c>
@@ -17561,7 +17987,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="446" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B446" t="s">
         <v>477</v>
       </c>
@@ -17587,7 +18013,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="447" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B447" t="s">
         <v>477</v>
       </c>
@@ -17613,7 +18039,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="448" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B448" t="s">
         <v>477</v>
       </c>
@@ -17645,7 +18071,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="449" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B449" t="s">
         <v>477</v>
       </c>
@@ -17677,7 +18103,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="450" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B450" t="s">
         <v>477</v>
       </c>
@@ -17709,7 +18135,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="451" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B451" t="s">
         <v>477</v>
       </c>
@@ -17741,7 +18167,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="452" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B452" t="s">
         <v>477</v>
       </c>
@@ -17773,7 +18199,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="453" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B453" t="s">
         <v>477</v>
       </c>
@@ -17805,7 +18231,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="454" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B454" t="s">
         <v>477</v>
       </c>
@@ -17837,7 +18263,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="455" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B455" t="s">
         <v>477</v>
       </c>
@@ -17869,7 +18295,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="456" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B456" t="s">
         <v>477</v>
       </c>
@@ -17901,7 +18327,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="457" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B457" t="s">
         <v>477</v>
       </c>
@@ -17927,7 +18353,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="458" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B458" t="s">
         <v>477</v>
       </c>
@@ -17953,7 +18379,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="459" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B459" t="s">
         <v>477</v>
       </c>
@@ -17979,7 +18405,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="460" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B460" t="s">
         <v>477</v>
       </c>
@@ -18005,7 +18431,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="461" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B461" t="s">
         <v>477</v>
       </c>
@@ -18031,7 +18457,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="462" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B462" t="s">
         <v>477</v>
       </c>
@@ -18057,7 +18483,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="463" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B463" t="s">
         <v>477</v>
       </c>
@@ -18083,7 +18509,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="464" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B464" t="s">
         <v>477</v>
       </c>
@@ -18109,7 +18535,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="465" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B465" t="s">
         <v>477</v>
       </c>
@@ -18135,7 +18561,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="466" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B466" t="s">
         <v>477</v>
       </c>
@@ -18161,7 +18587,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="467" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B467" t="s">
         <v>477</v>
       </c>
@@ -18199,7 +18625,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="468" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B468" t="s">
         <v>477</v>
       </c>
@@ -18234,7 +18660,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="469" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B469" t="s">
         <v>477</v>
       </c>
@@ -18269,7 +18695,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="470" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B470" t="s">
         <v>477</v>
       </c>
@@ -18304,7 +18730,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="471" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B471" t="s">
         <v>477</v>
       </c>
@@ -18339,7 +18765,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="472" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B472" t="s">
         <v>858</v>
       </c>
@@ -18374,7 +18800,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="473" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B473" t="s">
         <v>858</v>
       </c>
@@ -18409,7 +18835,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="474" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B474" t="s">
         <v>858</v>
       </c>
@@ -18447,7 +18873,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="475" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B475" t="s">
         <v>858</v>
       </c>
@@ -18482,7 +18908,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="476" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B476" t="s">
         <v>858</v>
       </c>
@@ -18499,7 +18925,7 @@
         <v>877</v>
       </c>
       <c r="H476" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I476" t="s">
         <v>839</v>
@@ -18520,7 +18946,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="477" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B477" t="s">
         <v>858</v>
       </c>
@@ -18561,7 +18987,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="478" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B478" t="s">
         <v>858</v>
       </c>
@@ -18581,7 +19007,7 @@
         <v>888</v>
       </c>
       <c r="H478" t="s">
-        <v>891</v>
+        <v>1002</v>
       </c>
       <c r="I478" t="s">
         <v>839</v>
@@ -18602,7 +19028,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="479" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B479" t="s">
         <v>858</v>
       </c>
@@ -18616,19 +19042,19 @@
         <v>140</v>
       </c>
       <c r="F479" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G479" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H479" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I479" t="s">
         <v>839</v>
       </c>
       <c r="J479" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L479" t="s">
         <v>768</v>
@@ -18640,33 +19066,33 @@
         <v>467</v>
       </c>
       <c r="O479" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="480" spans="2:15" x14ac:dyDescent="0.35">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="480" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B480" t="s">
         <v>858</v>
       </c>
       <c r="C480" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E480" t="s">
         <v>140</v>
       </c>
       <c r="F480" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G480" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H480" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I480" t="s">
         <v>839</v>
       </c>
       <c r="J480" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L480" t="s">
         <v>865</v>
@@ -18678,30 +19104,30 @@
         <v>467</v>
       </c>
     </row>
-    <row r="481" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B481" t="s">
         <v>858</v>
       </c>
       <c r="C481" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E481" t="s">
         <v>140</v>
       </c>
       <c r="F481" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G481" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H481" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I481" t="s">
         <v>839</v>
       </c>
       <c r="J481" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="L481" t="s">
         <v>865</v>
@@ -18713,33 +19139,33 @@
         <v>467</v>
       </c>
       <c r="O481" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="482" spans="2:15" x14ac:dyDescent="0.35">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="482" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B482" t="s">
         <v>858</v>
       </c>
       <c r="C482" t="s">
+        <v>901</v>
+      </c>
+      <c r="E482" t="s">
+        <v>140</v>
+      </c>
+      <c r="F482" t="s">
         <v>902</v>
       </c>
-      <c r="E482" t="s">
-        <v>140</v>
-      </c>
-      <c r="F482" t="s">
-        <v>903</v>
-      </c>
       <c r="G482" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H482" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I482" t="s">
         <v>839</v>
       </c>
       <c r="J482" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L482" t="s">
         <v>865</v>
@@ -18751,36 +19177,36 @@
         <v>467</v>
       </c>
       <c r="O482" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="483" spans="2:15" x14ac:dyDescent="0.35">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="483" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B483" t="s">
         <v>858</v>
       </c>
       <c r="C483" t="s">
+        <v>906</v>
+      </c>
+      <c r="E483" t="s">
+        <v>140</v>
+      </c>
+      <c r="F483" t="s">
         <v>907</v>
       </c>
-      <c r="E483" t="s">
-        <v>140</v>
-      </c>
-      <c r="F483" t="s">
+      <c r="G483" t="s">
         <v>908</v>
       </c>
-      <c r="G483" t="s">
-        <v>909</v>
-      </c>
       <c r="H483" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I483" t="s">
         <v>839</v>
       </c>
       <c r="J483" t="s">
+        <v>910</v>
+      </c>
+      <c r="L483" t="s">
         <v>911</v>
-      </c>
-      <c r="L483" t="s">
-        <v>912</v>
       </c>
       <c r="M483" t="s">
         <v>876</v>
@@ -18789,36 +19215,36 @@
         <v>467</v>
       </c>
       <c r="O483" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="484" spans="2:15" x14ac:dyDescent="0.35">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="484" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B484" t="s">
         <v>858</v>
       </c>
       <c r="C484" t="s">
+        <v>912</v>
+      </c>
+      <c r="D484" t="s">
+        <v>929</v>
+      </c>
+      <c r="E484" t="s">
+        <v>140</v>
+      </c>
+      <c r="F484" t="s">
         <v>913</v>
       </c>
-      <c r="D484" t="s">
-        <v>930</v>
-      </c>
-      <c r="E484" t="s">
-        <v>140</v>
-      </c>
-      <c r="F484" t="s">
-        <v>914</v>
-      </c>
       <c r="G484" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H484" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I484" t="s">
         <v>839</v>
       </c>
       <c r="J484" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L484" t="s">
         <v>768</v>
@@ -18830,36 +19256,36 @@
         <v>467</v>
       </c>
       <c r="O484" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="485" spans="2:15" x14ac:dyDescent="0.35">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="485" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B485" t="s">
         <v>858</v>
       </c>
       <c r="C485" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D485" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E485" t="s">
         <v>140</v>
       </c>
       <c r="F485" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G485" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H485" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I485" t="s">
         <v>839</v>
       </c>
       <c r="J485" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="L485" t="s">
         <v>768</v>
@@ -18871,36 +19297,36 @@
         <v>467</v>
       </c>
       <c r="O485" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="486" spans="2:15" x14ac:dyDescent="0.35">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="486" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B486" t="s">
         <v>858</v>
       </c>
       <c r="C486" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D486" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E486" t="s">
         <v>140</v>
       </c>
       <c r="F486" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G486" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H486" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I486" t="s">
         <v>839</v>
       </c>
       <c r="J486" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L486" t="s">
         <v>768</v>
@@ -18912,36 +19338,36 @@
         <v>467</v>
       </c>
       <c r="O486" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="487" spans="2:15" x14ac:dyDescent="0.35">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="487" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B487" t="s">
         <v>858</v>
       </c>
       <c r="C487" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D487" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E487" t="s">
         <v>140</v>
       </c>
       <c r="F487" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G487" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H487" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I487" t="s">
         <v>839</v>
       </c>
       <c r="J487" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L487" t="s">
         <v>768</v>
@@ -18953,36 +19379,36 @@
         <v>467</v>
       </c>
       <c r="O487" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="488" spans="2:15" x14ac:dyDescent="0.35">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="488" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B488" t="s">
         <v>858</v>
       </c>
       <c r="C488" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D488" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E488" t="s">
         <v>140</v>
       </c>
       <c r="F488" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G488" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H488" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I488" t="s">
         <v>839</v>
       </c>
       <c r="J488" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L488" t="s">
         <v>768</v>
@@ -18994,33 +19420,33 @@
         <v>467</v>
       </c>
       <c r="O488" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="489" spans="2:15" x14ac:dyDescent="0.35">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="489" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B489" t="s">
         <v>858</v>
       </c>
       <c r="C489" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E489" t="s">
         <v>140</v>
       </c>
       <c r="F489" t="s">
+        <v>931</v>
+      </c>
+      <c r="G489" t="s">
+        <v>931</v>
+      </c>
+      <c r="H489" t="s">
         <v>932</v>
       </c>
-      <c r="G489" t="s">
-        <v>932</v>
-      </c>
-      <c r="H489" t="s">
+      <c r="I489" t="s">
+        <v>300</v>
+      </c>
+      <c r="J489" t="s">
         <v>933</v>
-      </c>
-      <c r="I489" t="s">
-        <v>300</v>
-      </c>
-      <c r="J489" t="s">
-        <v>934</v>
       </c>
       <c r="L489" t="s">
         <v>865</v>
@@ -19032,36 +19458,36 @@
         <v>467</v>
       </c>
       <c r="O489" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="490" spans="2:15" x14ac:dyDescent="0.35">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="490" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B490" t="s">
         <v>858</v>
       </c>
       <c r="C490" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D490" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E490" t="s">
         <v>140</v>
       </c>
       <c r="F490" t="s">
+        <v>935</v>
+      </c>
+      <c r="G490" t="s">
+        <v>935</v>
+      </c>
+      <c r="H490" t="s">
         <v>936</v>
       </c>
-      <c r="G490" t="s">
-        <v>936</v>
-      </c>
-      <c r="H490" t="s">
+      <c r="I490" t="s">
+        <v>300</v>
+      </c>
+      <c r="J490" t="s">
         <v>937</v>
-      </c>
-      <c r="I490" t="s">
-        <v>300</v>
-      </c>
-      <c r="J490" t="s">
-        <v>938</v>
       </c>
       <c r="L490" t="s">
         <v>865</v>
@@ -19073,33 +19499,33 @@
         <v>467</v>
       </c>
       <c r="O490" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="491" spans="2:15" x14ac:dyDescent="0.35">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="491" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B491" t="s">
         <v>858</v>
       </c>
       <c r="C491" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D491" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E491" t="s">
         <v>140</v>
       </c>
       <c r="F491" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G491" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I491" t="s">
         <v>843</v>
       </c>
       <c r="J491" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L491" t="s">
         <v>865</v>
@@ -19111,33 +19537,33 @@
         <v>467</v>
       </c>
       <c r="O491" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="492" spans="2:15" x14ac:dyDescent="0.35">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="492" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B492" t="s">
         <v>858</v>
       </c>
       <c r="C492" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E492" t="s">
         <v>140</v>
       </c>
       <c r="F492" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G492" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H492" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="I492" t="s">
         <v>146</v>
       </c>
       <c r="J492" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="L492" t="s">
         <v>865</v>
@@ -19149,10 +19575,10 @@
         <v>467</v>
       </c>
       <c r="O492" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="493" spans="2:15" x14ac:dyDescent="0.35">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="493" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B493" t="s">
         <v>858</v>
       </c>
@@ -19163,19 +19589,19 @@
         <v>140</v>
       </c>
       <c r="F493" t="s">
+        <v>948</v>
+      </c>
+      <c r="G493" t="s">
+        <v>948</v>
+      </c>
+      <c r="H493" t="s">
         <v>949</v>
-      </c>
-      <c r="G493" t="s">
-        <v>949</v>
-      </c>
-      <c r="H493" t="s">
-        <v>950</v>
       </c>
       <c r="I493" t="s">
         <v>146</v>
       </c>
       <c r="J493" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="L493" t="s">
         <v>873</v>
@@ -19187,30 +19613,30 @@
         <v>467</v>
       </c>
       <c r="O493" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="494" spans="2:15" x14ac:dyDescent="0.35">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="494" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B494" t="s">
         <v>858</v>
       </c>
       <c r="C494" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E494" t="s">
         <v>140</v>
       </c>
       <c r="F494" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G494" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I494" t="s">
         <v>145</v>
       </c>
       <c r="J494" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="L494" t="s">
         <v>865</v>
@@ -19222,10 +19648,10 @@
         <v>467</v>
       </c>
       <c r="O494" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="495" spans="2:15" x14ac:dyDescent="0.35">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="495" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B495" t="s">
         <v>858</v>
       </c>
@@ -19236,19 +19662,19 @@
         <v>140</v>
       </c>
       <c r="F495" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G495" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H495" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="I495" t="s">
         <v>145</v>
       </c>
       <c r="J495" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L495" t="s">
         <v>873</v>
@@ -19260,10 +19686,1656 @@
         <v>467</v>
       </c>
       <c r="O495" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="496" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B496" t="s">
+        <v>858</v>
+      </c>
+      <c r="C496" t="s">
+        <v>943</v>
+      </c>
+      <c r="D496" t="s">
+        <v>942</v>
+      </c>
+      <c r="E496" t="s">
+        <v>140</v>
+      </c>
+      <c r="F496" t="s">
         <v>959</v>
       </c>
+      <c r="G496" t="s">
+        <v>959</v>
+      </c>
+      <c r="I496" t="s">
+        <v>487</v>
+      </c>
+      <c r="J496" t="s">
+        <v>961</v>
+      </c>
+      <c r="L496" t="s">
+        <v>865</v>
+      </c>
+      <c r="M496" t="s">
+        <v>457</v>
+      </c>
+      <c r="N496" t="s">
+        <v>467</v>
+      </c>
+      <c r="O496" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="497" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B497" t="s">
+        <v>858</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D497" t="s">
+        <v>962</v>
+      </c>
+      <c r="E497" t="s">
+        <v>140</v>
+      </c>
+      <c r="F497" t="s">
+        <v>964</v>
+      </c>
+      <c r="H497" t="s">
+        <v>461</v>
+      </c>
+      <c r="I497" t="s">
+        <v>839</v>
+      </c>
+      <c r="J497" t="s">
+        <v>972</v>
+      </c>
+      <c r="L497" t="s">
+        <v>768</v>
+      </c>
+      <c r="M497" t="s">
+        <v>402</v>
+      </c>
+      <c r="N497" t="s">
+        <v>971</v>
+      </c>
+      <c r="O497" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="498" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B498" t="s">
+        <v>858</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D498" t="s">
+        <v>962</v>
+      </c>
+      <c r="E498" t="s">
+        <v>140</v>
+      </c>
+      <c r="F498" t="s">
+        <v>965</v>
+      </c>
+      <c r="H498" t="s">
+        <v>461</v>
+      </c>
+      <c r="I498" t="s">
+        <v>839</v>
+      </c>
+      <c r="J498" t="s">
+        <v>973</v>
+      </c>
+      <c r="L498" t="s">
+        <v>768</v>
+      </c>
+      <c r="M498" t="s">
+        <v>402</v>
+      </c>
+      <c r="N498" t="s">
+        <v>971</v>
+      </c>
+      <c r="O498" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="499" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B499" t="s">
+        <v>858</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D499" t="s">
+        <v>963</v>
+      </c>
+      <c r="E499" t="s">
+        <v>140</v>
+      </c>
+      <c r="F499" t="s">
+        <v>966</v>
+      </c>
+      <c r="H499" t="s">
+        <v>461</v>
+      </c>
+      <c r="I499" t="s">
+        <v>839</v>
+      </c>
+      <c r="J499" t="s">
+        <v>974</v>
+      </c>
+      <c r="L499" t="s">
+        <v>768</v>
+      </c>
+      <c r="M499" t="s">
+        <v>402</v>
+      </c>
+      <c r="N499" t="s">
+        <v>971</v>
+      </c>
+      <c r="O499" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="500" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B500" t="s">
+        <v>858</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D500" t="s">
+        <v>980</v>
+      </c>
+      <c r="E500" t="s">
+        <v>140</v>
+      </c>
+      <c r="F500" t="s">
+        <v>967</v>
+      </c>
+      <c r="H500" t="s">
+        <v>461</v>
+      </c>
+      <c r="I500" t="s">
+        <v>839</v>
+      </c>
+      <c r="J500" t="s">
+        <v>975</v>
+      </c>
+      <c r="L500" t="s">
+        <v>768</v>
+      </c>
+      <c r="M500" t="s">
+        <v>402</v>
+      </c>
+      <c r="N500" t="s">
+        <v>971</v>
+      </c>
+      <c r="O500" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="501" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B501" t="s">
+        <v>858</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D501" t="s">
+        <v>981</v>
+      </c>
+      <c r="E501" t="s">
+        <v>140</v>
+      </c>
+      <c r="F501" t="s">
+        <v>968</v>
+      </c>
+      <c r="H501" t="s">
+        <v>461</v>
+      </c>
+      <c r="I501" t="s">
+        <v>839</v>
+      </c>
+      <c r="J501" t="s">
+        <v>976</v>
+      </c>
+      <c r="L501" t="s">
+        <v>768</v>
+      </c>
+      <c r="M501" t="s">
+        <v>402</v>
+      </c>
+      <c r="N501" t="s">
+        <v>971</v>
+      </c>
+      <c r="O501" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="502" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B502" t="s">
+        <v>858</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D502" t="s">
+        <v>981</v>
+      </c>
+      <c r="E502" t="s">
+        <v>140</v>
+      </c>
+      <c r="F502" t="s">
+        <v>969</v>
+      </c>
+      <c r="H502" t="s">
+        <v>461</v>
+      </c>
+      <c r="I502" t="s">
+        <v>839</v>
+      </c>
+      <c r="J502" t="s">
+        <v>977</v>
+      </c>
+      <c r="L502" t="s">
+        <v>768</v>
+      </c>
+      <c r="M502" t="s">
+        <v>402</v>
+      </c>
+      <c r="N502" t="s">
+        <v>971</v>
+      </c>
+      <c r="O502" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="503" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B503" t="s">
+        <v>858</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D503" t="s">
+        <v>962</v>
+      </c>
+      <c r="E503" t="s">
+        <v>140</v>
+      </c>
+      <c r="F503" t="s">
+        <v>982</v>
+      </c>
+      <c r="G503" t="s">
+        <v>982</v>
+      </c>
+      <c r="H503" t="s">
+        <v>978</v>
+      </c>
+      <c r="I503" t="s">
+        <v>839</v>
+      </c>
+      <c r="J503" t="s">
+        <v>979</v>
+      </c>
+      <c r="L503" t="s">
+        <v>768</v>
+      </c>
+      <c r="M503" t="s">
+        <v>403</v>
+      </c>
+      <c r="N503" t="s">
+        <v>978</v>
+      </c>
+      <c r="O503" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="504" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B504" t="s">
+        <v>858</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D504" t="s">
+        <v>980</v>
+      </c>
+      <c r="E504" t="s">
+        <v>140</v>
+      </c>
+      <c r="F504" t="s">
+        <v>993</v>
+      </c>
+      <c r="H504" t="s">
+        <v>978</v>
+      </c>
+      <c r="I504" t="s">
+        <v>839</v>
+      </c>
+      <c r="J504" t="s">
+        <v>983</v>
+      </c>
+      <c r="L504" t="s">
+        <v>768</v>
+      </c>
+      <c r="M504" t="s">
+        <v>403</v>
+      </c>
+      <c r="N504" t="s">
+        <v>978</v>
+      </c>
+      <c r="O504" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="505" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B505" t="s">
+        <v>858</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D505" t="s">
+        <v>463</v>
+      </c>
+      <c r="E505" t="s">
+        <v>140</v>
+      </c>
+      <c r="F505" t="s">
+        <v>994</v>
+      </c>
+      <c r="H505" t="s">
+        <v>978</v>
+      </c>
+      <c r="I505" t="s">
+        <v>839</v>
+      </c>
+      <c r="J505" t="s">
+        <v>984</v>
+      </c>
+      <c r="L505" t="s">
+        <v>768</v>
+      </c>
+      <c r="M505" t="s">
+        <v>403</v>
+      </c>
+      <c r="N505" t="s">
+        <v>978</v>
+      </c>
+      <c r="O505" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="506" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B506" t="s">
+        <v>858</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D506" t="s">
+        <v>981</v>
+      </c>
+      <c r="E506" t="s">
+        <v>140</v>
+      </c>
+      <c r="F506" t="s">
+        <v>995</v>
+      </c>
+      <c r="H506" t="s">
+        <v>978</v>
+      </c>
+      <c r="I506" t="s">
+        <v>839</v>
+      </c>
+      <c r="J506" t="s">
+        <v>985</v>
+      </c>
+      <c r="L506" t="s">
+        <v>768</v>
+      </c>
+      <c r="M506" t="s">
+        <v>403</v>
+      </c>
+      <c r="N506" t="s">
+        <v>978</v>
+      </c>
+      <c r="O506" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="507" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B507" t="s">
+        <v>858</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D507" t="s">
+        <v>463</v>
+      </c>
+      <c r="E507" t="s">
+        <v>140</v>
+      </c>
+      <c r="F507" t="s">
+        <v>996</v>
+      </c>
+      <c r="H507" t="s">
+        <v>978</v>
+      </c>
+      <c r="I507" t="s">
+        <v>839</v>
+      </c>
+      <c r="J507" t="s">
+        <v>986</v>
+      </c>
+      <c r="L507" t="s">
+        <v>768</v>
+      </c>
+      <c r="M507" t="s">
+        <v>403</v>
+      </c>
+      <c r="N507" t="s">
+        <v>978</v>
+      </c>
+      <c r="O507" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="508" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B508" t="s">
+        <v>858</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D508" t="s">
+        <v>963</v>
+      </c>
+      <c r="E508" t="s">
+        <v>140</v>
+      </c>
+      <c r="F508" t="s">
+        <v>997</v>
+      </c>
+      <c r="H508" t="s">
+        <v>978</v>
+      </c>
+      <c r="I508" t="s">
+        <v>839</v>
+      </c>
+      <c r="J508" t="s">
+        <v>987</v>
+      </c>
+      <c r="L508" t="s">
+        <v>768</v>
+      </c>
+      <c r="M508" t="s">
+        <v>403</v>
+      </c>
+      <c r="N508" t="s">
+        <v>978</v>
+      </c>
+      <c r="O508" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="509" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B509" t="s">
+        <v>858</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D509" t="s">
+        <v>962</v>
+      </c>
+      <c r="E509" t="s">
+        <v>140</v>
+      </c>
+      <c r="F509" t="s">
+        <v>998</v>
+      </c>
+      <c r="H509" t="s">
+        <v>978</v>
+      </c>
+      <c r="I509" t="s">
+        <v>839</v>
+      </c>
+      <c r="J509" t="s">
+        <v>988</v>
+      </c>
+      <c r="L509" t="s">
+        <v>768</v>
+      </c>
+      <c r="M509" t="s">
+        <v>403</v>
+      </c>
+      <c r="N509" t="s">
+        <v>978</v>
+      </c>
+      <c r="O509" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="510" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B510" t="s">
+        <v>858</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D510" t="s">
+        <v>962</v>
+      </c>
+      <c r="E510" t="s">
+        <v>140</v>
+      </c>
+      <c r="F510" t="s">
+        <v>999</v>
+      </c>
+      <c r="H510" t="s">
+        <v>978</v>
+      </c>
+      <c r="I510" t="s">
+        <v>464</v>
+      </c>
+      <c r="J510" t="s">
+        <v>989</v>
+      </c>
+      <c r="L510" t="s">
+        <v>768</v>
+      </c>
+      <c r="M510" t="s">
+        <v>403</v>
+      </c>
+      <c r="N510" t="s">
+        <v>978</v>
+      </c>
+      <c r="O510" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="511" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B511" t="s">
+        <v>858</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D511" t="s">
+        <v>962</v>
+      </c>
+      <c r="E511" t="s">
+        <v>140</v>
+      </c>
+      <c r="F511" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H511" t="s">
+        <v>978</v>
+      </c>
+      <c r="I511" t="s">
+        <v>464</v>
+      </c>
+      <c r="J511" t="s">
+        <v>990</v>
+      </c>
+      <c r="L511" t="s">
+        <v>768</v>
+      </c>
+      <c r="M511" t="s">
+        <v>403</v>
+      </c>
+      <c r="N511" t="s">
+        <v>978</v>
+      </c>
+      <c r="O511" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="512" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B512" t="s">
+        <v>463</v>
+      </c>
+      <c r="C512" t="s">
+        <v>451</v>
+      </c>
+      <c r="E512" t="s">
+        <v>140</v>
+      </c>
+      <c r="F512" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G512" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I512" t="s">
+        <v>839</v>
+      </c>
+      <c r="J512" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L512" t="s">
+        <v>768</v>
+      </c>
+      <c r="M512" t="s">
+        <v>403</v>
+      </c>
+      <c r="N512" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="513" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B513" t="s">
+        <v>463</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E513" t="s">
+        <v>140</v>
+      </c>
+      <c r="F513" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G513" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I513" t="s">
+        <v>839</v>
+      </c>
+      <c r="J513" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L513" t="s">
+        <v>768</v>
+      </c>
+      <c r="M513" t="s">
+        <v>403</v>
+      </c>
+      <c r="N513" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="514" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B514" t="s">
+        <v>463</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E514" t="s">
+        <v>140</v>
+      </c>
+      <c r="F514" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G514" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I514" t="s">
+        <v>839</v>
+      </c>
+      <c r="J514" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L514" t="s">
+        <v>768</v>
+      </c>
+      <c r="M514" t="s">
+        <v>403</v>
+      </c>
+      <c r="N514" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="515" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B515" t="s">
+        <v>463</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E515" t="s">
+        <v>140</v>
+      </c>
+      <c r="F515" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G515" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I515" t="s">
+        <v>839</v>
+      </c>
+      <c r="J515" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L515" t="s">
+        <v>768</v>
+      </c>
+      <c r="M515" t="s">
+        <v>403</v>
+      </c>
+      <c r="N515" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="516" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B516" t="s">
+        <v>463</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E516" t="s">
+        <v>140</v>
+      </c>
+      <c r="F516" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G516" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I516" t="s">
+        <v>839</v>
+      </c>
+      <c r="J516" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L516" t="s">
+        <v>768</v>
+      </c>
+      <c r="M516" t="s">
+        <v>403</v>
+      </c>
+      <c r="N516" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="517" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B517" t="s">
+        <v>463</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E517" t="s">
+        <v>140</v>
+      </c>
+      <c r="F517" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G517" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I517" t="s">
+        <v>839</v>
+      </c>
+      <c r="J517" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L517" t="s">
+        <v>768</v>
+      </c>
+      <c r="M517" t="s">
+        <v>403</v>
+      </c>
+      <c r="N517" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="518" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B518" t="s">
+        <v>463</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E518" t="s">
+        <v>140</v>
+      </c>
+      <c r="F518" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G518" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I518" t="s">
+        <v>839</v>
+      </c>
+      <c r="J518" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L518" t="s">
+        <v>768</v>
+      </c>
+      <c r="M518" t="s">
+        <v>403</v>
+      </c>
+      <c r="N518" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="519" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B519" t="s">
+        <v>463</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E519" t="s">
+        <v>140</v>
+      </c>
+      <c r="F519" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G519" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I519" t="s">
+        <v>839</v>
+      </c>
+      <c r="J519" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L519" t="s">
+        <v>768</v>
+      </c>
+      <c r="M519" t="s">
+        <v>403</v>
+      </c>
+      <c r="N519" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="520" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B520" t="s">
+        <v>463</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E520" t="s">
+        <v>140</v>
+      </c>
+      <c r="F520" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G520" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I520" t="s">
+        <v>839</v>
+      </c>
+      <c r="J520" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L520" t="s">
+        <v>768</v>
+      </c>
+      <c r="M520" t="s">
+        <v>403</v>
+      </c>
+      <c r="N520" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="521" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B521" t="s">
+        <v>463</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E521" t="s">
+        <v>140</v>
+      </c>
+      <c r="F521" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G521" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I521" t="s">
+        <v>839</v>
+      </c>
+      <c r="J521" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L521" t="s">
+        <v>768</v>
+      </c>
+      <c r="M521" t="s">
+        <v>403</v>
+      </c>
+      <c r="N521" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="522" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B522" t="s">
+        <v>463</v>
+      </c>
+      <c r="C522" t="s">
+        <v>486</v>
+      </c>
+      <c r="E522" t="s">
+        <v>140</v>
+      </c>
+      <c r="F522" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G522" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I522" t="s">
+        <v>839</v>
+      </c>
+      <c r="J522" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L522" t="s">
+        <v>768</v>
+      </c>
+      <c r="M522" t="s">
+        <v>403</v>
+      </c>
+      <c r="N522" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="523" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B523" t="s">
+        <v>463</v>
+      </c>
+      <c r="C523" t="s">
+        <v>451</v>
+      </c>
+      <c r="E523" t="s">
+        <v>140</v>
+      </c>
+      <c r="F523" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I523" t="s">
+        <v>839</v>
+      </c>
+      <c r="J523" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L523" t="s">
+        <v>768</v>
+      </c>
+      <c r="M523" t="s">
+        <v>403</v>
+      </c>
+      <c r="N523" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="524" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B524" t="s">
+        <v>463</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E524" t="s">
+        <v>140</v>
+      </c>
+      <c r="F524" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I524" t="s">
+        <v>839</v>
+      </c>
+      <c r="J524" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L524" t="s">
+        <v>768</v>
+      </c>
+      <c r="M524" t="s">
+        <v>403</v>
+      </c>
+      <c r="N524" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="525" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B525" t="s">
+        <v>463</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E525" t="s">
+        <v>140</v>
+      </c>
+      <c r="F525" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I525" t="s">
+        <v>839</v>
+      </c>
+      <c r="J525" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L525" t="s">
+        <v>768</v>
+      </c>
+      <c r="M525" t="s">
+        <v>403</v>
+      </c>
+      <c r="N525" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="526" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B526" t="s">
+        <v>463</v>
+      </c>
+      <c r="C526" t="s">
+        <v>451</v>
+      </c>
+      <c r="E526" t="s">
+        <v>140</v>
+      </c>
+      <c r="F526" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I526" t="s">
+        <v>839</v>
+      </c>
+      <c r="J526" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L526" t="s">
+        <v>768</v>
+      </c>
+      <c r="M526" t="s">
+        <v>403</v>
+      </c>
+      <c r="N526" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="527" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B527" t="s">
+        <v>963</v>
+      </c>
+      <c r="C527" t="s">
+        <v>962</v>
+      </c>
+      <c r="E527" t="s">
+        <v>140</v>
+      </c>
+      <c r="F527" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G527" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H527" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I527" t="s">
+        <v>839</v>
+      </c>
+      <c r="J527" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L527" t="s">
+        <v>768</v>
+      </c>
+      <c r="M527" t="s">
+        <v>403</v>
+      </c>
+      <c r="N527" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="528" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B528" t="s">
+        <v>963</v>
+      </c>
+      <c r="C528" t="s">
+        <v>962</v>
+      </c>
+      <c r="E528" t="s">
+        <v>140</v>
+      </c>
+      <c r="F528" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G528" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H528" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I528" t="s">
+        <v>839</v>
+      </c>
+      <c r="J528" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L528" t="s">
+        <v>768</v>
+      </c>
+      <c r="M528" t="s">
+        <v>403</v>
+      </c>
+      <c r="N528" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="529" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B529" t="s">
+        <v>963</v>
+      </c>
+      <c r="C529" t="s">
+        <v>962</v>
+      </c>
+      <c r="E529" t="s">
+        <v>140</v>
+      </c>
+      <c r="F529" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G529" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H529" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I529" t="s">
+        <v>839</v>
+      </c>
+      <c r="J529" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L529" t="s">
+        <v>768</v>
+      </c>
+      <c r="M529" t="s">
+        <v>403</v>
+      </c>
+      <c r="N529" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="530" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B530" t="s">
+        <v>963</v>
+      </c>
+      <c r="C530" t="s">
+        <v>962</v>
+      </c>
+      <c r="E530" t="s">
+        <v>140</v>
+      </c>
+      <c r="F530" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G530" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H530" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I530" t="s">
+        <v>839</v>
+      </c>
+      <c r="J530" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L530" t="s">
+        <v>768</v>
+      </c>
+      <c r="M530" t="s">
+        <v>403</v>
+      </c>
+      <c r="N530" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="531" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B531" t="s">
+        <v>963</v>
+      </c>
+      <c r="C531" t="s">
+        <v>962</v>
+      </c>
+      <c r="E531" t="s">
+        <v>140</v>
+      </c>
+      <c r="F531" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G531" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H531" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I531" t="s">
+        <v>839</v>
+      </c>
+      <c r="J531" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L531" t="s">
+        <v>768</v>
+      </c>
+      <c r="M531" t="s">
+        <v>403</v>
+      </c>
+      <c r="N531" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="532" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B532" t="s">
+        <v>963</v>
+      </c>
+      <c r="C532" t="s">
+        <v>962</v>
+      </c>
+      <c r="E532" t="s">
+        <v>140</v>
+      </c>
+      <c r="F532" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G532" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H532" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I532" t="s">
+        <v>146</v>
+      </c>
+      <c r="J532" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L532" t="s">
+        <v>768</v>
+      </c>
+      <c r="M532" t="s">
+        <v>403</v>
+      </c>
+      <c r="N532" t="s">
+        <v>467</v>
+      </c>
+      <c r="O532" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="533" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B533" t="s">
+        <v>963</v>
+      </c>
+      <c r="C533" t="s">
+        <v>962</v>
+      </c>
+      <c r="E533" t="s">
+        <v>140</v>
+      </c>
+      <c r="F533" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G533" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H533" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I533" t="s">
+        <v>145</v>
+      </c>
+      <c r="J533" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L533" t="s">
+        <v>768</v>
+      </c>
+      <c r="M533" t="s">
+        <v>403</v>
+      </c>
+      <c r="N533" t="s">
+        <v>467</v>
+      </c>
+      <c r="O533" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="534" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B534" t="s">
+        <v>963</v>
+      </c>
+      <c r="C534" t="s">
+        <v>962</v>
+      </c>
+      <c r="E534" t="s">
+        <v>140</v>
+      </c>
+      <c r="F534" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G534" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H534" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I534" t="s">
+        <v>300</v>
+      </c>
+      <c r="J534" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L534" t="s">
+        <v>768</v>
+      </c>
+      <c r="M534" t="s">
+        <v>403</v>
+      </c>
+      <c r="N534" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="535" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B535" t="s">
+        <v>963</v>
+      </c>
+      <c r="C535" t="s">
+        <v>962</v>
+      </c>
+      <c r="E535" t="s">
+        <v>140</v>
+      </c>
+      <c r="F535" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G535" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H535" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I535" t="s">
+        <v>487</v>
+      </c>
+      <c r="J535" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L535" t="s">
+        <v>768</v>
+      </c>
+      <c r="M535" t="s">
+        <v>403</v>
+      </c>
+      <c r="N535" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="536" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B536" t="s">
+        <v>963</v>
+      </c>
+      <c r="C536" t="s">
+        <v>962</v>
+      </c>
+      <c r="E536" t="s">
+        <v>140</v>
+      </c>
+      <c r="F536" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G536" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H536" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I536" t="s">
+        <v>839</v>
+      </c>
+      <c r="J536" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L536" t="s">
+        <v>768</v>
+      </c>
+      <c r="M536" t="s">
+        <v>403</v>
+      </c>
+      <c r="N536" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="537" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B537" t="s">
+        <v>963</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E537" t="s">
+        <v>140</v>
+      </c>
+      <c r="F537" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G537" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H537" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I537" t="s">
+        <v>839</v>
+      </c>
+      <c r="J537" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L537" t="s">
+        <v>768</v>
+      </c>
+      <c r="M537" t="s">
+        <v>403</v>
+      </c>
+      <c r="N537" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="538" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B538" t="s">
+        <v>963</v>
+      </c>
+      <c r="C538" t="s">
+        <v>450</v>
+      </c>
+      <c r="E538" t="s">
+        <v>140</v>
+      </c>
+      <c r="F538" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G538" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H538" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I538" t="s">
+        <v>839</v>
+      </c>
+      <c r="J538" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L538" t="s">
+        <v>768</v>
+      </c>
+      <c r="M538" t="s">
+        <v>403</v>
+      </c>
+      <c r="N538" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="539" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B539" t="s">
+        <v>963</v>
+      </c>
+      <c r="C539" t="s">
+        <v>450</v>
+      </c>
+      <c r="E539" t="s">
+        <v>140</v>
+      </c>
+      <c r="F539" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G539" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H539" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I539" t="s">
+        <v>839</v>
+      </c>
+      <c r="J539" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L539" t="s">
+        <v>768</v>
+      </c>
+      <c r="M539" t="s">
+        <v>403</v>
+      </c>
+      <c r="N539" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="540" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B540" t="s">
+        <v>963</v>
+      </c>
+      <c r="C540" t="s">
+        <v>450</v>
+      </c>
+      <c r="E540" t="s">
+        <v>140</v>
+      </c>
+      <c r="F540" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G540" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H540" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I540" t="s">
+        <v>839</v>
+      </c>
+      <c r="J540" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L540" t="s">
+        <v>768</v>
+      </c>
+      <c r="M540" t="s">
+        <v>403</v>
+      </c>
+      <c r="N540" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="541" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B541" t="s">
+        <v>963</v>
+      </c>
+      <c r="C541" t="s">
+        <v>450</v>
+      </c>
+      <c r="E541" t="s">
+        <v>140</v>
+      </c>
+      <c r="F541" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G541" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H541" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I541" t="s">
+        <v>839</v>
+      </c>
+      <c r="J541" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L541" t="s">
+        <v>768</v>
+      </c>
+      <c r="M541" t="s">
+        <v>403</v>
+      </c>
+      <c r="N541" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="542" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B542" t="s">
+        <v>963</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E542" t="s">
+        <v>140</v>
+      </c>
+      <c r="F542" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G542" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H542" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I542" t="s">
+        <v>839</v>
+      </c>
+      <c r="J542" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L542" t="s">
+        <v>768</v>
+      </c>
+      <c r="M542" t="s">
+        <v>403</v>
+      </c>
+      <c r="N542" t="s">
+        <v>1070</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC4BA61-C5D9-465E-8F2E-D58F34E7BECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB25518-A991-48FD-BBCF-C954F6EE7DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9109" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9111" uniqueCount="1765">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -5337,6 +5337,9 @@
   </si>
   <si>
     <t>러셀 3000지수</t>
+  </si>
+  <si>
+    <t>ADP</t>
   </si>
 </sst>
 </file>
@@ -24233,6 +24236,9 @@
       <c r="G473" s="5" t="s">
         <v>841</v>
       </c>
+      <c r="H473" t="s">
+        <v>1764</v>
+      </c>
       <c r="I473" t="s">
         <v>817</v>
       </c>
@@ -24270,6 +24276,9 @@
       </c>
       <c r="G474" s="5" t="s">
         <v>845</v>
+      </c>
+      <c r="H474" t="s">
+        <v>882</v>
       </c>
       <c r="I474" t="s">
         <v>817</v>

--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB25518-A991-48FD-BBCF-C954F6EE7DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5E2D8B-5E0B-4B16-8628-B683E39352C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9111" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9279" uniqueCount="1863">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -5340,6 +5340,300 @@
   </si>
   <si>
     <t>ADP</t>
+  </si>
+  <si>
+    <t>VXD</t>
+  </si>
+  <si>
+    <t>RVX</t>
+  </si>
+  <si>
+    <t>CBOEFTSE</t>
+  </si>
+  <si>
+    <t>DV1X</t>
+  </si>
+  <si>
+    <t>INDIAVIX</t>
+  </si>
+  <si>
+    <t>NSE</t>
+  </si>
+  <si>
+    <t>V3X</t>
+  </si>
+  <si>
+    <t>SIX</t>
+  </si>
+  <si>
+    <t>VXEFA</t>
+  </si>
+  <si>
+    <t>VXEWZ</t>
+  </si>
+  <si>
+    <t>CBOE Brazil ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE Developed Markets ETF Volatility Index</t>
+  </si>
+  <si>
+    <t>Volatility Index on the SMI</t>
+  </si>
+  <si>
+    <t>India VIX Index</t>
+  </si>
+  <si>
+    <t>DAX Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE RUSSELL 2000 VOLATILITY Index</t>
+  </si>
+  <si>
+    <t>Swiss</t>
+  </si>
+  <si>
+    <t>VDAX</t>
+  </si>
+  <si>
+    <t>VSMI</t>
+  </si>
+  <si>
+    <t>VXEMZ</t>
+  </si>
+  <si>
+    <t>CBOE 브라질 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 선진국시장 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>KOSPI 변동성지수</t>
+  </si>
+  <si>
+    <t>EUROSTOXX50 변동성지수</t>
+  </si>
+  <si>
+    <t>NIKKEI 변동성지수</t>
+  </si>
+  <si>
+    <t>Hang Seng 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 개도국시장 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>ICE BofA 채권 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 금 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 금 채굴기업 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 은 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 원유 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 비트코인 ETF 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE 다우존스 변동성지수</t>
+  </si>
+  <si>
+    <t>CBOE DJIA Volatility Index</t>
+  </si>
+  <si>
+    <t>CBOE 러셀2000 변동성지수</t>
+  </si>
+  <si>
+    <t>DAX 변동성지수</t>
+  </si>
+  <si>
+    <t>NIFTY 변동성지수</t>
+  </si>
+  <si>
+    <t>SMI 변동성지수</t>
+  </si>
+  <si>
+    <t>상해종합지수</t>
+  </si>
+  <si>
+    <t>심천종합지수</t>
+  </si>
+  <si>
+    <t>ChiNext 지수</t>
+  </si>
+  <si>
+    <t>CSI 300 지수</t>
+  </si>
+  <si>
+    <t>CSI 300 에너지지수</t>
+  </si>
+  <si>
+    <t>CSI 300 소재지수</t>
+  </si>
+  <si>
+    <t>CSI 300 산업재지수</t>
+  </si>
+  <si>
+    <t>CSI 300 경기소비재지수</t>
+  </si>
+  <si>
+    <t>CSI 300 필수소비재지수</t>
+  </si>
+  <si>
+    <t>CSI 300 헬스케어지수</t>
+  </si>
+  <si>
+    <t>CSI 300 금융지수</t>
+  </si>
+  <si>
+    <t>CSI 300 정보기술지수</t>
+  </si>
+  <si>
+    <t>CSI 300 커뮤니케이션 서비스지수</t>
+  </si>
+  <si>
+    <t>CSI 300 유틸리티지수</t>
+  </si>
+  <si>
+    <t>CSI 300 부동산지수</t>
+  </si>
+  <si>
+    <t>TOPIX 은행지수</t>
+  </si>
+  <si>
+    <t>TOPIX 장비기업지수</t>
+  </si>
+  <si>
+    <t>TOPIX 소매기업지수</t>
+  </si>
+  <si>
+    <t>TOPIX 식료품기업지수</t>
+  </si>
+  <si>
+    <t>TOPIX 부동산지수</t>
+  </si>
+  <si>
+    <t>TOPIX 에너지원재료지수</t>
+  </si>
+  <si>
+    <t>TOPIX 은행제외 금융지수</t>
+  </si>
+  <si>
+    <t>TOPIX 제약지수</t>
+  </si>
+  <si>
+    <t>TOPIX 전기및가스지수</t>
+  </si>
+  <si>
+    <t>TOPIX IT산업및서비스지수</t>
+  </si>
+  <si>
+    <t>TOPIX 철강및비철금속지수</t>
+  </si>
+  <si>
+    <t>TOPIX 소재화학지수</t>
+  </si>
+  <si>
+    <t>TOPIX 건설및자재지수</t>
+  </si>
+  <si>
+    <t>TOPIX 교통및운송지수</t>
+  </si>
+  <si>
+    <t>TOPIX 유통기업지수</t>
+  </si>
+  <si>
+    <t>TOPIX 자동차및교통기업지수</t>
+  </si>
+  <si>
+    <t>TOPIX 가전제품기업지수</t>
+  </si>
+  <si>
+    <t>CRSP 전체시장지수</t>
+  </si>
+  <si>
+    <t>CRSP 대형주지수</t>
+  </si>
+  <si>
+    <t>CRSP 초대형주지수</t>
+  </si>
+  <si>
+    <t>CRSP 중형주지수</t>
+  </si>
+  <si>
+    <t>CRSP 소형주지수</t>
+  </si>
+  <si>
+    <t>CRSP 초소형주지수</t>
+  </si>
+  <si>
+    <t>CRSP 에너지지수</t>
+  </si>
+  <si>
+    <t>CRSP 소재지수</t>
+  </si>
+  <si>
+    <t>CRSP 산업재지수</t>
+  </si>
+  <si>
+    <t>CRSP 경기소비재지수</t>
+  </si>
+  <si>
+    <t>CRSP 필수소비재지수</t>
+  </si>
+  <si>
+    <t>CRSP 헬스케어지수</t>
+  </si>
+  <si>
+    <t>CRSP 금융지수</t>
+  </si>
+  <si>
+    <t>CRSP 정보기술지수</t>
+  </si>
+  <si>
+    <t>CRSP 미디어 및 커뮤니케이션지수</t>
+  </si>
+  <si>
+    <t>CRSP 유틸리티지수</t>
+  </si>
+  <si>
+    <t>CRSP 부동산 및 리츠지수</t>
+  </si>
+  <si>
+    <t>NAAIM 투자자 익스포저 평균지수</t>
+  </si>
+  <si>
+    <t>CBOE 실현변동성지수</t>
+  </si>
+  <si>
+    <t>FTSE</t>
+  </si>
+  <si>
+    <t>UKX</t>
+  </si>
+  <si>
+    <t>FTSE100</t>
+  </si>
+  <si>
+    <t>FTSE100 Index</t>
+  </si>
+  <si>
+    <t>FTSE100 지수</t>
+  </si>
+  <si>
+    <t>NIFTY50 Index</t>
+  </si>
+  <si>
+    <t>NIFTY50 지수</t>
+  </si>
+  <si>
+    <t>NIFTY</t>
   </si>
 </sst>
 </file>
@@ -5684,7 +5978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O658"/>
+  <dimension ref="A1:O667"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -5696,7 +5990,7 @@
     <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="40.44140625" customWidth="1"/>
-    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.77734375" customWidth="1"/>
     <col min="14" max="14" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -5753,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C2" t="s">
         <v>438</v>
@@ -5794,7 +6088,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C3" t="s">
         <v>438</v>
@@ -5835,7 +6129,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C4" t="s">
         <v>438</v>
@@ -5876,7 +6170,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C5" t="s">
         <v>438</v>
@@ -5917,7 +6211,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C6" t="s">
         <v>438</v>
@@ -26772,6 +27066,9 @@
       <c r="J535" t="s">
         <v>1048</v>
       </c>
+      <c r="K535" t="s">
+        <v>1854</v>
+      </c>
       <c r="L535" t="s">
         <v>746</v>
       </c>
@@ -26892,6 +27189,9 @@
       <c r="J538" t="s">
         <v>1071</v>
       </c>
+      <c r="K538" t="s">
+        <v>1788</v>
+      </c>
       <c r="L538" t="s">
         <v>746</v>
       </c>
@@ -26933,6 +27233,9 @@
       <c r="J539" t="s">
         <v>1074</v>
       </c>
+      <c r="K539" t="s">
+        <v>1789</v>
+      </c>
       <c r="L539" t="s">
         <v>746</v>
       </c>
@@ -26974,6 +27277,9 @@
       <c r="J540" t="s">
         <v>1054</v>
       </c>
+      <c r="K540" t="s">
+        <v>1790</v>
+      </c>
       <c r="L540" t="s">
         <v>746</v>
       </c>
@@ -27012,6 +27318,9 @@
       <c r="J541" t="s">
         <v>1055</v>
       </c>
+      <c r="K541" t="s">
+        <v>1787</v>
+      </c>
       <c r="L541" t="s">
         <v>746</v>
       </c>
@@ -27050,6 +27359,9 @@
       <c r="J542" t="s">
         <v>1058</v>
       </c>
+      <c r="K542" t="s">
+        <v>1791</v>
+      </c>
       <c r="L542" t="s">
         <v>746</v>
       </c>
@@ -27088,6 +27400,9 @@
       <c r="J543" t="s">
         <v>1059</v>
       </c>
+      <c r="K543" t="s">
+        <v>1792</v>
+      </c>
       <c r="L543" t="s">
         <v>746</v>
       </c>
@@ -27126,6 +27441,9 @@
       <c r="J544" t="s">
         <v>1061</v>
       </c>
+      <c r="K544" t="s">
+        <v>1793</v>
+      </c>
       <c r="L544" t="s">
         <v>746</v>
       </c>
@@ -27164,6 +27482,9 @@
       <c r="J545" t="s">
         <v>1062</v>
       </c>
+      <c r="K545" t="s">
+        <v>1794</v>
+      </c>
       <c r="L545" t="s">
         <v>746</v>
       </c>
@@ -27202,6 +27523,9 @@
       <c r="J546" t="s">
         <v>1063</v>
       </c>
+      <c r="K546" t="s">
+        <v>1795</v>
+      </c>
       <c r="L546" t="s">
         <v>746</v>
       </c>
@@ -27240,6 +27564,9 @@
       <c r="J547" t="s">
         <v>1064</v>
       </c>
+      <c r="K547" t="s">
+        <v>1796</v>
+      </c>
       <c r="L547" t="s">
         <v>746</v>
       </c>
@@ -27278,6 +27605,9 @@
       <c r="J548" t="s">
         <v>1065</v>
       </c>
+      <c r="K548" t="s">
+        <v>1797</v>
+      </c>
       <c r="L548" t="s">
         <v>746</v>
       </c>
@@ -27293,31 +27623,31 @@
         <v>548</v>
       </c>
       <c r="B549" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C549" t="s">
-        <v>1190</v>
+        <v>939</v>
       </c>
       <c r="E549" t="s">
         <v>128</v>
       </c>
       <c r="F549" t="s">
-        <v>1075</v>
+        <v>1765</v>
       </c>
       <c r="G549" s="5" t="s">
-        <v>1087</v>
+        <v>1765</v>
       </c>
       <c r="H549" t="s">
-        <v>1089</v>
+        <v>1057</v>
       </c>
       <c r="I549" t="s">
         <v>817</v>
       </c>
       <c r="J549" t="s">
-        <v>1104</v>
+        <v>1799</v>
       </c>
       <c r="K549" t="s">
-        <v>1531</v>
+        <v>1798</v>
       </c>
       <c r="L549" t="s">
         <v>746</v>
@@ -27334,31 +27664,31 @@
         <v>549</v>
       </c>
       <c r="B550" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C550" t="s">
-        <v>1190</v>
+        <v>939</v>
       </c>
       <c r="E550" t="s">
         <v>128</v>
       </c>
       <c r="F550" t="s">
-        <v>1076</v>
+        <v>1766</v>
       </c>
       <c r="G550" s="5" t="s">
-        <v>1088</v>
+        <v>1766</v>
       </c>
       <c r="H550" t="s">
-        <v>1091</v>
+        <v>1767</v>
       </c>
       <c r="I550" t="s">
         <v>817</v>
       </c>
       <c r="J550" t="s">
-        <v>1105</v>
+        <v>1780</v>
       </c>
       <c r="K550" t="s">
-        <v>1532</v>
+        <v>1800</v>
       </c>
       <c r="L550" t="s">
         <v>746</v>
@@ -27375,31 +27705,31 @@
         <v>550</v>
       </c>
       <c r="B551" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C551" t="s">
-        <v>1190</v>
+        <v>939</v>
       </c>
       <c r="E551" t="s">
         <v>128</v>
       </c>
       <c r="F551" t="s">
-        <v>1092</v>
+        <v>1782</v>
       </c>
       <c r="G551" s="5" t="s">
-        <v>1092</v>
+        <v>1768</v>
       </c>
       <c r="H551" t="s">
-        <v>1090</v>
+        <v>128</v>
       </c>
       <c r="I551" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="J551" t="s">
-        <v>1093</v>
+        <v>1779</v>
       </c>
       <c r="K551" t="s">
-        <v>1533</v>
+        <v>1801</v>
       </c>
       <c r="L551" t="s">
         <v>746</v>
@@ -27408,10 +27738,7 @@
         <v>390</v>
       </c>
       <c r="N551" t="s">
-        <v>452</v>
-      </c>
-      <c r="O551" t="s">
-        <v>1112</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="552" spans="1:15" x14ac:dyDescent="0.3">
@@ -27419,34 +27746,31 @@
         <v>551</v>
       </c>
       <c r="B552" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C552" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1107</v>
+        <v>939</v>
       </c>
       <c r="E552" t="s">
         <v>128</v>
       </c>
       <c r="F552" t="s">
-        <v>1077</v>
+        <v>1769</v>
       </c>
       <c r="G552" s="5" t="s">
-        <v>1077</v>
+        <v>1769</v>
       </c>
       <c r="H552" t="s">
-        <v>1090</v>
+        <v>1770</v>
       </c>
       <c r="I552" t="s">
-        <v>817</v>
+        <v>1413</v>
       </c>
       <c r="J552" t="s">
-        <v>1094</v>
+        <v>1778</v>
       </c>
       <c r="K552" t="s">
-        <v>1534</v>
+        <v>1802</v>
       </c>
       <c r="L552" t="s">
         <v>746</v>
@@ -27463,34 +27787,31 @@
         <v>552</v>
       </c>
       <c r="B553" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C553" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1109</v>
+        <v>939</v>
       </c>
       <c r="E553" t="s">
         <v>128</v>
       </c>
       <c r="F553" t="s">
-        <v>1078</v>
+        <v>1783</v>
       </c>
       <c r="G553" s="5" t="s">
-        <v>1078</v>
+        <v>1771</v>
       </c>
       <c r="H553" t="s">
-        <v>1090</v>
+        <v>1772</v>
       </c>
       <c r="I553" t="s">
-        <v>817</v>
+        <v>1781</v>
       </c>
       <c r="J553" t="s">
-        <v>1095</v>
+        <v>1777</v>
       </c>
       <c r="K553" t="s">
-        <v>1535</v>
+        <v>1803</v>
       </c>
       <c r="L553" t="s">
         <v>746</v>
@@ -27507,34 +27828,31 @@
         <v>553</v>
       </c>
       <c r="B554" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C554" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1109</v>
+        <v>939</v>
       </c>
       <c r="E554" t="s">
         <v>128</v>
       </c>
       <c r="F554" t="s">
-        <v>1079</v>
+        <v>1773</v>
       </c>
       <c r="G554" s="5" t="s">
-        <v>1079</v>
+        <v>1773</v>
       </c>
       <c r="H554" t="s">
-        <v>1090</v>
+        <v>1057</v>
       </c>
       <c r="I554" t="s">
         <v>817</v>
       </c>
       <c r="J554" t="s">
-        <v>1096</v>
+        <v>1776</v>
       </c>
       <c r="K554" t="s">
-        <v>1536</v>
+        <v>1786</v>
       </c>
       <c r="L554" t="s">
         <v>746</v>
@@ -27551,34 +27869,31 @@
         <v>554</v>
       </c>
       <c r="B555" t="s">
-        <v>437</v>
+        <v>940</v>
       </c>
       <c r="C555" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D555" t="s">
-        <v>1110</v>
+        <v>939</v>
       </c>
       <c r="E555" t="s">
         <v>128</v>
       </c>
       <c r="F555" t="s">
-        <v>1080</v>
+        <v>1784</v>
       </c>
       <c r="G555" s="5" t="s">
-        <v>1080</v>
+        <v>1774</v>
       </c>
       <c r="H555" t="s">
-        <v>1090</v>
+        <v>1057</v>
       </c>
       <c r="I555" t="s">
         <v>817</v>
       </c>
       <c r="J555" t="s">
-        <v>1097</v>
+        <v>1775</v>
       </c>
       <c r="K555" t="s">
-        <v>1537</v>
+        <v>1785</v>
       </c>
       <c r="L555" t="s">
         <v>746</v>
@@ -27598,31 +27913,28 @@
         <v>437</v>
       </c>
       <c r="C556" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1109</v>
+        <v>1190</v>
       </c>
       <c r="E556" t="s">
         <v>128</v>
       </c>
       <c r="F556" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G556" s="5" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="H556" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I556" t="s">
         <v>817</v>
       </c>
       <c r="J556" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="K556" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="L556" t="s">
         <v>746</v>
@@ -27642,31 +27954,28 @@
         <v>437</v>
       </c>
       <c r="C557" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D557" t="s">
-        <v>1107</v>
+        <v>1190</v>
       </c>
       <c r="E557" t="s">
         <v>128</v>
       </c>
       <c r="F557" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="G557" s="5" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="H557" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="I557" t="s">
         <v>817</v>
       </c>
       <c r="J557" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="K557" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="L557" t="s">
         <v>746</v>
@@ -27686,19 +27995,16 @@
         <v>437</v>
       </c>
       <c r="C558" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1111</v>
+        <v>1190</v>
       </c>
       <c r="E558" t="s">
         <v>128</v>
       </c>
       <c r="F558" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="G558" s="5" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="H558" t="s">
         <v>1090</v>
@@ -27707,10 +28013,10 @@
         <v>817</v>
       </c>
       <c r="J558" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="K558" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="L558" t="s">
         <v>746</v>
@@ -27719,7 +28025,10 @@
         <v>390</v>
       </c>
       <c r="N558" t="s">
-        <v>1047</v>
+        <v>452</v>
+      </c>
+      <c r="O558" t="s">
+        <v>1112</v>
       </c>
     </row>
     <row r="559" spans="1:15" x14ac:dyDescent="0.3">
@@ -27730,16 +28039,19 @@
         <v>437</v>
       </c>
       <c r="C559" t="s">
-        <v>438</v>
+        <v>1106</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1107</v>
       </c>
       <c r="E559" t="s">
         <v>128</v>
       </c>
       <c r="F559" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="G559" s="5" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="H559" t="s">
         <v>1090</v>
@@ -27748,10 +28060,10 @@
         <v>817</v>
       </c>
       <c r="J559" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="K559" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="L559" t="s">
         <v>746</v>
@@ -27774,16 +28086,16 @@
         <v>1108</v>
       </c>
       <c r="D560" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E560" t="s">
         <v>128</v>
       </c>
       <c r="F560" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="G560" s="5" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="H560" t="s">
         <v>1090</v>
@@ -27792,10 +28104,10 @@
         <v>817</v>
       </c>
       <c r="J560" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="K560" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
       <c r="L560" t="s">
         <v>746</v>
@@ -27817,14 +28129,17 @@
       <c r="C561" t="s">
         <v>1108</v>
       </c>
+      <c r="D561" t="s">
+        <v>1109</v>
+      </c>
       <c r="E561" t="s">
         <v>128</v>
       </c>
       <c r="F561" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G561" s="5" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="H561" t="s">
         <v>1090</v>
@@ -27833,10 +28148,10 @@
         <v>817</v>
       </c>
       <c r="J561" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="K561" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="L561" t="s">
         <v>746</v>
@@ -27853,43 +28168,43 @@
         <v>561</v>
       </c>
       <c r="B562" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C562" t="s">
-        <v>863</v>
+        <v>1108</v>
       </c>
       <c r="D562" t="s">
-        <v>864</v>
+        <v>1110</v>
       </c>
       <c r="E562" t="s">
         <v>128</v>
       </c>
       <c r="F562" t="s">
-        <v>1120</v>
+        <v>1080</v>
+      </c>
+      <c r="G562" s="5" t="s">
+        <v>1080</v>
       </c>
       <c r="H562" t="s">
-        <v>1115</v>
+        <v>1090</v>
       </c>
       <c r="I562" t="s">
         <v>817</v>
       </c>
       <c r="J562" t="s">
-        <v>1117</v>
+        <v>1097</v>
       </c>
       <c r="K562" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="L562" t="s">
-        <v>851</v>
+        <v>746</v>
       </c>
       <c r="M562" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N562" t="s">
-        <v>1115</v>
-      </c>
-      <c r="O562" t="s">
-        <v>1116</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="563" spans="1:15" x14ac:dyDescent="0.3">
@@ -27897,43 +28212,43 @@
         <v>562</v>
       </c>
       <c r="B563" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C563" t="s">
-        <v>863</v>
+        <v>1108</v>
       </c>
       <c r="D563" t="s">
-        <v>864</v>
+        <v>1109</v>
       </c>
       <c r="E563" t="s">
         <v>128</v>
       </c>
       <c r="F563" t="s">
-        <v>1121</v>
+        <v>1081</v>
+      </c>
+      <c r="G563" s="5" t="s">
+        <v>1081</v>
       </c>
       <c r="H563" t="s">
-        <v>1115</v>
+        <v>1090</v>
       </c>
       <c r="I563" t="s">
         <v>817</v>
       </c>
       <c r="J563" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="K563" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="L563" t="s">
-        <v>851</v>
+        <v>746</v>
       </c>
       <c r="M563" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N563" t="s">
-        <v>1115</v>
-      </c>
-      <c r="O563" t="s">
-        <v>1116</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="564" spans="1:15" x14ac:dyDescent="0.3">
@@ -27941,43 +28256,43 @@
         <v>563</v>
       </c>
       <c r="B564" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C564" t="s">
-        <v>863</v>
+        <v>1106</v>
       </c>
       <c r="D564" t="s">
-        <v>864</v>
+        <v>1107</v>
       </c>
       <c r="E564" t="s">
         <v>128</v>
       </c>
       <c r="F564" t="s">
-        <v>1122</v>
+        <v>1082</v>
+      </c>
+      <c r="G564" s="5" t="s">
+        <v>1082</v>
       </c>
       <c r="H564" t="s">
-        <v>1115</v>
+        <v>1090</v>
       </c>
       <c r="I564" t="s">
         <v>817</v>
       </c>
       <c r="J564" t="s">
-        <v>1119</v>
+        <v>1099</v>
       </c>
       <c r="K564" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="L564" t="s">
-        <v>851</v>
+        <v>746</v>
       </c>
       <c r="M564" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N564" t="s">
-        <v>1115</v>
-      </c>
-      <c r="O564" t="s">
-        <v>1116</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="565" spans="1:15" x14ac:dyDescent="0.3">
@@ -27985,34 +28300,34 @@
         <v>564</v>
       </c>
       <c r="B565" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C565" t="s">
-        <v>863</v>
+        <v>1106</v>
       </c>
       <c r="D565" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="E565" t="s">
         <v>128</v>
       </c>
       <c r="F565" t="s">
-        <v>1123</v>
+        <v>1083</v>
       </c>
       <c r="G565" s="5" t="s">
-        <v>1123</v>
+        <v>1083</v>
       </c>
       <c r="H565" t="s">
-        <v>1124</v>
+        <v>1090</v>
       </c>
       <c r="I565" t="s">
         <v>817</v>
       </c>
       <c r="J565" t="s">
-        <v>1127</v>
+        <v>1100</v>
       </c>
       <c r="K565" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="L565" t="s">
         <v>746</v>
@@ -28021,10 +28336,7 @@
         <v>390</v>
       </c>
       <c r="N565" t="s">
-        <v>1126</v>
-      </c>
-      <c r="O565" t="s">
-        <v>1125</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="566" spans="1:15" x14ac:dyDescent="0.3">
@@ -28032,43 +28344,40 @@
         <v>565</v>
       </c>
       <c r="B566" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C566" t="s">
-        <v>863</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1113</v>
+        <v>438</v>
       </c>
       <c r="E566" t="s">
         <v>128</v>
       </c>
       <c r="F566" t="s">
-        <v>1130</v>
+        <v>1084</v>
+      </c>
+      <c r="G566" s="5" t="s">
+        <v>1084</v>
       </c>
       <c r="H566" t="s">
-        <v>446</v>
+        <v>1090</v>
       </c>
       <c r="I566" t="s">
         <v>817</v>
       </c>
       <c r="J566" t="s">
-        <v>1128</v>
+        <v>1101</v>
       </c>
       <c r="K566" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="L566" t="s">
         <v>746</v>
       </c>
       <c r="M566" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N566" t="s">
-        <v>446</v>
-      </c>
-      <c r="O566" t="s">
-        <v>1129</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="567" spans="1:15" x14ac:dyDescent="0.3">
@@ -28076,40 +28385,43 @@
         <v>566</v>
       </c>
       <c r="B567" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C567" t="s">
-        <v>863</v>
+        <v>1108</v>
       </c>
       <c r="D567" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="E567" t="s">
         <v>128</v>
       </c>
       <c r="F567" t="s">
-        <v>1140</v>
+        <v>1085</v>
+      </c>
+      <c r="G567" s="5" t="s">
+        <v>1085</v>
       </c>
       <c r="H567" t="s">
-        <v>1131</v>
+        <v>1090</v>
       </c>
       <c r="I567" t="s">
         <v>817</v>
       </c>
       <c r="J567" t="s">
-        <v>1132</v>
+        <v>1102</v>
+      </c>
+      <c r="K567" t="s">
+        <v>1542</v>
       </c>
       <c r="L567" t="s">
         <v>746</v>
       </c>
       <c r="M567" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N567" t="s">
-        <v>1131</v>
-      </c>
-      <c r="O567" t="s">
-        <v>1139</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="568" spans="1:15" x14ac:dyDescent="0.3">
@@ -28117,40 +28429,40 @@
         <v>567</v>
       </c>
       <c r="B568" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C568" t="s">
-        <v>863</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="E568" t="s">
         <v>128</v>
       </c>
       <c r="F568" t="s">
-        <v>1141</v>
+        <v>1086</v>
+      </c>
+      <c r="G568" s="5" t="s">
+        <v>1086</v>
       </c>
       <c r="H568" t="s">
-        <v>1131</v>
+        <v>1090</v>
       </c>
       <c r="I568" t="s">
         <v>817</v>
       </c>
       <c r="J568" t="s">
-        <v>1133</v>
+        <v>1103</v>
+      </c>
+      <c r="K568" t="s">
+        <v>1543</v>
       </c>
       <c r="L568" t="s">
         <v>746</v>
       </c>
       <c r="M568" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N568" t="s">
-        <v>1131</v>
-      </c>
-      <c r="O568" t="s">
-        <v>1139</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="569" spans="1:15" x14ac:dyDescent="0.3">
@@ -28164,34 +28476,37 @@
         <v>863</v>
       </c>
       <c r="D569" t="s">
-        <v>1114</v>
+        <v>864</v>
       </c>
       <c r="E569" t="s">
         <v>128</v>
       </c>
       <c r="F569" t="s">
-        <v>1145</v>
+        <v>1120</v>
       </c>
       <c r="H569" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="I569" t="s">
         <v>817</v>
       </c>
       <c r="J569" t="s">
-        <v>1134</v>
+        <v>1117</v>
+      </c>
+      <c r="K569" t="s">
+        <v>1544</v>
       </c>
       <c r="L569" t="s">
-        <v>746</v>
+        <v>851</v>
       </c>
       <c r="M569" t="s">
         <v>389</v>
       </c>
       <c r="N569" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="O569" t="s">
-        <v>1139</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="570" spans="1:15" x14ac:dyDescent="0.3">
@@ -28205,34 +28520,37 @@
         <v>863</v>
       </c>
       <c r="D570" t="s">
-        <v>1114</v>
+        <v>864</v>
       </c>
       <c r="E570" t="s">
         <v>128</v>
       </c>
       <c r="F570" t="s">
-        <v>1142</v>
+        <v>1121</v>
       </c>
       <c r="H570" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="I570" t="s">
         <v>817</v>
       </c>
       <c r="J570" t="s">
-        <v>1135</v>
+        <v>1118</v>
+      </c>
+      <c r="K570" t="s">
+        <v>1545</v>
       </c>
       <c r="L570" t="s">
-        <v>746</v>
+        <v>851</v>
       </c>
       <c r="M570" t="s">
         <v>389</v>
       </c>
       <c r="N570" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="O570" t="s">
-        <v>1139</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="571" spans="1:15" x14ac:dyDescent="0.3">
@@ -28246,34 +28564,37 @@
         <v>863</v>
       </c>
       <c r="D571" t="s">
-        <v>1114</v>
+        <v>864</v>
       </c>
       <c r="E571" t="s">
         <v>128</v>
       </c>
       <c r="F571" t="s">
-        <v>1146</v>
+        <v>1122</v>
       </c>
       <c r="H571" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="I571" t="s">
         <v>817</v>
       </c>
       <c r="J571" t="s">
-        <v>1136</v>
+        <v>1119</v>
+      </c>
+      <c r="K571" t="s">
+        <v>1546</v>
       </c>
       <c r="L571" t="s">
-        <v>746</v>
+        <v>851</v>
       </c>
       <c r="M571" t="s">
         <v>389</v>
       </c>
       <c r="N571" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="O571" t="s">
-        <v>1139</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="572" spans="1:15" x14ac:dyDescent="0.3">
@@ -28287,34 +28608,40 @@
         <v>863</v>
       </c>
       <c r="D572" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E572" t="s">
         <v>128</v>
       </c>
       <c r="F572" t="s">
-        <v>1143</v>
+        <v>1123</v>
+      </c>
+      <c r="G572" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="H572" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="I572" t="s">
         <v>817</v>
       </c>
       <c r="J572" t="s">
-        <v>1137</v>
+        <v>1127</v>
+      </c>
+      <c r="K572" t="s">
+        <v>1547</v>
       </c>
       <c r="L572" t="s">
         <v>746</v>
       </c>
       <c r="M572" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N572" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="O572" t="s">
-        <v>1139</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="573" spans="1:15" x14ac:dyDescent="0.3">
@@ -28328,22 +28655,25 @@
         <v>863</v>
       </c>
       <c r="D573" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E573" t="s">
         <v>128</v>
       </c>
       <c r="F573" t="s">
-        <v>1144</v>
+        <v>1130</v>
       </c>
       <c r="H573" t="s">
-        <v>1131</v>
+        <v>446</v>
       </c>
       <c r="I573" t="s">
         <v>817</v>
       </c>
       <c r="J573" t="s">
-        <v>1138</v>
+        <v>1128</v>
+      </c>
+      <c r="K573" t="s">
+        <v>1548</v>
       </c>
       <c r="L573" t="s">
         <v>746</v>
@@ -28352,10 +28682,10 @@
         <v>389</v>
       </c>
       <c r="N573" t="s">
-        <v>1131</v>
+        <v>446</v>
       </c>
       <c r="O573" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="574" spans="1:15" x14ac:dyDescent="0.3">
@@ -28366,37 +28696,40 @@
         <v>448</v>
       </c>
       <c r="C574" t="s">
-        <v>1190</v>
+        <v>863</v>
+      </c>
+      <c r="D574" t="s">
+        <v>1114</v>
       </c>
       <c r="E574" t="s">
         <v>128</v>
       </c>
       <c r="F574" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G574" s="5" t="s">
-        <v>1168</v>
+        <v>1140</v>
       </c>
       <c r="H574" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I574" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J574" t="s">
-        <v>1147</v>
+        <v>1132</v>
       </c>
       <c r="K574" t="s">
-        <v>1302</v>
+        <v>1853</v>
       </c>
       <c r="L574" t="s">
         <v>746</v>
       </c>
       <c r="M574" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N574" t="s">
-        <v>1047</v>
+        <v>1131</v>
+      </c>
+      <c r="O574" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="575" spans="1:15" x14ac:dyDescent="0.3">
@@ -28407,37 +28740,37 @@
         <v>448</v>
       </c>
       <c r="C575" t="s">
-        <v>1191</v>
+        <v>863</v>
+      </c>
+      <c r="D575" t="s">
+        <v>1114</v>
       </c>
       <c r="E575" t="s">
         <v>128</v>
       </c>
       <c r="F575" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G575" s="5" t="s">
-        <v>1170</v>
+        <v>1141</v>
       </c>
       <c r="H575" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I575" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J575" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K575" t="s">
-        <v>1304</v>
+        <v>1133</v>
       </c>
       <c r="L575" t="s">
         <v>746</v>
       </c>
       <c r="M575" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N575" t="s">
-        <v>1047</v>
+        <v>1131</v>
+      </c>
+      <c r="O575" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="576" spans="1:15" x14ac:dyDescent="0.3">
@@ -28448,40 +28781,40 @@
         <v>448</v>
       </c>
       <c r="C576" t="s">
-        <v>1190</v>
+        <v>863</v>
+      </c>
+      <c r="D576" t="s">
+        <v>1114</v>
       </c>
       <c r="E576" t="s">
         <v>128</v>
       </c>
       <c r="F576" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G576" s="5" t="s">
-        <v>1169</v>
+        <v>1145</v>
       </c>
       <c r="H576" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I576" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J576" t="s">
-        <v>1149</v>
-      </c>
-      <c r="K576" t="s">
-        <v>1306</v>
+        <v>1134</v>
       </c>
       <c r="L576" t="s">
         <v>746</v>
       </c>
       <c r="M576" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N576" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+      <c r="O576" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>576</v>
       </c>
@@ -28489,40 +28822,40 @@
         <v>448</v>
       </c>
       <c r="C577" t="s">
-        <v>1191</v>
+        <v>863</v>
+      </c>
+      <c r="D577" t="s">
+        <v>1114</v>
       </c>
       <c r="E577" t="s">
         <v>128</v>
       </c>
       <c r="F577" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G577" s="5" t="s">
-        <v>1171</v>
+        <v>1142</v>
       </c>
       <c r="H577" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I577" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J577" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K577" t="s">
-        <v>1305</v>
+        <v>1135</v>
       </c>
       <c r="L577" t="s">
         <v>746</v>
       </c>
       <c r="M577" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N577" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+      <c r="O577" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>577</v>
       </c>
@@ -28530,40 +28863,40 @@
         <v>448</v>
       </c>
       <c r="C578" t="s">
-        <v>1191</v>
+        <v>863</v>
+      </c>
+      <c r="D578" t="s">
+        <v>1114</v>
       </c>
       <c r="E578" t="s">
         <v>128</v>
       </c>
       <c r="F578" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G578" s="5" t="s">
-        <v>1189</v>
+        <v>1146</v>
       </c>
       <c r="H578" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I578" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J578" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K578" t="s">
-        <v>1303</v>
+        <v>1136</v>
       </c>
       <c r="L578" t="s">
         <v>746</v>
       </c>
       <c r="M578" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N578" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+      <c r="O578" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>578</v>
       </c>
@@ -28571,40 +28904,40 @@
         <v>448</v>
       </c>
       <c r="C579" t="s">
-        <v>981</v>
+        <v>863</v>
+      </c>
+      <c r="D579" t="s">
+        <v>1114</v>
       </c>
       <c r="E579" t="s">
         <v>128</v>
       </c>
       <c r="F579" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G579" s="5" t="s">
-        <v>1173</v>
+        <v>1143</v>
       </c>
       <c r="H579" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I579" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J579" t="s">
-        <v>1152</v>
-      </c>
-      <c r="K579" t="s">
-        <v>1307</v>
+        <v>1137</v>
       </c>
       <c r="L579" t="s">
         <v>746</v>
       </c>
       <c r="M579" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N579" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+      <c r="O579" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>579</v>
       </c>
@@ -28612,40 +28945,40 @@
         <v>448</v>
       </c>
       <c r="C580" t="s">
-        <v>986</v>
+        <v>863</v>
+      </c>
+      <c r="D580" t="s">
+        <v>1114</v>
       </c>
       <c r="E580" t="s">
         <v>128</v>
       </c>
       <c r="F580" t="s">
-        <v>1174</v>
-      </c>
-      <c r="G580" s="5" t="s">
-        <v>1174</v>
+        <v>1144</v>
       </c>
       <c r="H580" t="s">
-        <v>1056</v>
+        <v>1131</v>
       </c>
       <c r="I580" t="s">
-        <v>472</v>
+        <v>817</v>
       </c>
       <c r="J580" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K580" t="s">
-        <v>1308</v>
+        <v>1138</v>
       </c>
       <c r="L580" t="s">
         <v>746</v>
       </c>
       <c r="M580" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N580" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+      <c r="O580" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>580</v>
       </c>
@@ -28653,16 +28986,16 @@
         <v>448</v>
       </c>
       <c r="C581" t="s">
-        <v>984</v>
+        <v>1190</v>
       </c>
       <c r="E581" t="s">
         <v>128</v>
       </c>
       <c r="F581" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="G581" s="5" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="H581" t="s">
         <v>1056</v>
@@ -28671,10 +29004,10 @@
         <v>472</v>
       </c>
       <c r="J581" t="s">
-        <v>1156</v>
+        <v>1147</v>
       </c>
       <c r="K581" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="L581" t="s">
         <v>746</v>
@@ -28686,7 +29019,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>581</v>
       </c>
@@ -28694,16 +29027,16 @@
         <v>448</v>
       </c>
       <c r="C582" t="s">
-        <v>985</v>
+        <v>1191</v>
       </c>
       <c r="E582" t="s">
         <v>128</v>
       </c>
       <c r="F582" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="G582" s="5" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="H582" t="s">
         <v>1056</v>
@@ -28712,10 +29045,10 @@
         <v>472</v>
       </c>
       <c r="J582" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="K582" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="L582" t="s">
         <v>746</v>
@@ -28727,7 +29060,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>582</v>
       </c>
@@ -28735,16 +29068,16 @@
         <v>448</v>
       </c>
       <c r="C583" t="s">
-        <v>438</v>
+        <v>1190</v>
       </c>
       <c r="E583" t="s">
         <v>128</v>
       </c>
       <c r="F583" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="G583" s="5" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="H583" t="s">
         <v>1056</v>
@@ -28753,10 +29086,10 @@
         <v>472</v>
       </c>
       <c r="J583" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="K583" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="L583" t="s">
         <v>746</v>
@@ -28768,7 +29101,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>583</v>
       </c>
@@ -28776,16 +29109,16 @@
         <v>448</v>
       </c>
       <c r="C584" t="s">
-        <v>980</v>
+        <v>1191</v>
       </c>
       <c r="E584" t="s">
         <v>128</v>
       </c>
       <c r="F584" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="G584" s="5" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="H584" t="s">
         <v>1056</v>
@@ -28794,10 +29127,10 @@
         <v>472</v>
       </c>
       <c r="J584" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="K584" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="L584" t="s">
         <v>746</v>
@@ -28809,7 +29142,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>584</v>
       </c>
@@ -28817,16 +29150,16 @@
         <v>448</v>
       </c>
       <c r="C585" t="s">
-        <v>988</v>
+        <v>1191</v>
       </c>
       <c r="E585" t="s">
         <v>128</v>
       </c>
       <c r="F585" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="G585" s="5" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="H585" t="s">
         <v>1056</v>
@@ -28835,10 +29168,10 @@
         <v>472</v>
       </c>
       <c r="J585" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="K585" t="s">
-        <v>1313</v>
+        <v>1303</v>
       </c>
       <c r="L585" t="s">
         <v>746</v>
@@ -28850,7 +29183,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>585</v>
       </c>
@@ -28864,10 +29197,10 @@
         <v>128</v>
       </c>
       <c r="F586" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="G586" s="5" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="H586" t="s">
         <v>1056</v>
@@ -28876,10 +29209,10 @@
         <v>472</v>
       </c>
       <c r="J586" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="K586" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
       <c r="L586" t="s">
         <v>746</v>
@@ -28891,7 +29224,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>586</v>
       </c>
@@ -28899,16 +29232,16 @@
         <v>448</v>
       </c>
       <c r="C587" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E587" t="s">
         <v>128</v>
       </c>
       <c r="F587" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="G587" s="5" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="H587" t="s">
         <v>1056</v>
@@ -28917,10 +29250,10 @@
         <v>472</v>
       </c>
       <c r="J587" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="K587" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
       <c r="L587" t="s">
         <v>746</v>
@@ -28932,7 +29265,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>587</v>
       </c>
@@ -28940,16 +29273,16 @@
         <v>448</v>
       </c>
       <c r="C588" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E588" t="s">
         <v>128</v>
       </c>
       <c r="F588" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="G588" s="5" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="H588" t="s">
         <v>1056</v>
@@ -28958,10 +29291,10 @@
         <v>472</v>
       </c>
       <c r="J588" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="K588" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
       <c r="L588" t="s">
         <v>746</v>
@@ -28973,7 +29306,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>588</v>
       </c>
@@ -28987,10 +29320,10 @@
         <v>128</v>
       </c>
       <c r="F589" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="G589" s="5" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="H589" t="s">
         <v>1056</v>
@@ -28999,10 +29332,10 @@
         <v>472</v>
       </c>
       <c r="J589" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="K589" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="L589" t="s">
         <v>746</v>
@@ -29014,7 +29347,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>589</v>
       </c>
@@ -29022,16 +29355,16 @@
         <v>448</v>
       </c>
       <c r="C590" t="s">
-        <v>981</v>
+        <v>438</v>
       </c>
       <c r="E590" t="s">
         <v>128</v>
       </c>
       <c r="F590" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="G590" s="5" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="H590" t="s">
         <v>1056</v>
@@ -29040,10 +29373,10 @@
         <v>472</v>
       </c>
       <c r="J590" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="K590" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
       <c r="L590" t="s">
         <v>746</v>
@@ -29055,7 +29388,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>590</v>
       </c>
@@ -29063,16 +29396,16 @@
         <v>448</v>
       </c>
       <c r="C591" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E591" t="s">
         <v>128</v>
       </c>
       <c r="F591" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="G591" s="5" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="H591" t="s">
         <v>1056</v>
@@ -29081,10 +29414,10 @@
         <v>472</v>
       </c>
       <c r="J591" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="K591" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="L591" t="s">
         <v>746</v>
@@ -29096,7 +29429,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>591</v>
       </c>
@@ -29104,16 +29437,16 @@
         <v>448</v>
       </c>
       <c r="C592" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="E592" t="s">
         <v>128</v>
       </c>
       <c r="F592" t="s">
-        <v>1237</v>
+        <v>1179</v>
       </c>
       <c r="G592" s="5" t="s">
-        <v>1237</v>
+        <v>1179</v>
       </c>
       <c r="H592" t="s">
         <v>1056</v>
@@ -29122,10 +29455,10 @@
         <v>472</v>
       </c>
       <c r="J592" t="s">
-        <v>1238</v>
+        <v>1158</v>
       </c>
       <c r="K592" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
       <c r="L592" t="s">
         <v>746</v>
@@ -29145,16 +29478,16 @@
         <v>448</v>
       </c>
       <c r="C593" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="E593" t="s">
         <v>128</v>
       </c>
       <c r="F593" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="G593" s="5" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="H593" t="s">
         <v>1056</v>
@@ -29163,10 +29496,10 @@
         <v>472</v>
       </c>
       <c r="J593" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="K593" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="L593" t="s">
         <v>746</v>
@@ -29186,16 +29519,16 @@
         <v>448</v>
       </c>
       <c r="C594" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E594" t="s">
         <v>128</v>
       </c>
       <c r="F594" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="G594" s="5" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="H594" t="s">
         <v>1056</v>
@@ -29204,10 +29537,10 @@
         <v>472</v>
       </c>
       <c r="J594" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="K594" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
       <c r="L594" t="s">
         <v>746</v>
@@ -29227,16 +29560,16 @@
         <v>448</v>
       </c>
       <c r="C595" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="E595" t="s">
         <v>128</v>
       </c>
       <c r="F595" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="G595" s="5" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="H595" t="s">
         <v>1056</v>
@@ -29245,10 +29578,10 @@
         <v>472</v>
       </c>
       <c r="J595" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="K595" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
       <c r="L595" t="s">
         <v>746</v>
@@ -29268,25 +29601,28 @@
         <v>448</v>
       </c>
       <c r="C596" t="s">
-        <v>1190</v>
+        <v>985</v>
       </c>
       <c r="E596" t="s">
         <v>128</v>
       </c>
       <c r="F596" t="s">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="G596" s="5" t="s">
-        <v>1231</v>
+        <v>1183</v>
       </c>
       <c r="H596" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I596" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J596" t="s">
-        <v>1192</v>
+        <v>1162</v>
+      </c>
+      <c r="K596" t="s">
+        <v>1317</v>
       </c>
       <c r="L596" t="s">
         <v>746</v>
@@ -29306,25 +29642,28 @@
         <v>448</v>
       </c>
       <c r="C597" t="s">
-        <v>1233</v>
+        <v>981</v>
       </c>
       <c r="E597" t="s">
         <v>128</v>
       </c>
       <c r="F597" t="s">
-        <v>1210</v>
+        <v>1184</v>
       </c>
       <c r="G597" s="5" t="s">
-        <v>1215</v>
+        <v>1184</v>
       </c>
       <c r="H597" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I597" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J597" t="s">
-        <v>1193</v>
+        <v>1163</v>
+      </c>
+      <c r="K597" t="s">
+        <v>1318</v>
       </c>
       <c r="L597" t="s">
         <v>746</v>
@@ -29344,25 +29683,28 @@
         <v>448</v>
       </c>
       <c r="C598" t="s">
-        <v>1191</v>
+        <v>982</v>
       </c>
       <c r="E598" t="s">
         <v>128</v>
       </c>
       <c r="F598" t="s">
-        <v>1211</v>
+        <v>1185</v>
       </c>
       <c r="G598" s="5" t="s">
-        <v>1216</v>
+        <v>1185</v>
       </c>
       <c r="H598" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I598" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J598" t="s">
-        <v>1194</v>
+        <v>1164</v>
+      </c>
+      <c r="K598" t="s">
+        <v>1319</v>
       </c>
       <c r="L598" t="s">
         <v>746</v>
@@ -29382,25 +29724,28 @@
         <v>448</v>
       </c>
       <c r="C599" t="s">
-        <v>1234</v>
+        <v>983</v>
       </c>
       <c r="E599" t="s">
         <v>128</v>
       </c>
       <c r="F599" t="s">
-        <v>1212</v>
+        <v>1237</v>
       </c>
       <c r="G599" s="5" t="s">
-        <v>1217</v>
+        <v>1237</v>
       </c>
       <c r="H599" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I599" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J599" t="s">
-        <v>1195</v>
+        <v>1238</v>
+      </c>
+      <c r="K599" t="s">
+        <v>1320</v>
       </c>
       <c r="L599" t="s">
         <v>746</v>
@@ -29420,25 +29765,28 @@
         <v>448</v>
       </c>
       <c r="C600" t="s">
-        <v>1235</v>
+        <v>988</v>
       </c>
       <c r="E600" t="s">
         <v>128</v>
       </c>
       <c r="F600" t="s">
-        <v>1213</v>
+        <v>1186</v>
       </c>
       <c r="G600" s="5" t="s">
-        <v>1218</v>
+        <v>1186</v>
       </c>
       <c r="H600" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I600" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J600" t="s">
-        <v>1196</v>
+        <v>1165</v>
+      </c>
+      <c r="K600" t="s">
+        <v>1321</v>
       </c>
       <c r="L600" t="s">
         <v>746</v>
@@ -29458,25 +29806,28 @@
         <v>448</v>
       </c>
       <c r="C601" t="s">
-        <v>1236</v>
+        <v>986</v>
       </c>
       <c r="E601" t="s">
         <v>128</v>
       </c>
       <c r="F601" t="s">
-        <v>1214</v>
+        <v>1187</v>
       </c>
       <c r="G601" s="5" t="s">
-        <v>1219</v>
+        <v>1187</v>
       </c>
       <c r="H601" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I601" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J601" t="s">
-        <v>1197</v>
+        <v>1166</v>
+      </c>
+      <c r="K601" t="s">
+        <v>1322</v>
       </c>
       <c r="L601" t="s">
         <v>746</v>
@@ -29496,25 +29847,28 @@
         <v>448</v>
       </c>
       <c r="C602" t="s">
-        <v>438</v>
+        <v>987</v>
       </c>
       <c r="E602" t="s">
         <v>128</v>
       </c>
       <c r="F602" t="s">
-        <v>1375</v>
+        <v>1188</v>
       </c>
       <c r="G602" s="5" t="s">
-        <v>1220</v>
+        <v>1188</v>
       </c>
       <c r="H602" t="s">
-        <v>1232</v>
+        <v>1056</v>
       </c>
       <c r="I602" t="s">
-        <v>817</v>
+        <v>472</v>
       </c>
       <c r="J602" t="s">
-        <v>1198</v>
+        <v>1167</v>
+      </c>
+      <c r="K602" t="s">
+        <v>1323</v>
       </c>
       <c r="L602" t="s">
         <v>746</v>
@@ -29534,16 +29888,16 @@
         <v>448</v>
       </c>
       <c r="C603" t="s">
-        <v>980</v>
+        <v>1190</v>
       </c>
       <c r="E603" t="s">
         <v>128</v>
       </c>
       <c r="F603" t="s">
-        <v>1376</v>
+        <v>1209</v>
       </c>
       <c r="G603" s="5" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="H603" t="s">
         <v>1232</v>
@@ -29552,7 +29906,10 @@
         <v>817</v>
       </c>
       <c r="J603" t="s">
-        <v>1199</v>
+        <v>1192</v>
+      </c>
+      <c r="K603" t="s">
+        <v>1836</v>
       </c>
       <c r="L603" t="s">
         <v>746</v>
@@ -29572,16 +29929,16 @@
         <v>448</v>
       </c>
       <c r="C604" t="s">
-        <v>981</v>
+        <v>1233</v>
       </c>
       <c r="E604" t="s">
         <v>128</v>
       </c>
       <c r="F604" t="s">
-        <v>1377</v>
+        <v>1210</v>
       </c>
       <c r="G604" s="5" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="H604" t="s">
         <v>1232</v>
@@ -29590,7 +29947,10 @@
         <v>817</v>
       </c>
       <c r="J604" t="s">
-        <v>1200</v>
+        <v>1193</v>
+      </c>
+      <c r="K604" t="s">
+        <v>1838</v>
       </c>
       <c r="L604" t="s">
         <v>746</v>
@@ -29610,16 +29970,16 @@
         <v>448</v>
       </c>
       <c r="C605" t="s">
-        <v>982</v>
+        <v>1191</v>
       </c>
       <c r="E605" t="s">
         <v>128</v>
       </c>
       <c r="F605" t="s">
-        <v>1378</v>
+        <v>1211</v>
       </c>
       <c r="G605" s="5" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="H605" t="s">
         <v>1232</v>
@@ -29628,7 +29988,10 @@
         <v>817</v>
       </c>
       <c r="J605" t="s">
-        <v>1201</v>
+        <v>1194</v>
+      </c>
+      <c r="K605" t="s">
+        <v>1837</v>
       </c>
       <c r="L605" t="s">
         <v>746</v>
@@ -29648,16 +30011,16 @@
         <v>448</v>
       </c>
       <c r="C606" t="s">
-        <v>983</v>
+        <v>1234</v>
       </c>
       <c r="E606" t="s">
         <v>128</v>
       </c>
       <c r="F606" t="s">
-        <v>1379</v>
+        <v>1212</v>
       </c>
       <c r="G606" s="5" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="H606" t="s">
         <v>1232</v>
@@ -29666,7 +30029,10 @@
         <v>817</v>
       </c>
       <c r="J606" t="s">
-        <v>1202</v>
+        <v>1195</v>
+      </c>
+      <c r="K606" t="s">
+        <v>1839</v>
       </c>
       <c r="L606" t="s">
         <v>746</v>
@@ -29686,16 +30052,16 @@
         <v>448</v>
       </c>
       <c r="C607" t="s">
-        <v>984</v>
+        <v>1235</v>
       </c>
       <c r="E607" t="s">
         <v>128</v>
       </c>
       <c r="F607" t="s">
-        <v>1380</v>
+        <v>1213</v>
       </c>
       <c r="G607" s="5" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="H607" t="s">
         <v>1232</v>
@@ -29704,7 +30070,10 @@
         <v>817</v>
       </c>
       <c r="J607" t="s">
-        <v>1203</v>
+        <v>1196</v>
+      </c>
+      <c r="K607" t="s">
+        <v>1840</v>
       </c>
       <c r="L607" t="s">
         <v>746</v>
@@ -29724,16 +30093,16 @@
         <v>448</v>
       </c>
       <c r="C608" t="s">
-        <v>985</v>
+        <v>1236</v>
       </c>
       <c r="E608" t="s">
         <v>128</v>
       </c>
       <c r="F608" t="s">
-        <v>1381</v>
+        <v>1214</v>
       </c>
       <c r="G608" s="5" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="H608" t="s">
         <v>1232</v>
@@ -29742,7 +30111,10 @@
         <v>817</v>
       </c>
       <c r="J608" t="s">
-        <v>1204</v>
+        <v>1197</v>
+      </c>
+      <c r="K608" t="s">
+        <v>1841</v>
       </c>
       <c r="L608" t="s">
         <v>746</v>
@@ -29762,16 +30134,16 @@
         <v>448</v>
       </c>
       <c r="C609" t="s">
-        <v>986</v>
+        <v>438</v>
       </c>
       <c r="E609" t="s">
         <v>128</v>
       </c>
       <c r="F609" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
       <c r="G609" s="5" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="H609" t="s">
         <v>1232</v>
@@ -29780,7 +30152,10 @@
         <v>817</v>
       </c>
       <c r="J609" t="s">
-        <v>1205</v>
+        <v>1198</v>
+      </c>
+      <c r="K609" t="s">
+        <v>1842</v>
       </c>
       <c r="L609" t="s">
         <v>746</v>
@@ -29800,16 +30175,16 @@
         <v>448</v>
       </c>
       <c r="C610" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="E610" t="s">
         <v>128</v>
       </c>
       <c r="F610" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="G610" s="5" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="H610" t="s">
         <v>1232</v>
@@ -29818,7 +30193,10 @@
         <v>817</v>
       </c>
       <c r="J610" t="s">
-        <v>1206</v>
+        <v>1199</v>
+      </c>
+      <c r="K610" t="s">
+        <v>1843</v>
       </c>
       <c r="L610" t="s">
         <v>746</v>
@@ -29838,16 +30216,16 @@
         <v>448</v>
       </c>
       <c r="C611" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="E611" t="s">
         <v>128</v>
       </c>
       <c r="F611" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="G611" s="5" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="H611" t="s">
         <v>1232</v>
@@ -29856,7 +30234,10 @@
         <v>817</v>
       </c>
       <c r="J611" t="s">
-        <v>1207</v>
+        <v>1200</v>
+      </c>
+      <c r="K611" t="s">
+        <v>1844</v>
       </c>
       <c r="L611" t="s">
         <v>746</v>
@@ -29876,16 +30257,16 @@
         <v>448</v>
       </c>
       <c r="C612" t="s">
-        <v>471</v>
+        <v>982</v>
       </c>
       <c r="E612" t="s">
         <v>128</v>
       </c>
       <c r="F612" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="G612" s="5" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="H612" t="s">
         <v>1232</v>
@@ -29894,7 +30275,10 @@
         <v>817</v>
       </c>
       <c r="J612" t="s">
-        <v>1208</v>
+        <v>1201</v>
+      </c>
+      <c r="K612" t="s">
+        <v>1845</v>
       </c>
       <c r="L612" t="s">
         <v>746</v>
@@ -29914,28 +30298,28 @@
         <v>448</v>
       </c>
       <c r="C613" t="s">
-        <v>1190</v>
+        <v>983</v>
       </c>
       <c r="E613" t="s">
         <v>128</v>
       </c>
       <c r="F613" t="s">
-        <v>1244</v>
+        <v>1379</v>
       </c>
       <c r="G613" s="5" t="s">
-        <v>1244</v>
+        <v>1224</v>
       </c>
       <c r="H613" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I613" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J613" t="s">
-        <v>1301</v>
+        <v>1202</v>
       </c>
       <c r="K613" t="s">
-        <v>1559</v>
+        <v>1846</v>
       </c>
       <c r="L613" t="s">
         <v>746</v>
@@ -29955,28 +30339,28 @@
         <v>448</v>
       </c>
       <c r="C614" t="s">
-        <v>1191</v>
+        <v>984</v>
       </c>
       <c r="E614" t="s">
         <v>128</v>
       </c>
       <c r="F614" t="s">
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="G614" s="5" t="s">
-        <v>1245</v>
+        <v>1225</v>
       </c>
       <c r="H614" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I614" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J614" t="s">
-        <v>1246</v>
+        <v>1203</v>
       </c>
       <c r="K614" t="s">
-        <v>1560</v>
+        <v>1847</v>
       </c>
       <c r="L614" t="s">
         <v>746</v>
@@ -29996,28 +30380,28 @@
         <v>448</v>
       </c>
       <c r="C615" t="s">
-        <v>1191</v>
+        <v>985</v>
       </c>
       <c r="E615" t="s">
         <v>128</v>
       </c>
       <c r="F615" t="s">
-        <v>1247</v>
+        <v>1381</v>
       </c>
       <c r="G615" s="5" t="s">
-        <v>1247</v>
+        <v>1226</v>
       </c>
       <c r="H615" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I615" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J615" t="s">
-        <v>1248</v>
+        <v>1204</v>
       </c>
       <c r="K615" t="s">
-        <v>1561</v>
+        <v>1848</v>
       </c>
       <c r="L615" t="s">
         <v>746</v>
@@ -30037,28 +30421,28 @@
         <v>448</v>
       </c>
       <c r="C616" t="s">
-        <v>1243</v>
+        <v>986</v>
       </c>
       <c r="E616" t="s">
         <v>128</v>
       </c>
       <c r="F616" t="s">
-        <v>1249</v>
+        <v>1382</v>
       </c>
       <c r="G616" s="5" t="s">
-        <v>1249</v>
+        <v>1227</v>
       </c>
       <c r="H616" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I616" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J616" t="s">
-        <v>1250</v>
+        <v>1205</v>
       </c>
       <c r="K616" t="s">
-        <v>1562</v>
+        <v>1849</v>
       </c>
       <c r="L616" t="s">
         <v>746</v>
@@ -30078,28 +30462,28 @@
         <v>448</v>
       </c>
       <c r="C617" t="s">
-        <v>985</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1251</v>
+        <v>988</v>
       </c>
       <c r="E617" t="s">
         <v>128</v>
       </c>
       <c r="F617" t="s">
-        <v>1252</v>
+        <v>1383</v>
       </c>
       <c r="G617" s="5" t="s">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="H617" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I617" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J617" t="s">
-        <v>1253</v>
+        <v>1206</v>
+      </c>
+      <c r="K617" t="s">
+        <v>1850</v>
       </c>
       <c r="L617" t="s">
         <v>746</v>
@@ -30119,28 +30503,28 @@
         <v>448</v>
       </c>
       <c r="C618" t="s">
-        <v>983</v>
-      </c>
-      <c r="D618" t="s">
-        <v>1254</v>
+        <v>987</v>
       </c>
       <c r="E618" t="s">
         <v>128</v>
       </c>
       <c r="F618" t="s">
-        <v>1255</v>
+        <v>1384</v>
       </c>
       <c r="G618" s="5" t="s">
-        <v>1255</v>
+        <v>1229</v>
       </c>
       <c r="H618" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I618" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J618" t="s">
-        <v>1256</v>
+        <v>1207</v>
+      </c>
+      <c r="K618" t="s">
+        <v>1851</v>
       </c>
       <c r="L618" t="s">
         <v>746</v>
@@ -30160,28 +30544,28 @@
         <v>448</v>
       </c>
       <c r="C619" t="s">
-        <v>982</v>
-      </c>
-      <c r="D619" t="s">
-        <v>1257</v>
+        <v>471</v>
       </c>
       <c r="E619" t="s">
         <v>128</v>
       </c>
       <c r="F619" t="s">
-        <v>1258</v>
+        <v>1385</v>
       </c>
       <c r="G619" s="5" t="s">
-        <v>1258</v>
+        <v>1230</v>
       </c>
       <c r="H619" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="I619" t="s">
-        <v>133</v>
+        <v>817</v>
       </c>
       <c r="J619" t="s">
-        <v>1259</v>
+        <v>1208</v>
+      </c>
+      <c r="K619" t="s">
+        <v>1852</v>
       </c>
       <c r="L619" t="s">
         <v>746</v>
@@ -30201,19 +30585,16 @@
         <v>448</v>
       </c>
       <c r="C620" t="s">
-        <v>981</v>
-      </c>
-      <c r="D620" t="s">
-        <v>1260</v>
+        <v>1190</v>
       </c>
       <c r="E620" t="s">
         <v>128</v>
       </c>
       <c r="F620" t="s">
-        <v>1261</v>
+        <v>1244</v>
       </c>
       <c r="G620" s="5" t="s">
-        <v>1261</v>
+        <v>1244</v>
       </c>
       <c r="H620" t="s">
         <v>1242</v>
@@ -30222,7 +30603,10 @@
         <v>133</v>
       </c>
       <c r="J620" t="s">
-        <v>1262</v>
+        <v>1301</v>
+      </c>
+      <c r="K620" t="s">
+        <v>1559</v>
       </c>
       <c r="L620" t="s">
         <v>746</v>
@@ -30242,19 +30626,16 @@
         <v>448</v>
       </c>
       <c r="C621" t="s">
-        <v>471</v>
-      </c>
-      <c r="D621" t="s">
-        <v>471</v>
+        <v>1191</v>
       </c>
       <c r="E621" t="s">
         <v>128</v>
       </c>
       <c r="F621" t="s">
-        <v>1263</v>
+        <v>1245</v>
       </c>
       <c r="G621" s="5" t="s">
-        <v>1263</v>
+        <v>1245</v>
       </c>
       <c r="H621" t="s">
         <v>1242</v>
@@ -30263,7 +30644,10 @@
         <v>133</v>
       </c>
       <c r="J621" t="s">
-        <v>1264</v>
+        <v>1246</v>
+      </c>
+      <c r="K621" t="s">
+        <v>1560</v>
       </c>
       <c r="L621" t="s">
         <v>746</v>
@@ -30283,19 +30667,16 @@
         <v>448</v>
       </c>
       <c r="C622" t="s">
-        <v>438</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1265</v>
+        <v>1191</v>
       </c>
       <c r="E622" t="s">
         <v>128</v>
       </c>
       <c r="F622" t="s">
-        <v>1266</v>
+        <v>1247</v>
       </c>
       <c r="G622" s="5" t="s">
-        <v>1266</v>
+        <v>1247</v>
       </c>
       <c r="H622" t="s">
         <v>1242</v>
@@ -30304,7 +30685,10 @@
         <v>133</v>
       </c>
       <c r="J622" t="s">
-        <v>1267</v>
+        <v>1248</v>
+      </c>
+      <c r="K622" t="s">
+        <v>1561</v>
       </c>
       <c r="L622" t="s">
         <v>746</v>
@@ -30324,19 +30708,16 @@
         <v>448</v>
       </c>
       <c r="C623" t="s">
-        <v>985</v>
-      </c>
-      <c r="D623" t="s">
-        <v>1268</v>
+        <v>1243</v>
       </c>
       <c r="E623" t="s">
         <v>128</v>
       </c>
       <c r="F623" t="s">
-        <v>1269</v>
+        <v>1249</v>
       </c>
       <c r="G623" s="5" t="s">
-        <v>1269</v>
+        <v>1249</v>
       </c>
       <c r="H623" t="s">
         <v>1242</v>
@@ -30345,7 +30726,10 @@
         <v>133</v>
       </c>
       <c r="J623" t="s">
-        <v>1270</v>
+        <v>1250</v>
+      </c>
+      <c r="K623" t="s">
+        <v>1562</v>
       </c>
       <c r="L623" t="s">
         <v>746</v>
@@ -30365,19 +30749,19 @@
         <v>448</v>
       </c>
       <c r="C624" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D624" t="s">
-        <v>1271</v>
+        <v>1251</v>
       </c>
       <c r="E624" t="s">
         <v>128</v>
       </c>
       <c r="F624" t="s">
-        <v>1272</v>
+        <v>1252</v>
       </c>
       <c r="G624" s="5" t="s">
-        <v>1272</v>
+        <v>1252</v>
       </c>
       <c r="H624" t="s">
         <v>1242</v>
@@ -30386,7 +30770,10 @@
         <v>133</v>
       </c>
       <c r="J624" t="s">
-        <v>1273</v>
+        <v>1253</v>
+      </c>
+      <c r="K624" t="s">
+        <v>1819</v>
       </c>
       <c r="L624" t="s">
         <v>746</v>
@@ -30406,19 +30793,19 @@
         <v>448</v>
       </c>
       <c r="C625" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="D625" t="s">
-        <v>1274</v>
+        <v>1254</v>
       </c>
       <c r="E625" t="s">
         <v>128</v>
       </c>
       <c r="F625" t="s">
-        <v>1275</v>
+        <v>1255</v>
       </c>
       <c r="G625" s="5" t="s">
-        <v>1275</v>
+        <v>1255</v>
       </c>
       <c r="H625" t="s">
         <v>1242</v>
@@ -30427,7 +30814,10 @@
         <v>133</v>
       </c>
       <c r="J625" t="s">
-        <v>1276</v>
+        <v>1256</v>
+      </c>
+      <c r="K625" t="s">
+        <v>1822</v>
       </c>
       <c r="L625" t="s">
         <v>746</v>
@@ -30447,19 +30837,19 @@
         <v>448</v>
       </c>
       <c r="C626" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="D626" t="s">
-        <v>1277</v>
+        <v>1257</v>
       </c>
       <c r="E626" t="s">
         <v>128</v>
       </c>
       <c r="F626" t="s">
-        <v>1278</v>
+        <v>1258</v>
       </c>
       <c r="G626" s="5" t="s">
-        <v>1278</v>
+        <v>1258</v>
       </c>
       <c r="H626" t="s">
         <v>1242</v>
@@ -30468,7 +30858,10 @@
         <v>133</v>
       </c>
       <c r="J626" t="s">
-        <v>1279</v>
+        <v>1259</v>
+      </c>
+      <c r="K626" t="s">
+        <v>1821</v>
       </c>
       <c r="L626" t="s">
         <v>746</v>
@@ -30488,19 +30881,19 @@
         <v>448</v>
       </c>
       <c r="C627" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D627" t="s">
-        <v>1280</v>
+        <v>1260</v>
       </c>
       <c r="E627" t="s">
         <v>128</v>
       </c>
       <c r="F627" t="s">
-        <v>1281</v>
+        <v>1261</v>
       </c>
       <c r="G627" s="5" t="s">
-        <v>1281</v>
+        <v>1261</v>
       </c>
       <c r="H627" t="s">
         <v>1242</v>
@@ -30509,7 +30902,10 @@
         <v>133</v>
       </c>
       <c r="J627" t="s">
-        <v>1282</v>
+        <v>1262</v>
+      </c>
+      <c r="K627" t="s">
+        <v>1820</v>
       </c>
       <c r="L627" t="s">
         <v>746</v>
@@ -30529,19 +30925,19 @@
         <v>448</v>
       </c>
       <c r="C628" t="s">
-        <v>980</v>
+        <v>471</v>
       </c>
       <c r="D628" t="s">
-        <v>1283</v>
+        <v>471</v>
       </c>
       <c r="E628" t="s">
         <v>128</v>
       </c>
       <c r="F628" t="s">
-        <v>1284</v>
+        <v>1263</v>
       </c>
       <c r="G628" s="5" t="s">
-        <v>1284</v>
+        <v>1263</v>
       </c>
       <c r="H628" t="s">
         <v>1242</v>
@@ -30550,7 +30946,10 @@
         <v>133</v>
       </c>
       <c r="J628" t="s">
-        <v>1285</v>
+        <v>1264</v>
+      </c>
+      <c r="K628" t="s">
+        <v>1823</v>
       </c>
       <c r="L628" t="s">
         <v>746</v>
@@ -30570,19 +30969,19 @@
         <v>448</v>
       </c>
       <c r="C629" t="s">
-        <v>981</v>
+        <v>438</v>
       </c>
       <c r="D629" t="s">
-        <v>1286</v>
+        <v>1265</v>
       </c>
       <c r="E629" t="s">
         <v>128</v>
       </c>
       <c r="F629" t="s">
-        <v>1287</v>
+        <v>1266</v>
       </c>
       <c r="G629" s="5" t="s">
-        <v>1287</v>
+        <v>1266</v>
       </c>
       <c r="H629" t="s">
         <v>1242</v>
@@ -30591,7 +30990,10 @@
         <v>133</v>
       </c>
       <c r="J629" t="s">
-        <v>1288</v>
+        <v>1267</v>
+      </c>
+      <c r="K629" t="s">
+        <v>1824</v>
       </c>
       <c r="L629" t="s">
         <v>746</v>
@@ -30611,19 +31013,19 @@
         <v>448</v>
       </c>
       <c r="C630" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D630" t="s">
-        <v>1289</v>
+        <v>1268</v>
       </c>
       <c r="E630" t="s">
         <v>128</v>
       </c>
       <c r="F630" t="s">
-        <v>1290</v>
+        <v>1269</v>
       </c>
       <c r="G630" s="5" t="s">
-        <v>1290</v>
+        <v>1269</v>
       </c>
       <c r="H630" t="s">
         <v>1242</v>
@@ -30632,7 +31034,10 @@
         <v>133</v>
       </c>
       <c r="J630" t="s">
-        <v>1291</v>
+        <v>1270</v>
+      </c>
+      <c r="K630" t="s">
+        <v>1825</v>
       </c>
       <c r="L630" t="s">
         <v>746</v>
@@ -30652,19 +31057,19 @@
         <v>448</v>
       </c>
       <c r="C631" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D631" t="s">
-        <v>1292</v>
+        <v>1271</v>
       </c>
       <c r="E631" t="s">
         <v>128</v>
       </c>
       <c r="F631" t="s">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="G631" s="5" t="s">
-        <v>1293</v>
+        <v>1272</v>
       </c>
       <c r="H631" t="s">
         <v>1242</v>
@@ -30673,7 +31078,10 @@
         <v>133</v>
       </c>
       <c r="J631" t="s">
-        <v>1294</v>
+        <v>1273</v>
+      </c>
+      <c r="K631" t="s">
+        <v>1826</v>
       </c>
       <c r="L631" t="s">
         <v>746</v>
@@ -30693,19 +31101,19 @@
         <v>448</v>
       </c>
       <c r="C632" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="D632" t="s">
-        <v>1295</v>
+        <v>1274</v>
       </c>
       <c r="E632" t="s">
         <v>128</v>
       </c>
       <c r="F632" t="s">
-        <v>1296</v>
+        <v>1275</v>
       </c>
       <c r="G632" s="5" t="s">
-        <v>1296</v>
+        <v>1275</v>
       </c>
       <c r="H632" t="s">
         <v>1242</v>
@@ -30714,7 +31122,10 @@
         <v>133</v>
       </c>
       <c r="J632" t="s">
-        <v>1297</v>
+        <v>1276</v>
+      </c>
+      <c r="K632" t="s">
+        <v>1827</v>
       </c>
       <c r="L632" t="s">
         <v>746</v>
@@ -30734,19 +31145,19 @@
         <v>448</v>
       </c>
       <c r="C633" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D633" t="s">
-        <v>1298</v>
+        <v>1277</v>
       </c>
       <c r="E633" t="s">
         <v>128</v>
       </c>
       <c r="F633" t="s">
-        <v>1299</v>
+        <v>1278</v>
       </c>
       <c r="G633" s="5" t="s">
-        <v>1299</v>
+        <v>1278</v>
       </c>
       <c r="H633" t="s">
         <v>1242</v>
@@ -30755,7 +31166,10 @@
         <v>133</v>
       </c>
       <c r="J633" t="s">
-        <v>1300</v>
+        <v>1279</v>
+      </c>
+      <c r="K633" t="s">
+        <v>1828</v>
       </c>
       <c r="L633" t="s">
         <v>746</v>
@@ -30775,25 +31189,31 @@
         <v>448</v>
       </c>
       <c r="C634" t="s">
-        <v>1191</v>
+        <v>980</v>
+      </c>
+      <c r="D634" t="s">
+        <v>1280</v>
       </c>
       <c r="E634" t="s">
         <v>128</v>
       </c>
       <c r="F634" t="s">
-        <v>1346</v>
+        <v>1281</v>
       </c>
       <c r="G634" s="5" t="s">
-        <v>1360</v>
+        <v>1281</v>
       </c>
       <c r="H634" t="s">
-        <v>507</v>
+        <v>1242</v>
       </c>
       <c r="I634" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J634" t="s">
-        <v>1324</v>
+        <v>1282</v>
+      </c>
+      <c r="K634" t="s">
+        <v>1829</v>
       </c>
       <c r="L634" t="s">
         <v>746</v>
@@ -30813,25 +31233,31 @@
         <v>448</v>
       </c>
       <c r="C635" t="s">
-        <v>1191</v>
+        <v>980</v>
+      </c>
+      <c r="D635" t="s">
+        <v>1283</v>
       </c>
       <c r="E635" t="s">
         <v>128</v>
       </c>
       <c r="F635" t="s">
-        <v>1325</v>
+        <v>1284</v>
       </c>
       <c r="G635" s="5" t="s">
-        <v>1361</v>
+        <v>1284</v>
       </c>
       <c r="H635" t="s">
-        <v>1325</v>
+        <v>1242</v>
       </c>
       <c r="I635" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J635" t="s">
-        <v>1326</v>
+        <v>1285</v>
+      </c>
+      <c r="K635" t="s">
+        <v>1830</v>
       </c>
       <c r="L635" t="s">
         <v>746</v>
@@ -30851,25 +31277,31 @@
         <v>448</v>
       </c>
       <c r="C636" t="s">
-        <v>1190</v>
+        <v>981</v>
+      </c>
+      <c r="D636" t="s">
+        <v>1286</v>
       </c>
       <c r="E636" t="s">
         <v>128</v>
       </c>
       <c r="F636" t="s">
-        <v>1347</v>
+        <v>1287</v>
       </c>
       <c r="G636" s="5" t="s">
-        <v>1362</v>
+        <v>1287</v>
       </c>
       <c r="H636" t="s">
-        <v>1325</v>
+        <v>1242</v>
       </c>
       <c r="I636" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J636" t="s">
-        <v>1327</v>
+        <v>1288</v>
+      </c>
+      <c r="K636" t="s">
+        <v>1831</v>
       </c>
       <c r="L636" t="s">
         <v>746</v>
@@ -30889,25 +31321,31 @@
         <v>448</v>
       </c>
       <c r="C637" t="s">
-        <v>1243</v>
+        <v>981</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1289</v>
       </c>
       <c r="E637" t="s">
         <v>128</v>
       </c>
       <c r="F637" t="s">
-        <v>1348</v>
+        <v>1290</v>
       </c>
       <c r="G637" s="5" t="s">
-        <v>1363</v>
+        <v>1290</v>
       </c>
       <c r="H637" t="s">
-        <v>507</v>
+        <v>1242</v>
       </c>
       <c r="I637" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J637" t="s">
-        <v>1334</v>
+        <v>1291</v>
+      </c>
+      <c r="K637" t="s">
+        <v>1832</v>
       </c>
       <c r="L637" t="s">
         <v>746</v>
@@ -30927,25 +31365,31 @@
         <v>448</v>
       </c>
       <c r="C638" t="s">
-        <v>438</v>
+        <v>981</v>
+      </c>
+      <c r="D638" t="s">
+        <v>1292</v>
       </c>
       <c r="E638" t="s">
         <v>128</v>
       </c>
       <c r="F638" t="s">
-        <v>1349</v>
+        <v>1293</v>
       </c>
       <c r="G638" s="5" t="s">
-        <v>1364</v>
+        <v>1293</v>
       </c>
       <c r="H638" t="s">
-        <v>507</v>
+        <v>1242</v>
       </c>
       <c r="I638" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J638" t="s">
-        <v>1335</v>
+        <v>1294</v>
+      </c>
+      <c r="K638" t="s">
+        <v>1833</v>
       </c>
       <c r="L638" t="s">
         <v>746</v>
@@ -30965,25 +31409,31 @@
         <v>448</v>
       </c>
       <c r="C639" t="s">
-        <v>980</v>
+        <v>982</v>
+      </c>
+      <c r="D639" t="s">
+        <v>1295</v>
       </c>
       <c r="E639" t="s">
         <v>128</v>
       </c>
       <c r="F639" t="s">
-        <v>1350</v>
+        <v>1296</v>
       </c>
       <c r="G639" s="5" t="s">
-        <v>1365</v>
+        <v>1296</v>
       </c>
       <c r="H639" t="s">
-        <v>507</v>
+        <v>1242</v>
       </c>
       <c r="I639" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J639" t="s">
-        <v>1336</v>
+        <v>1297</v>
+      </c>
+      <c r="K639" t="s">
+        <v>1834</v>
       </c>
       <c r="L639" t="s">
         <v>746</v>
@@ -31003,25 +31453,31 @@
         <v>448</v>
       </c>
       <c r="C640" t="s">
-        <v>981</v>
+        <v>986</v>
+      </c>
+      <c r="D640" t="s">
+        <v>1298</v>
       </c>
       <c r="E640" t="s">
         <v>128</v>
       </c>
       <c r="F640" t="s">
-        <v>1351</v>
+        <v>1299</v>
       </c>
       <c r="G640" s="5" t="s">
-        <v>1366</v>
+        <v>1299</v>
       </c>
       <c r="H640" t="s">
-        <v>507</v>
+        <v>1242</v>
       </c>
       <c r="I640" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J640" t="s">
-        <v>1337</v>
+        <v>1300</v>
+      </c>
+      <c r="K640" t="s">
+        <v>1835</v>
       </c>
       <c r="L640" t="s">
         <v>746</v>
@@ -31041,16 +31497,16 @@
         <v>448</v>
       </c>
       <c r="C641" t="s">
-        <v>982</v>
+        <v>1191</v>
       </c>
       <c r="E641" t="s">
         <v>128</v>
       </c>
       <c r="F641" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="G641" s="5" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="H641" t="s">
         <v>507</v>
@@ -31059,7 +31515,10 @@
         <v>287</v>
       </c>
       <c r="J641" t="s">
-        <v>1338</v>
+        <v>1324</v>
+      </c>
+      <c r="K641" t="s">
+        <v>1804</v>
       </c>
       <c r="L641" t="s">
         <v>746</v>
@@ -31079,25 +31538,28 @@
         <v>448</v>
       </c>
       <c r="C642" t="s">
-        <v>983</v>
+        <v>1191</v>
       </c>
       <c r="E642" t="s">
         <v>128</v>
       </c>
       <c r="F642" t="s">
-        <v>1353</v>
+        <v>1325</v>
       </c>
       <c r="G642" s="5" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="H642" t="s">
-        <v>507</v>
+        <v>1325</v>
       </c>
       <c r="I642" t="s">
         <v>287</v>
       </c>
       <c r="J642" t="s">
-        <v>1339</v>
+        <v>1326</v>
+      </c>
+      <c r="K642" t="s">
+        <v>1805</v>
       </c>
       <c r="L642" t="s">
         <v>746</v>
@@ -31117,25 +31579,28 @@
         <v>448</v>
       </c>
       <c r="C643" t="s">
-        <v>984</v>
+        <v>1190</v>
       </c>
       <c r="E643" t="s">
         <v>128</v>
       </c>
       <c r="F643" t="s">
-        <v>1354</v>
+        <v>1347</v>
       </c>
       <c r="G643" s="5" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="H643" t="s">
-        <v>507</v>
+        <v>1325</v>
       </c>
       <c r="I643" t="s">
         <v>287</v>
       </c>
       <c r="J643" t="s">
-        <v>1340</v>
+        <v>1327</v>
+      </c>
+      <c r="K643" t="s">
+        <v>1806</v>
       </c>
       <c r="L643" t="s">
         <v>746</v>
@@ -31155,16 +31620,16 @@
         <v>448</v>
       </c>
       <c r="C644" t="s">
-        <v>985</v>
+        <v>1243</v>
       </c>
       <c r="E644" t="s">
         <v>128</v>
       </c>
       <c r="F644" t="s">
-        <v>1355</v>
+        <v>1348</v>
       </c>
       <c r="G644" s="5" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="H644" t="s">
         <v>507</v>
@@ -31173,7 +31638,10 @@
         <v>287</v>
       </c>
       <c r="J644" t="s">
-        <v>1341</v>
+        <v>1334</v>
+      </c>
+      <c r="K644" t="s">
+        <v>1807</v>
       </c>
       <c r="L644" t="s">
         <v>746</v>
@@ -31193,16 +31661,16 @@
         <v>448</v>
       </c>
       <c r="C645" t="s">
-        <v>986</v>
+        <v>438</v>
       </c>
       <c r="E645" t="s">
         <v>128</v>
       </c>
       <c r="F645" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
       <c r="G645" s="5" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="H645" t="s">
         <v>507</v>
@@ -31211,7 +31679,10 @@
         <v>287</v>
       </c>
       <c r="J645" t="s">
-        <v>1342</v>
+        <v>1335</v>
+      </c>
+      <c r="K645" t="s">
+        <v>1808</v>
       </c>
       <c r="L645" t="s">
         <v>746</v>
@@ -31231,16 +31702,16 @@
         <v>448</v>
       </c>
       <c r="C646" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="E646" t="s">
         <v>128</v>
       </c>
       <c r="F646" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
       <c r="G646" s="5" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="H646" t="s">
         <v>507</v>
@@ -31249,7 +31720,10 @@
         <v>287</v>
       </c>
       <c r="J646" t="s">
-        <v>1343</v>
+        <v>1336</v>
+      </c>
+      <c r="K646" t="s">
+        <v>1809</v>
       </c>
       <c r="L646" t="s">
         <v>746</v>
@@ -31269,16 +31743,16 @@
         <v>448</v>
       </c>
       <c r="C647" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="E647" t="s">
         <v>128</v>
       </c>
       <c r="F647" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="G647" s="5" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="H647" t="s">
         <v>507</v>
@@ -31287,7 +31761,10 @@
         <v>287</v>
       </c>
       <c r="J647" t="s">
-        <v>1344</v>
+        <v>1337</v>
+      </c>
+      <c r="K647" t="s">
+        <v>1810</v>
       </c>
       <c r="L647" t="s">
         <v>746</v>
@@ -31307,16 +31784,16 @@
         <v>448</v>
       </c>
       <c r="C648" t="s">
-        <v>471</v>
+        <v>982</v>
       </c>
       <c r="E648" t="s">
         <v>128</v>
       </c>
       <c r="F648" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
       <c r="G648" s="5" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="H648" t="s">
         <v>507</v>
@@ -31325,7 +31802,10 @@
         <v>287</v>
       </c>
       <c r="J648" t="s">
-        <v>1345</v>
+        <v>1338</v>
+      </c>
+      <c r="K648" t="s">
+        <v>1811</v>
       </c>
       <c r="L648" t="s">
         <v>746</v>
@@ -31345,28 +31825,28 @@
         <v>448</v>
       </c>
       <c r="C649" t="s">
-        <v>1191</v>
+        <v>983</v>
       </c>
       <c r="E649" t="s">
         <v>128</v>
       </c>
       <c r="F649" t="s">
-        <v>1328</v>
+        <v>1353</v>
       </c>
       <c r="G649" s="5" t="s">
-        <v>1328</v>
+        <v>1368</v>
       </c>
       <c r="H649" t="s">
-        <v>1328</v>
+        <v>507</v>
       </c>
       <c r="I649" t="s">
-        <v>1329</v>
+        <v>287</v>
       </c>
       <c r="J649" t="s">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="K649" t="s">
-        <v>1557</v>
+        <v>1812</v>
       </c>
       <c r="L649" t="s">
         <v>746</v>
@@ -31386,31 +31866,28 @@
         <v>448</v>
       </c>
       <c r="C650" t="s">
-        <v>986</v>
-      </c>
-      <c r="D650" t="s">
-        <v>1331</v>
+        <v>984</v>
       </c>
       <c r="E650" t="s">
         <v>128</v>
       </c>
       <c r="F650" t="s">
-        <v>1332</v>
+        <v>1354</v>
       </c>
       <c r="G650" s="5" t="s">
-        <v>1332</v>
+        <v>1369</v>
       </c>
       <c r="H650" t="s">
-        <v>1328</v>
+        <v>507</v>
       </c>
       <c r="I650" t="s">
-        <v>1329</v>
+        <v>287</v>
       </c>
       <c r="J650" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="K650" t="s">
-        <v>1558</v>
+        <v>1813</v>
       </c>
       <c r="L650" t="s">
         <v>746</v>
@@ -31430,28 +31907,28 @@
         <v>448</v>
       </c>
       <c r="C651" t="s">
-        <v>1191</v>
+        <v>985</v>
       </c>
       <c r="E651" t="s">
         <v>128</v>
       </c>
       <c r="F651" t="s">
-        <v>1388</v>
+        <v>1355</v>
       </c>
       <c r="G651" s="5" t="s">
-        <v>1389</v>
+        <v>1370</v>
       </c>
       <c r="H651" t="s">
-        <v>1232</v>
+        <v>507</v>
       </c>
       <c r="I651" t="s">
-        <v>817</v>
+        <v>287</v>
       </c>
       <c r="J651" t="s">
-        <v>1392</v>
+        <v>1341</v>
       </c>
       <c r="K651" t="s">
-        <v>1549</v>
+        <v>1814</v>
       </c>
       <c r="L651" t="s">
         <v>746</v>
@@ -31471,28 +31948,28 @@
         <v>448</v>
       </c>
       <c r="C652" t="s">
-        <v>1190</v>
+        <v>986</v>
       </c>
       <c r="E652" t="s">
         <v>128</v>
       </c>
       <c r="F652" t="s">
-        <v>1232</v>
+        <v>1356</v>
       </c>
       <c r="G652" s="5" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="H652" t="s">
-        <v>1232</v>
+        <v>507</v>
       </c>
       <c r="I652" t="s">
-        <v>817</v>
+        <v>287</v>
       </c>
       <c r="J652" t="s">
-        <v>1391</v>
+        <v>1342</v>
       </c>
       <c r="K652" t="s">
-        <v>1550</v>
+        <v>1815</v>
       </c>
       <c r="L652" t="s">
         <v>746</v>
@@ -31512,28 +31989,28 @@
         <v>448</v>
       </c>
       <c r="C653" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E653" t="s">
         <v>128</v>
       </c>
       <c r="F653" t="s">
-        <v>1393</v>
+        <v>1357</v>
       </c>
       <c r="G653" s="5" t="s">
-        <v>1393</v>
+        <v>1372</v>
       </c>
       <c r="H653" t="s">
-        <v>1232</v>
+        <v>507</v>
       </c>
       <c r="I653" t="s">
-        <v>817</v>
+        <v>287</v>
       </c>
       <c r="J653" t="s">
-        <v>1394</v>
+        <v>1343</v>
       </c>
       <c r="K653" t="s">
-        <v>1551</v>
+        <v>1816</v>
       </c>
       <c r="L653" t="s">
         <v>746</v>
@@ -31553,28 +32030,28 @@
         <v>448</v>
       </c>
       <c r="C654" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E654" t="s">
         <v>128</v>
       </c>
       <c r="F654" t="s">
-        <v>1395</v>
+        <v>1358</v>
       </c>
       <c r="G654" s="5" t="s">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="H654" t="s">
-        <v>1232</v>
+        <v>507</v>
       </c>
       <c r="I654" t="s">
-        <v>817</v>
+        <v>287</v>
       </c>
       <c r="J654" t="s">
-        <v>1396</v>
+        <v>1344</v>
       </c>
       <c r="K654" t="s">
-        <v>1552</v>
+        <v>1817</v>
       </c>
       <c r="L654" t="s">
         <v>746</v>
@@ -31594,28 +32071,28 @@
         <v>448</v>
       </c>
       <c r="C655" t="s">
-        <v>985</v>
+        <v>471</v>
       </c>
       <c r="E655" t="s">
         <v>128</v>
       </c>
       <c r="F655" t="s">
-        <v>1056</v>
+        <v>1359</v>
       </c>
       <c r="G655" s="5" t="s">
-        <v>1056</v>
+        <v>1374</v>
       </c>
       <c r="H655" t="s">
-        <v>1232</v>
+        <v>507</v>
       </c>
       <c r="I655" t="s">
-        <v>817</v>
+        <v>287</v>
       </c>
       <c r="J655" t="s">
-        <v>1397</v>
+        <v>1345</v>
       </c>
       <c r="K655" t="s">
-        <v>1553</v>
+        <v>1818</v>
       </c>
       <c r="L655" t="s">
         <v>746</v>
@@ -31635,28 +32112,28 @@
         <v>448</v>
       </c>
       <c r="C656" t="s">
-        <v>984</v>
+        <v>1191</v>
       </c>
       <c r="E656" t="s">
         <v>128</v>
       </c>
       <c r="F656" t="s">
-        <v>1398</v>
+        <v>1328</v>
       </c>
       <c r="G656" s="5" t="s">
-        <v>1398</v>
+        <v>1328</v>
       </c>
       <c r="H656" t="s">
-        <v>1232</v>
+        <v>1328</v>
       </c>
       <c r="I656" t="s">
-        <v>817</v>
+        <v>1329</v>
       </c>
       <c r="J656" t="s">
-        <v>1399</v>
+        <v>1330</v>
       </c>
       <c r="K656" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="L656" t="s">
         <v>746</v>
@@ -31676,28 +32153,31 @@
         <v>448</v>
       </c>
       <c r="C657" t="s">
-        <v>981</v>
+        <v>986</v>
+      </c>
+      <c r="D657" t="s">
+        <v>1331</v>
       </c>
       <c r="E657" t="s">
         <v>128</v>
       </c>
       <c r="F657" t="s">
-        <v>1400</v>
+        <v>1332</v>
       </c>
       <c r="G657" s="5" t="s">
-        <v>1400</v>
+        <v>1332</v>
       </c>
       <c r="H657" t="s">
-        <v>1090</v>
+        <v>1328</v>
       </c>
       <c r="I657" t="s">
-        <v>817</v>
+        <v>1329</v>
       </c>
       <c r="J657" t="s">
-        <v>1401</v>
+        <v>1333</v>
       </c>
       <c r="K657" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="L657" t="s">
         <v>746</v>
@@ -31717,28 +32197,28 @@
         <v>448</v>
       </c>
       <c r="C658" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E658" t="s">
         <v>128</v>
       </c>
       <c r="F658" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
       <c r="G658" s="5" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
       <c r="H658" t="s">
-        <v>1060</v>
+        <v>1232</v>
       </c>
       <c r="I658" t="s">
         <v>817</v>
       </c>
       <c r="J658" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="K658" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="L658" t="s">
         <v>746</v>
@@ -31747,6 +32227,363 @@
         <v>390</v>
       </c>
       <c r="N658" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="659" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A659">
+        <v>658</v>
+      </c>
+      <c r="B659" t="s">
+        <v>448</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E659" t="s">
+        <v>128</v>
+      </c>
+      <c r="F659" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G659" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H659" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I659" t="s">
+        <v>817</v>
+      </c>
+      <c r="J659" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K659" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L659" t="s">
+        <v>746</v>
+      </c>
+      <c r="M659" t="s">
+        <v>390</v>
+      </c>
+      <c r="N659" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="660" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A660">
+        <v>659</v>
+      </c>
+      <c r="B660" t="s">
+        <v>448</v>
+      </c>
+      <c r="C660" t="s">
+        <v>985</v>
+      </c>
+      <c r="E660" t="s">
+        <v>128</v>
+      </c>
+      <c r="F660" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G660" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H660" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I660" t="s">
+        <v>817</v>
+      </c>
+      <c r="J660" t="s">
+        <v>1394</v>
+      </c>
+      <c r="K660" t="s">
+        <v>1551</v>
+      </c>
+      <c r="L660" t="s">
+        <v>746</v>
+      </c>
+      <c r="M660" t="s">
+        <v>390</v>
+      </c>
+      <c r="N660" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="661" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A661">
+        <v>660</v>
+      </c>
+      <c r="B661" t="s">
+        <v>448</v>
+      </c>
+      <c r="C661" t="s">
+        <v>986</v>
+      </c>
+      <c r="E661" t="s">
+        <v>128</v>
+      </c>
+      <c r="F661" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G661" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H661" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I661" t="s">
+        <v>817</v>
+      </c>
+      <c r="J661" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K661" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L661" t="s">
+        <v>746</v>
+      </c>
+      <c r="M661" t="s">
+        <v>390</v>
+      </c>
+      <c r="N661" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="662" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A662">
+        <v>661</v>
+      </c>
+      <c r="B662" t="s">
+        <v>448</v>
+      </c>
+      <c r="C662" t="s">
+        <v>985</v>
+      </c>
+      <c r="E662" t="s">
+        <v>128</v>
+      </c>
+      <c r="F662" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G662" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H662" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I662" t="s">
+        <v>817</v>
+      </c>
+      <c r="J662" t="s">
+        <v>1397</v>
+      </c>
+      <c r="K662" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L662" t="s">
+        <v>746</v>
+      </c>
+      <c r="M662" t="s">
+        <v>390</v>
+      </c>
+      <c r="N662" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="663" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A663">
+        <v>662</v>
+      </c>
+      <c r="B663" t="s">
+        <v>448</v>
+      </c>
+      <c r="C663" t="s">
+        <v>984</v>
+      </c>
+      <c r="E663" t="s">
+        <v>128</v>
+      </c>
+      <c r="F663" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G663" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H663" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I663" t="s">
+        <v>817</v>
+      </c>
+      <c r="J663" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K663" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L663" t="s">
+        <v>746</v>
+      </c>
+      <c r="M663" t="s">
+        <v>390</v>
+      </c>
+      <c r="N663" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="664" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A664">
+        <v>663</v>
+      </c>
+      <c r="B664" t="s">
+        <v>448</v>
+      </c>
+      <c r="C664" t="s">
+        <v>981</v>
+      </c>
+      <c r="E664" t="s">
+        <v>128</v>
+      </c>
+      <c r="F664" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G664" s="5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H664" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I664" t="s">
+        <v>817</v>
+      </c>
+      <c r="J664" t="s">
+        <v>1401</v>
+      </c>
+      <c r="K664" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L664" t="s">
+        <v>746</v>
+      </c>
+      <c r="M664" t="s">
+        <v>390</v>
+      </c>
+      <c r="N664" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="665" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A665">
+        <v>664</v>
+      </c>
+      <c r="B665" t="s">
+        <v>448</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E665" t="s">
+        <v>128</v>
+      </c>
+      <c r="F665" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G665" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H665" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I665" t="s">
+        <v>817</v>
+      </c>
+      <c r="J665" t="s">
+        <v>1404</v>
+      </c>
+      <c r="K665" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L665" t="s">
+        <v>746</v>
+      </c>
+      <c r="M665" t="s">
+        <v>390</v>
+      </c>
+      <c r="N665" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="666" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B666" t="s">
+        <v>448</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E666" t="s">
+        <v>128</v>
+      </c>
+      <c r="F666" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G666" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H666" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I666" t="s">
+        <v>818</v>
+      </c>
+      <c r="J666" t="s">
+        <v>1858</v>
+      </c>
+      <c r="K666" t="s">
+        <v>1859</v>
+      </c>
+      <c r="L666" t="s">
+        <v>746</v>
+      </c>
+      <c r="M666" t="s">
+        <v>390</v>
+      </c>
+      <c r="N666" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E667" t="s">
+        <v>128</v>
+      </c>
+      <c r="F667" t="s">
+        <v>1862</v>
+      </c>
+      <c r="G667" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H667" t="s">
+        <v>1770</v>
+      </c>
+      <c r="I667" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J667" t="s">
+        <v>1860</v>
+      </c>
+      <c r="K667" t="s">
+        <v>1861</v>
+      </c>
+      <c r="L667" t="s">
+        <v>746</v>
+      </c>
+      <c r="M667" t="s">
+        <v>390</v>
+      </c>
+      <c r="N667" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -31754,7 +32591,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G634:G636 G637:G648" numberStoredAsText="1"/>
+    <ignoredError sqref="G641:G643 G644:G655" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5E2D8B-5E0B-4B16-8628-B683E39352C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842FA50F-F653-4C86-9584-B48EAE816274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9279" uniqueCount="1863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9617" uniqueCount="1954">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -5634,6 +5634,279 @@
   </si>
   <si>
     <t>NIFTY</t>
+  </si>
+  <si>
+    <t>Foreign Exchange</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>JXY</t>
+  </si>
+  <si>
+    <t>EXY</t>
+  </si>
+  <si>
+    <t>BXY</t>
+  </si>
+  <si>
+    <t>SXY</t>
+  </si>
+  <si>
+    <t>CXY</t>
+  </si>
+  <si>
+    <t>AXY</t>
+  </si>
+  <si>
+    <t>ZXY</t>
+  </si>
+  <si>
+    <t>British Pound Currency Index</t>
+  </si>
+  <si>
+    <t>Swiss Franc Currency Index</t>
+  </si>
+  <si>
+    <t>Canadian Dollar Currency Index</t>
+  </si>
+  <si>
+    <t>U.S. Dollar Currency Index</t>
+  </si>
+  <si>
+    <t>Japanese Yen Currency Index</t>
+  </si>
+  <si>
+    <t>Euro Currency Index</t>
+  </si>
+  <si>
+    <t>Australian Dollar Currency Index</t>
+  </si>
+  <si>
+    <t>New Zealand Dollar Currency Index</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>유로 지수</t>
+  </si>
+  <si>
+    <t>영국 파운드화 지수</t>
+  </si>
+  <si>
+    <t>미국 달러화 지수</t>
+  </si>
+  <si>
+    <t>일본 엔화 지수</t>
+  </si>
+  <si>
+    <t>스위스 프랑화 지수</t>
+  </si>
+  <si>
+    <t>캐나다 달러화 지수</t>
+  </si>
+  <si>
+    <t>호주 달러화 지수</t>
+  </si>
+  <si>
+    <t>뉴질랜드 달러화 지수</t>
+  </si>
+  <si>
+    <t>America</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>USDKRW</t>
+  </si>
+  <si>
+    <t>JPYKRW</t>
+  </si>
+  <si>
+    <t>EURKRW</t>
+  </si>
+  <si>
+    <t>GBPKRW</t>
+  </si>
+  <si>
+    <t>CNYKRW</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>KRWJPY</t>
+  </si>
+  <si>
+    <t>EURJPY</t>
+  </si>
+  <si>
+    <t>CNYJPY</t>
+  </si>
+  <si>
+    <t>GBPJPY</t>
+  </si>
+  <si>
+    <t>KRWUSD</t>
+  </si>
+  <si>
+    <t>JPYUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>CNYUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>KRWEUR</t>
+  </si>
+  <si>
+    <t>JPYEUR</t>
+  </si>
+  <si>
+    <t>USDEUR</t>
+  </si>
+  <si>
+    <t>GBPEUR</t>
+  </si>
+  <si>
+    <t>CNYEUR</t>
+  </si>
+  <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>달러/원</t>
+  </si>
+  <si>
+    <t>엔/원</t>
+  </si>
+  <si>
+    <t>유로/원</t>
+  </si>
+  <si>
+    <t>파운드/원</t>
+  </si>
+  <si>
+    <t>위안/원</t>
+  </si>
+  <si>
+    <t>달러/엔</t>
+  </si>
+  <si>
+    <t>원/엔</t>
+  </si>
+  <si>
+    <t>유로/엔</t>
+  </si>
+  <si>
+    <t>파운드/엔</t>
+  </si>
+  <si>
+    <t>위안/엔</t>
+  </si>
+  <si>
+    <t>원/달러</t>
+  </si>
+  <si>
+    <t>엔/달러</t>
+  </si>
+  <si>
+    <t>유로/달러</t>
+  </si>
+  <si>
+    <t>위안/달러</t>
+  </si>
+  <si>
+    <t>파운드/달러</t>
+  </si>
+  <si>
+    <t>원/유로</t>
+  </si>
+  <si>
+    <t>엔/유로</t>
+  </si>
+  <si>
+    <t>달러/유로</t>
+  </si>
+  <si>
+    <t>파운드/유로</t>
+  </si>
+  <si>
+    <t>위안/유로</t>
+  </si>
+  <si>
+    <t>US Dollar / South Korean Won</t>
+  </si>
+  <si>
+    <t>Japanese Yen / South Korean Won</t>
+  </si>
+  <si>
+    <t>Euro / South Korean Won</t>
+  </si>
+  <si>
+    <t>British Pound / South Korean Won</t>
+  </si>
+  <si>
+    <t>Chinese Yuan / South Korean Won</t>
+  </si>
+  <si>
+    <t>US Dollar / Japanese Yen</t>
+  </si>
+  <si>
+    <t>South Korean Won / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Euro / Japanese Yen</t>
+  </si>
+  <si>
+    <t>British Pound / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Chinese Yuan / Japanese Yen</t>
+  </si>
+  <si>
+    <t>South Korean Won / US Dollar</t>
+  </si>
+  <si>
+    <t>Japanese Yen / US Dollar</t>
+  </si>
+  <si>
+    <t>Euro / US Dollar</t>
+  </si>
+  <si>
+    <t>Chinese Yuan / US Dollar</t>
+  </si>
+  <si>
+    <t>British Pound / US Dollar</t>
+  </si>
+  <si>
+    <t>South Korean Won / Euro</t>
+  </si>
+  <si>
+    <t>Japanese Yen / Euro</t>
+  </si>
+  <si>
+    <t>US Dollar / Euro</t>
+  </si>
+  <si>
+    <t>British Pound / Euro</t>
+  </si>
+  <si>
+    <t>Chinese Yuan / Euro</t>
+  </si>
+  <si>
+    <t>FX_IDC</t>
   </si>
 </sst>
 </file>
@@ -5978,10 +6251,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O667"/>
+  <dimension ref="A1:O695"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -32518,6 +32791,9 @@
       </c>
     </row>
     <row r="666" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A666">
+        <v>665</v>
+      </c>
       <c r="B666" t="s">
         <v>448</v>
       </c>
@@ -32556,6 +32832,15 @@
       </c>
     </row>
     <row r="667" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A667">
+        <v>666</v>
+      </c>
+      <c r="B667" t="s">
+        <v>448</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1190</v>
+      </c>
       <c r="E667" t="s">
         <v>128</v>
       </c>
@@ -32584,6 +32869,1154 @@
         <v>390</v>
       </c>
       <c r="N667" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A668">
+        <v>667</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E668" t="s">
+        <v>128</v>
+      </c>
+      <c r="F668" s="5" t="s">
+        <v>1864</v>
+      </c>
+      <c r="G668" s="5" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H668" t="s">
+        <v>78</v>
+      </c>
+      <c r="I668" t="s">
+        <v>817</v>
+      </c>
+      <c r="J668" t="s">
+        <v>1875</v>
+      </c>
+      <c r="K668" t="s">
+        <v>1883</v>
+      </c>
+      <c r="L668" t="s">
+        <v>746</v>
+      </c>
+      <c r="M668" t="s">
+        <v>390</v>
+      </c>
+      <c r="N668" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A669">
+        <v>668</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E669" t="s">
+        <v>128</v>
+      </c>
+      <c r="F669" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G669" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H669" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I669" t="s">
+        <v>133</v>
+      </c>
+      <c r="J669" t="s">
+        <v>1876</v>
+      </c>
+      <c r="K669" t="s">
+        <v>1884</v>
+      </c>
+      <c r="L669" t="s">
+        <v>746</v>
+      </c>
+      <c r="M669" t="s">
+        <v>390</v>
+      </c>
+      <c r="N669" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A670">
+        <v>669</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C670" t="s">
+        <v>134</v>
+      </c>
+      <c r="E670" t="s">
+        <v>128</v>
+      </c>
+      <c r="F670" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G670" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H670" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I670" t="s">
+        <v>134</v>
+      </c>
+      <c r="J670" t="s">
+        <v>1877</v>
+      </c>
+      <c r="K670" t="s">
+        <v>1881</v>
+      </c>
+      <c r="L670" t="s">
+        <v>746</v>
+      </c>
+      <c r="M670" t="s">
+        <v>390</v>
+      </c>
+      <c r="N670" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="671" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A671">
+        <v>670</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C671" t="s">
+        <v>134</v>
+      </c>
+      <c r="E671" t="s">
+        <v>128</v>
+      </c>
+      <c r="F671" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G671" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H671" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I671" t="s">
+        <v>818</v>
+      </c>
+      <c r="J671" t="s">
+        <v>1872</v>
+      </c>
+      <c r="K671" t="s">
+        <v>1882</v>
+      </c>
+      <c r="L671" t="s">
+        <v>746</v>
+      </c>
+      <c r="M671" t="s">
+        <v>390</v>
+      </c>
+      <c r="N671" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="672" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A672">
+        <v>671</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C672" t="s">
+        <v>134</v>
+      </c>
+      <c r="E672" t="s">
+        <v>128</v>
+      </c>
+      <c r="F672" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G672" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H672" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I672" t="s">
+        <v>1781</v>
+      </c>
+      <c r="J672" t="s">
+        <v>1873</v>
+      </c>
+      <c r="K672" t="s">
+        <v>1885</v>
+      </c>
+      <c r="L672" t="s">
+        <v>746</v>
+      </c>
+      <c r="M672" t="s">
+        <v>390</v>
+      </c>
+      <c r="N672" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="673" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A673">
+        <v>672</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E673" t="s">
+        <v>128</v>
+      </c>
+      <c r="F673" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G673" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H673" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I673" t="s">
+        <v>1580</v>
+      </c>
+      <c r="J673" t="s">
+        <v>1874</v>
+      </c>
+      <c r="K673" t="s">
+        <v>1886</v>
+      </c>
+      <c r="L673" t="s">
+        <v>746</v>
+      </c>
+      <c r="M673" t="s">
+        <v>390</v>
+      </c>
+      <c r="N673" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="674" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A674">
+        <v>673</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E674" t="s">
+        <v>128</v>
+      </c>
+      <c r="F674" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G674" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H674" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I674" t="s">
+        <v>1880</v>
+      </c>
+      <c r="J674" t="s">
+        <v>1878</v>
+      </c>
+      <c r="K674" t="s">
+        <v>1887</v>
+      </c>
+      <c r="L674" t="s">
+        <v>746</v>
+      </c>
+      <c r="M674" t="s">
+        <v>390</v>
+      </c>
+      <c r="N674" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="675" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A675">
+        <v>674</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E675" t="s">
+        <v>128</v>
+      </c>
+      <c r="F675" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="G675" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H675" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I675" t="s">
+        <v>1438</v>
+      </c>
+      <c r="J675" t="s">
+        <v>1879</v>
+      </c>
+      <c r="K675" t="s">
+        <v>1888</v>
+      </c>
+      <c r="L675" t="s">
+        <v>746</v>
+      </c>
+      <c r="M675" t="s">
+        <v>390</v>
+      </c>
+      <c r="N675" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="676" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A676">
+        <v>675</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E676" t="s">
+        <v>126</v>
+      </c>
+      <c r="F676" t="s">
+        <v>1892</v>
+      </c>
+      <c r="G676" t="s">
+        <v>1892</v>
+      </c>
+      <c r="H676" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I676" t="s">
+        <v>472</v>
+      </c>
+      <c r="J676" t="s">
+        <v>1933</v>
+      </c>
+      <c r="K676" t="s">
+        <v>1913</v>
+      </c>
+      <c r="L676" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M676" t="s">
+        <v>390</v>
+      </c>
+      <c r="N676" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="677" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A677">
+        <v>676</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E677" t="s">
+        <v>126</v>
+      </c>
+      <c r="F677" s="5" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G677" s="5" t="s">
+        <v>1893</v>
+      </c>
+      <c r="H677" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I677" t="s">
+        <v>472</v>
+      </c>
+      <c r="J677" t="s">
+        <v>1934</v>
+      </c>
+      <c r="K677" t="s">
+        <v>1914</v>
+      </c>
+      <c r="L677" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M677" t="s">
+        <v>390</v>
+      </c>
+      <c r="N677" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="678" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A678">
+        <v>677</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E678" t="s">
+        <v>126</v>
+      </c>
+      <c r="F678" s="5" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G678" s="5" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H678" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I678" t="s">
+        <v>472</v>
+      </c>
+      <c r="J678" t="s">
+        <v>1935</v>
+      </c>
+      <c r="K678" t="s">
+        <v>1915</v>
+      </c>
+      <c r="L678" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M678" t="s">
+        <v>390</v>
+      </c>
+      <c r="N678" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="679" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A679">
+        <v>678</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E679" t="s">
+        <v>126</v>
+      </c>
+      <c r="F679" s="5" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G679" s="5" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H679" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I679" t="s">
+        <v>472</v>
+      </c>
+      <c r="J679" t="s">
+        <v>1936</v>
+      </c>
+      <c r="K679" t="s">
+        <v>1916</v>
+      </c>
+      <c r="L679" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M679" t="s">
+        <v>390</v>
+      </c>
+      <c r="N679" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="680" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A680">
+        <v>679</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E680" t="s">
+        <v>126</v>
+      </c>
+      <c r="F680" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G680" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H680" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I680" t="s">
+        <v>472</v>
+      </c>
+      <c r="J680" t="s">
+        <v>1937</v>
+      </c>
+      <c r="K680" t="s">
+        <v>1917</v>
+      </c>
+      <c r="L680" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M680" t="s">
+        <v>390</v>
+      </c>
+      <c r="N680" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="681" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A681">
+        <v>680</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E681" t="s">
+        <v>126</v>
+      </c>
+      <c r="F681" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G681" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="H681" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I681" t="s">
+        <v>133</v>
+      </c>
+      <c r="J681" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K681" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L681" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M681" t="s">
+        <v>390</v>
+      </c>
+      <c r="N681" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="682" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A682">
+        <v>681</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E682" t="s">
+        <v>126</v>
+      </c>
+      <c r="F682" s="5" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G682" s="5" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H682" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I682" t="s">
+        <v>133</v>
+      </c>
+      <c r="J682" t="s">
+        <v>1939</v>
+      </c>
+      <c r="K682" t="s">
+        <v>1919</v>
+      </c>
+      <c r="L682" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M682" t="s">
+        <v>390</v>
+      </c>
+      <c r="N682" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="683" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A683">
+        <v>682</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E683" t="s">
+        <v>126</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H683" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I683" t="s">
+        <v>133</v>
+      </c>
+      <c r="J683" t="s">
+        <v>1940</v>
+      </c>
+      <c r="K683" t="s">
+        <v>1920</v>
+      </c>
+      <c r="L683" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M683" t="s">
+        <v>390</v>
+      </c>
+      <c r="N683" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="684" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A684">
+        <v>683</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E684" t="s">
+        <v>126</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="H684" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I684" t="s">
+        <v>133</v>
+      </c>
+      <c r="J684" t="s">
+        <v>1941</v>
+      </c>
+      <c r="K684" t="s">
+        <v>1921</v>
+      </c>
+      <c r="L684" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M684" t="s">
+        <v>390</v>
+      </c>
+      <c r="N684" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="685" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A685">
+        <v>684</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E685" t="s">
+        <v>126</v>
+      </c>
+      <c r="F685" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G685" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H685" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I685" t="s">
+        <v>133</v>
+      </c>
+      <c r="J685" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K685" t="s">
+        <v>1922</v>
+      </c>
+      <c r="L685" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M685" t="s">
+        <v>390</v>
+      </c>
+      <c r="N685" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="686" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A686">
+        <v>685</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E686" t="s">
+        <v>126</v>
+      </c>
+      <c r="F686" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G686" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H686" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I686" t="s">
+        <v>817</v>
+      </c>
+      <c r="J686" t="s">
+        <v>1943</v>
+      </c>
+      <c r="K686" t="s">
+        <v>1923</v>
+      </c>
+      <c r="L686" t="s">
+        <v>712</v>
+      </c>
+      <c r="M686" t="s">
+        <v>390</v>
+      </c>
+      <c r="N686" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="687" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A687">
+        <v>686</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E687" t="s">
+        <v>126</v>
+      </c>
+      <c r="F687" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G687" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H687" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I687" t="s">
+        <v>817</v>
+      </c>
+      <c r="J687" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K687" t="s">
+        <v>1924</v>
+      </c>
+      <c r="L687" t="s">
+        <v>712</v>
+      </c>
+      <c r="M687" t="s">
+        <v>390</v>
+      </c>
+      <c r="N687" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="688" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A688">
+        <v>687</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E688" t="s">
+        <v>126</v>
+      </c>
+      <c r="F688" s="5" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G688" s="5" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H688" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I688" t="s">
+        <v>817</v>
+      </c>
+      <c r="J688" t="s">
+        <v>1945</v>
+      </c>
+      <c r="K688" t="s">
+        <v>1925</v>
+      </c>
+      <c r="L688" t="s">
+        <v>712</v>
+      </c>
+      <c r="M688" t="s">
+        <v>390</v>
+      </c>
+      <c r="N688" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="689" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A689">
+        <v>688</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E689" t="s">
+        <v>126</v>
+      </c>
+      <c r="F689" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G689" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="H689" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I689" t="s">
+        <v>817</v>
+      </c>
+      <c r="J689" t="s">
+        <v>1946</v>
+      </c>
+      <c r="K689" t="s">
+        <v>1926</v>
+      </c>
+      <c r="L689" t="s">
+        <v>712</v>
+      </c>
+      <c r="M689" t="s">
+        <v>390</v>
+      </c>
+      <c r="N689" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="690" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A690">
+        <v>689</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E690" t="s">
+        <v>126</v>
+      </c>
+      <c r="F690" s="5" t="s">
+        <v>1906</v>
+      </c>
+      <c r="G690" s="5" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H690" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I690" t="s">
+        <v>817</v>
+      </c>
+      <c r="J690" t="s">
+        <v>1947</v>
+      </c>
+      <c r="K690" t="s">
+        <v>1927</v>
+      </c>
+      <c r="L690" t="s">
+        <v>712</v>
+      </c>
+      <c r="M690" t="s">
+        <v>390</v>
+      </c>
+      <c r="N690" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="691" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A691">
+        <v>690</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C691" t="s">
+        <v>134</v>
+      </c>
+      <c r="E691" t="s">
+        <v>126</v>
+      </c>
+      <c r="F691" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G691" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H691" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I691" t="s">
+        <v>134</v>
+      </c>
+      <c r="J691" t="s">
+        <v>1948</v>
+      </c>
+      <c r="K691" t="s">
+        <v>1928</v>
+      </c>
+      <c r="L691" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M691" t="s">
+        <v>390</v>
+      </c>
+      <c r="N691" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="692" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A692">
+        <v>691</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C692" t="s">
+        <v>134</v>
+      </c>
+      <c r="E692" t="s">
+        <v>126</v>
+      </c>
+      <c r="F692" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G692" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H692" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I692" t="s">
+        <v>134</v>
+      </c>
+      <c r="J692" t="s">
+        <v>1949</v>
+      </c>
+      <c r="K692" t="s">
+        <v>1929</v>
+      </c>
+      <c r="L692" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M692" t="s">
+        <v>390</v>
+      </c>
+      <c r="N692" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="693" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A693">
+        <v>692</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C693" t="s">
+        <v>134</v>
+      </c>
+      <c r="E693" t="s">
+        <v>126</v>
+      </c>
+      <c r="F693" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G693" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H693" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I693" t="s">
+        <v>134</v>
+      </c>
+      <c r="J693" t="s">
+        <v>1950</v>
+      </c>
+      <c r="K693" t="s">
+        <v>1930</v>
+      </c>
+      <c r="L693" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M693" t="s">
+        <v>390</v>
+      </c>
+      <c r="N693" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="694" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A694">
+        <v>693</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C694" t="s">
+        <v>134</v>
+      </c>
+      <c r="E694" t="s">
+        <v>126</v>
+      </c>
+      <c r="F694" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G694" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H694" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I694" t="s">
+        <v>134</v>
+      </c>
+      <c r="J694" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K694" t="s">
+        <v>1931</v>
+      </c>
+      <c r="L694" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M694" t="s">
+        <v>390</v>
+      </c>
+      <c r="N694" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="695" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A695">
+        <v>694</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C695" t="s">
+        <v>134</v>
+      </c>
+      <c r="E695" t="s">
+        <v>126</v>
+      </c>
+      <c r="F695" s="5" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G695" s="5" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H695" t="s">
+        <v>1953</v>
+      </c>
+      <c r="I695" t="s">
+        <v>134</v>
+      </c>
+      <c r="J695" t="s">
+        <v>1952</v>
+      </c>
+      <c r="K695" t="s">
+        <v>1932</v>
+      </c>
+      <c r="L695" t="s">
+        <v>1585</v>
+      </c>
+      <c r="M695" t="s">
+        <v>390</v>
+      </c>
+      <c r="N695" t="s">
         <v>1047</v>
       </c>
     </row>

--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49CAA10-A7B9-4400-934C-3FD9D58B4D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A32188C-A82E-45E7-AB01-F9C0069EABEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10919" uniqueCount="2331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10949" uniqueCount="2339">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -7038,6 +7038,30 @@
   </si>
   <si>
     <t>Korea Treasury Bond 50 Year Maturity Yield</t>
+  </si>
+  <si>
+    <t>MARGDEBT</t>
+  </si>
+  <si>
+    <t>CASHCRDT</t>
+  </si>
+  <si>
+    <t>MARGCRDT</t>
+  </si>
+  <si>
+    <t>FINRA</t>
+  </si>
+  <si>
+    <t>Debit Balances in Customers' Securities Margin Accounts</t>
+  </si>
+  <si>
+    <t>Free Credit Balances in Customers' Cash Accounts</t>
+  </si>
+  <si>
+    <t>Free Credit Balances in Customers' Securities Margin Accounts</t>
+  </si>
+  <si>
+    <t>https://www.finra.org/rules-guidance/key-topics/margin-accounts/margin-statistics</t>
   </si>
 </sst>
 </file>
@@ -7049,7 +7073,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7084,6 +7108,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7108,12 +7146,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -7129,11 +7168,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7411,25 +7455,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O854"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O857"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" style="6" customWidth="1"/>
     <col min="10" max="10" width="43" style="6" customWidth="1"/>
-    <col min="11" max="11" width="31.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.77734375" style="6" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.77734375" style="6"/>
+    <col min="11" max="11" width="31.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.81640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -7476,7 +7520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7520,7 +7564,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7564,7 +7608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7608,7 +7652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7652,7 +7696,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7696,7 +7740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7740,7 +7784,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7784,7 +7828,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7828,7 +7872,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7872,7 +7916,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7913,7 +7957,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7957,7 +8001,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8001,7 +8045,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8045,7 +8089,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8089,7 +8133,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8133,7 +8177,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8174,7 +8218,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8215,7 +8259,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8259,7 +8303,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8300,7 +8344,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8344,7 +8388,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8388,7 +8432,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8432,7 +8476,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8476,7 +8520,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8520,7 +8564,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8564,7 +8608,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8605,7 +8649,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8646,7 +8690,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8690,7 +8734,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8734,7 +8778,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8778,7 +8822,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8819,7 +8863,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8863,7 +8907,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8907,7 +8951,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8951,7 +8995,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8995,7 +9039,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9039,7 +9083,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9083,7 +9127,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9124,7 +9168,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9165,7 +9209,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9209,7 +9253,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9250,7 +9294,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9294,7 +9338,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9338,7 +9382,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -9382,7 +9426,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -9426,7 +9470,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -9470,7 +9514,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -9514,7 +9558,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -9558,7 +9602,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -9599,7 +9643,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -9643,7 +9687,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -9684,7 +9728,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -9728,7 +9772,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -9769,7 +9813,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -9810,7 +9854,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -9851,7 +9895,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9892,7 +9936,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9933,7 +9977,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9977,7 +10021,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -10015,7 +10059,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -10053,7 +10097,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -10091,7 +10135,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -10129,7 +10173,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -10167,7 +10211,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -10205,7 +10249,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -10243,7 +10287,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -10281,7 +10325,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -10322,7 +10366,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -10360,7 +10404,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -10401,7 +10445,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -10442,7 +10486,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -10483,7 +10527,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -10521,7 +10565,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10562,7 +10606,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10603,7 +10647,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10641,7 +10685,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10682,7 +10726,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10723,7 +10767,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10761,7 +10805,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10799,7 +10843,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -10837,7 +10881,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -10875,7 +10919,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -10913,7 +10957,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -10951,7 +10995,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -10989,7 +11033,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11027,7 +11071,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11065,7 +11109,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11103,7 +11147,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11141,7 +11185,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11179,7 +11223,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -11220,7 +11264,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -11258,7 +11302,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -11296,7 +11340,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -11337,7 +11381,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -11378,7 +11422,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -11416,7 +11460,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -11454,7 +11498,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -11492,7 +11536,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -11530,7 +11574,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -11568,7 +11612,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -11606,7 +11650,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -11644,7 +11688,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -11682,7 +11726,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -11720,7 +11764,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -11758,7 +11802,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -11796,7 +11840,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -11834,7 +11878,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -11872,7 +11916,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -11910,7 +11954,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -11948,7 +11992,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -11986,7 +12030,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -12024,7 +12068,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -12062,7 +12106,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -12100,7 +12144,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -12138,7 +12182,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -12176,7 +12220,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -12214,7 +12258,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -12252,7 +12296,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -12290,7 +12334,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -12328,7 +12372,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -12366,7 +12410,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -12407,7 +12451,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -12442,7 +12486,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -12477,7 +12521,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -12512,7 +12556,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -12547,7 +12591,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -12582,7 +12626,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -12623,7 +12667,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -12658,7 +12702,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -12693,7 +12737,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -12728,7 +12772,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -12766,7 +12810,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -12807,7 +12851,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -12845,7 +12889,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -12883,7 +12927,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -12921,7 +12965,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -12959,7 +13003,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -13000,7 +13044,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -13038,7 +13082,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -13076,7 +13120,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -13114,7 +13158,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -13152,7 +13196,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -13190,7 +13234,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -13231,7 +13275,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -13269,7 +13313,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -13307,7 +13351,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -13345,7 +13389,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -13386,7 +13430,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -13424,7 +13468,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -13465,7 +13509,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -13506,7 +13550,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -13547,7 +13591,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -13591,7 +13635,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -13629,7 +13673,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -13667,7 +13711,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -13705,7 +13749,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -13743,7 +13787,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -13781,7 +13825,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -13825,7 +13869,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -13863,7 +13907,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -13901,7 +13945,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -13939,7 +13983,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -13977,7 +14021,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -14015,7 +14059,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -14053,7 +14097,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -14091,7 +14135,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -14129,7 +14173,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -14173,7 +14217,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -14211,7 +14255,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -14249,7 +14293,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -14287,7 +14331,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -14325,7 +14369,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -14363,7 +14407,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -14401,7 +14445,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -14439,7 +14483,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -14480,7 +14524,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -14521,7 +14565,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -14562,7 +14606,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -14603,7 +14647,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -14644,7 +14688,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -14685,7 +14729,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -14726,7 +14770,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -14767,7 +14811,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -14808,7 +14852,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -14849,7 +14893,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -14890,7 +14934,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -14931,7 +14975,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -14972,7 +15016,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -15013,7 +15057,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -15054,7 +15098,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -15092,7 +15136,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -15130,7 +15174,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -15168,7 +15212,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -15206,7 +15250,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -15244,7 +15288,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -15282,7 +15326,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -15320,7 +15364,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -15358,7 +15402,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -15396,7 +15440,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -15434,7 +15478,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -15472,7 +15516,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -15510,7 +15554,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -15548,7 +15592,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -15586,7 +15630,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -15624,7 +15668,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -15662,7 +15706,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -15700,7 +15744,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -15738,7 +15782,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15776,7 +15820,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -15814,7 +15858,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -15852,7 +15896,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -15890,7 +15934,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -15928,7 +15972,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -15966,7 +16010,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -16004,7 +16048,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -16042,7 +16086,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -16080,7 +16124,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -16118,7 +16162,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -16156,7 +16200,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -16194,7 +16238,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -16232,7 +16276,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -16270,7 +16314,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -16308,7 +16352,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -16346,7 +16390,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -16384,7 +16428,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -16422,7 +16466,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -16460,7 +16504,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -16498,7 +16542,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -16536,7 +16580,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -16574,7 +16618,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -16612,7 +16656,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -16650,7 +16694,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -16688,7 +16732,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -16726,7 +16770,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -16764,7 +16808,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -16802,7 +16846,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -16840,7 +16884,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -16878,7 +16922,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -16916,7 +16960,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -16954,7 +16998,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -16992,7 +17036,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -17030,7 +17074,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -17068,7 +17112,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -17106,7 +17150,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -17144,7 +17188,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -17182,7 +17226,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -17220,7 +17264,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -17258,7 +17302,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -17296,7 +17340,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -17334,7 +17378,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -17372,7 +17416,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -17410,7 +17454,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -17448,7 +17492,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -17486,7 +17530,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
@@ -17524,7 +17568,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
@@ -17562,7 +17606,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
@@ -17600,7 +17644,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
@@ -17638,7 +17682,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
@@ -17676,7 +17720,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
@@ -17714,7 +17758,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>260</v>
       </c>
@@ -17752,7 +17796,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>261</v>
       </c>
@@ -17790,7 +17834,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>262</v>
       </c>
@@ -17828,7 +17872,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>263</v>
       </c>
@@ -17866,7 +17910,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>264</v>
       </c>
@@ -17904,7 +17948,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>265</v>
       </c>
@@ -17942,7 +17986,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>266</v>
       </c>
@@ -17980,7 +18024,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>267</v>
       </c>
@@ -18018,7 +18062,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>268</v>
       </c>
@@ -18056,7 +18100,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>269</v>
       </c>
@@ -18094,7 +18138,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>270</v>
       </c>
@@ -18132,7 +18176,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>271</v>
       </c>
@@ -18170,7 +18214,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>272</v>
       </c>
@@ -18208,7 +18252,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>273</v>
       </c>
@@ -18246,7 +18290,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>274</v>
       </c>
@@ -18284,7 +18328,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>275</v>
       </c>
@@ -18322,7 +18366,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>276</v>
       </c>
@@ -18360,7 +18404,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>277</v>
       </c>
@@ -18398,7 +18442,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>278</v>
       </c>
@@ -18436,7 +18480,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>279</v>
       </c>
@@ -18474,7 +18518,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>280</v>
       </c>
@@ -18512,7 +18556,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>281</v>
       </c>
@@ -18550,7 +18594,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>282</v>
       </c>
@@ -18588,7 +18632,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>283</v>
       </c>
@@ -18626,7 +18670,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>284</v>
       </c>
@@ -18664,7 +18708,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>285</v>
       </c>
@@ -18702,7 +18746,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>286</v>
       </c>
@@ -18740,7 +18784,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>287</v>
       </c>
@@ -18778,7 +18822,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>288</v>
       </c>
@@ -18816,7 +18860,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>289</v>
       </c>
@@ -18854,7 +18898,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>290</v>
       </c>
@@ -18892,7 +18936,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>291</v>
       </c>
@@ -18930,7 +18974,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>292</v>
       </c>
@@ -18968,7 +19012,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>293</v>
       </c>
@@ -19009,7 +19053,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>294</v>
       </c>
@@ -19050,7 +19094,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>295</v>
       </c>
@@ -19091,7 +19135,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>296</v>
       </c>
@@ -19132,7 +19176,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>297</v>
       </c>
@@ -19173,7 +19217,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>298</v>
       </c>
@@ -19214,7 +19258,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>299</v>
       </c>
@@ -19255,7 +19299,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>300</v>
       </c>
@@ -19296,7 +19340,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>301</v>
       </c>
@@ -19337,7 +19381,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>302</v>
       </c>
@@ -19378,7 +19422,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>303</v>
       </c>
@@ -19419,7 +19463,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>304</v>
       </c>
@@ -19460,7 +19504,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>305</v>
       </c>
@@ -19501,7 +19545,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>306</v>
       </c>
@@ -19539,7 +19583,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>307</v>
       </c>
@@ -19577,7 +19621,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>308</v>
       </c>
@@ -19615,7 +19659,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>309</v>
       </c>
@@ -19653,7 +19697,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>310</v>
       </c>
@@ -19691,7 +19735,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>311</v>
       </c>
@@ -19729,7 +19773,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>312</v>
       </c>
@@ -19767,7 +19811,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>313</v>
       </c>
@@ -19805,7 +19849,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>314</v>
       </c>
@@ -19843,7 +19887,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>315</v>
       </c>
@@ -19881,7 +19925,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>316</v>
       </c>
@@ -19922,7 +19966,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>317</v>
       </c>
@@ -19963,7 +20007,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>318</v>
       </c>
@@ -20004,7 +20048,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>319</v>
       </c>
@@ -20045,7 +20089,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>320</v>
       </c>
@@ -20086,7 +20130,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>321</v>
       </c>
@@ -20127,7 +20171,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>322</v>
       </c>
@@ -20168,7 +20212,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>323</v>
       </c>
@@ -20209,7 +20253,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>324</v>
       </c>
@@ -20250,7 +20294,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>325</v>
       </c>
@@ -20291,7 +20335,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>326</v>
       </c>
@@ -20332,7 +20376,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>327</v>
       </c>
@@ -20373,7 +20417,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>328</v>
       </c>
@@ -20414,7 +20458,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>329</v>
       </c>
@@ -20455,7 +20499,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>330</v>
       </c>
@@ -20496,7 +20540,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>331</v>
       </c>
@@ -20534,7 +20578,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>332</v>
       </c>
@@ -20572,7 +20616,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>333</v>
       </c>
@@ -20610,7 +20654,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>334</v>
       </c>
@@ -20648,7 +20692,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>335</v>
       </c>
@@ -20686,7 +20730,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>336</v>
       </c>
@@ -20724,7 +20768,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>337</v>
       </c>
@@ -20762,7 +20806,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>338</v>
       </c>
@@ -20800,7 +20844,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>339</v>
       </c>
@@ -20841,7 +20885,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>340</v>
       </c>
@@ -20885,7 +20929,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>341</v>
       </c>
@@ -20926,7 +20970,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>342</v>
       </c>
@@ -20967,7 +21011,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>343</v>
       </c>
@@ -21008,7 +21052,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>344</v>
       </c>
@@ -21049,7 +21093,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>345</v>
       </c>
@@ -21090,7 +21134,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>346</v>
       </c>
@@ -21131,7 +21175,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>347</v>
       </c>
@@ -21172,7 +21216,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>348</v>
       </c>
@@ -21213,7 +21257,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>349</v>
       </c>
@@ -21254,7 +21298,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>350</v>
       </c>
@@ -21295,7 +21339,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>351</v>
       </c>
@@ -21330,7 +21374,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>352</v>
       </c>
@@ -21371,7 +21415,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>353</v>
       </c>
@@ -21412,7 +21456,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>354</v>
       </c>
@@ -21453,7 +21497,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>355</v>
       </c>
@@ -21494,7 +21538,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>356</v>
       </c>
@@ -21529,7 +21573,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>357</v>
       </c>
@@ -21564,7 +21608,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>358</v>
       </c>
@@ -21599,7 +21643,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>359</v>
       </c>
@@ -21634,7 +21678,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>360</v>
       </c>
@@ -21678,7 +21722,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>361</v>
       </c>
@@ -21722,7 +21766,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>362</v>
       </c>
@@ -21766,7 +21810,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>363</v>
       </c>
@@ -21810,7 +21854,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>364</v>
       </c>
@@ -21854,7 +21898,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>365</v>
       </c>
@@ -21898,7 +21942,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>366</v>
       </c>
@@ -21942,7 +21986,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>367</v>
       </c>
@@ -21986,7 +22030,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>368</v>
       </c>
@@ -22030,7 +22074,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>369</v>
       </c>
@@ -22074,7 +22118,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>370</v>
       </c>
@@ -22118,7 +22162,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>371</v>
       </c>
@@ -22162,7 +22206,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>372</v>
       </c>
@@ -22206,7 +22250,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>373</v>
       </c>
@@ -22247,7 +22291,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>374</v>
       </c>
@@ -22288,7 +22332,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>375</v>
       </c>
@@ -22329,7 +22373,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>376</v>
       </c>
@@ -22370,7 +22414,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>377</v>
       </c>
@@ -22411,7 +22455,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>378</v>
       </c>
@@ -22452,7 +22496,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>379</v>
       </c>
@@ -22493,7 +22537,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>380</v>
       </c>
@@ -22534,7 +22578,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>381</v>
       </c>
@@ -22575,7 +22619,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>382</v>
       </c>
@@ -22616,7 +22660,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>383</v>
       </c>
@@ -22657,7 +22701,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>384</v>
       </c>
@@ -22698,7 +22742,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>385</v>
       </c>
@@ -22739,7 +22783,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>386</v>
       </c>
@@ -22780,7 +22824,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>387</v>
       </c>
@@ -22821,7 +22865,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>388</v>
       </c>
@@ -22862,7 +22906,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>389</v>
       </c>
@@ -22903,7 +22947,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>390</v>
       </c>
@@ -22944,7 +22988,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>391</v>
       </c>
@@ -22985,7 +23029,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>392</v>
       </c>
@@ -23026,7 +23070,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>393</v>
       </c>
@@ -23067,7 +23111,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>394</v>
       </c>
@@ -23108,7 +23152,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>395</v>
       </c>
@@ -23146,7 +23190,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>396</v>
       </c>
@@ -23184,7 +23228,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>397</v>
       </c>
@@ -23222,7 +23266,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>398</v>
       </c>
@@ -23260,7 +23304,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>399</v>
       </c>
@@ -23298,7 +23342,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>400</v>
       </c>
@@ -23336,7 +23380,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>401</v>
       </c>
@@ -23374,7 +23418,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>402</v>
       </c>
@@ -23412,7 +23456,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>403</v>
       </c>
@@ -23450,7 +23494,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>404</v>
       </c>
@@ -23488,7 +23532,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>405</v>
       </c>
@@ -23526,7 +23570,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>406</v>
       </c>
@@ -23564,7 +23608,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>407</v>
       </c>
@@ -23602,7 +23646,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>408</v>
       </c>
@@ -23640,7 +23684,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>409</v>
       </c>
@@ -23678,7 +23722,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>410</v>
       </c>
@@ -23716,7 +23760,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>411</v>
       </c>
@@ -23754,7 +23798,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>412</v>
       </c>
@@ -23792,7 +23836,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>413</v>
       </c>
@@ -23830,7 +23874,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>414</v>
       </c>
@@ -23868,7 +23912,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>415</v>
       </c>
@@ -23906,7 +23950,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>416</v>
       </c>
@@ -23944,7 +23988,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>417</v>
       </c>
@@ -23982,7 +24026,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>418</v>
       </c>
@@ -24020,7 +24064,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>419</v>
       </c>
@@ -24058,7 +24102,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>420</v>
       </c>
@@ -24096,7 +24140,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>421</v>
       </c>
@@ -24134,7 +24178,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>422</v>
       </c>
@@ -24172,7 +24216,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>423</v>
       </c>
@@ -24210,7 +24254,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>424</v>
       </c>
@@ -24248,7 +24292,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>425</v>
       </c>
@@ -24286,7 +24330,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>426</v>
       </c>
@@ -24324,7 +24368,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>427</v>
       </c>
@@ -24362,7 +24406,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>428</v>
       </c>
@@ -24400,7 +24444,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>429</v>
       </c>
@@ -24438,7 +24482,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>430</v>
       </c>
@@ -24476,7 +24520,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>431</v>
       </c>
@@ -24514,7 +24558,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>432</v>
       </c>
@@ -24552,7 +24596,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>433</v>
       </c>
@@ -24590,7 +24634,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>434</v>
       </c>
@@ -24628,7 +24672,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>435</v>
       </c>
@@ -24666,7 +24710,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>436</v>
       </c>
@@ -24704,7 +24748,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>437</v>
       </c>
@@ -24742,7 +24786,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>438</v>
       </c>
@@ -24780,7 +24824,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>439</v>
       </c>
@@ -24818,7 +24862,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>440</v>
       </c>
@@ -24856,7 +24900,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>441</v>
       </c>
@@ -24894,7 +24938,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>442</v>
       </c>
@@ -24932,7 +24976,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>443</v>
       </c>
@@ -24970,7 +25014,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>444</v>
       </c>
@@ -25008,7 +25052,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>445</v>
       </c>
@@ -25046,7 +25090,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>446</v>
       </c>
@@ -25084,7 +25128,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>447</v>
       </c>
@@ -25122,7 +25166,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>448</v>
       </c>
@@ -25160,7 +25204,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A450">
         <v>449</v>
       </c>
@@ -25198,7 +25242,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A451">
         <v>450</v>
       </c>
@@ -25239,7 +25283,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A452">
         <v>451</v>
       </c>
@@ -25280,7 +25324,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A453">
         <v>452</v>
       </c>
@@ -25321,7 +25365,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A454">
         <v>453</v>
       </c>
@@ -25362,7 +25406,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A455">
         <v>454</v>
       </c>
@@ -25403,7 +25447,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A456">
         <v>455</v>
       </c>
@@ -25444,7 +25488,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A457">
         <v>456</v>
       </c>
@@ -25485,7 +25529,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>457</v>
       </c>
@@ -25526,7 +25570,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>458</v>
       </c>
@@ -25567,7 +25611,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>459</v>
       </c>
@@ -25608,7 +25652,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>460</v>
       </c>
@@ -25649,7 +25693,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>461</v>
       </c>
@@ -25690,7 +25734,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>462</v>
       </c>
@@ -25731,7 +25775,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>463</v>
       </c>
@@ -25772,7 +25816,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>464</v>
       </c>
@@ -25813,7 +25857,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>465</v>
       </c>
@@ -25854,7 +25898,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>466</v>
       </c>
@@ -25895,7 +25939,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>467</v>
       </c>
@@ -25936,7 +25980,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>468</v>
       </c>
@@ -25977,7 +26021,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>469</v>
       </c>
@@ -26018,7 +26062,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>470</v>
       </c>
@@ -26059,7 +26103,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>471</v>
       </c>
@@ -26100,7 +26144,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>472</v>
       </c>
@@ -26141,7 +26185,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>473</v>
       </c>
@@ -26182,7 +26226,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>474</v>
       </c>
@@ -26223,7 +26267,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>475</v>
       </c>
@@ -26264,7 +26308,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>476</v>
       </c>
@@ -26305,7 +26349,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>477</v>
       </c>
@@ -26346,7 +26390,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>478</v>
       </c>
@@ -26387,7 +26431,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>479</v>
       </c>
@@ -26428,7 +26472,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A481">
         <v>480</v>
       </c>
@@ -26469,7 +26513,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A482">
         <v>481</v>
       </c>
@@ -26510,7 +26554,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A483">
         <v>482</v>
       </c>
@@ -26551,7 +26595,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A484">
         <v>483</v>
       </c>
@@ -26592,7 +26636,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A485">
         <v>484</v>
       </c>
@@ -26633,7 +26677,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A486">
         <v>485</v>
       </c>
@@ -26674,7 +26718,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A487">
         <v>486</v>
       </c>
@@ -26715,7 +26759,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A488">
         <v>487</v>
       </c>
@@ -26756,7 +26800,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A489">
         <v>488</v>
       </c>
@@ -26797,7 +26841,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A490">
         <v>489</v>
       </c>
@@ -26838,7 +26882,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A491">
         <v>490</v>
       </c>
@@ -26879,7 +26923,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A492">
         <v>491</v>
       </c>
@@ -26920,7 +26964,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A493">
         <v>492</v>
       </c>
@@ -26961,7 +27005,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A494">
         <v>493</v>
       </c>
@@ -27002,7 +27046,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A495">
         <v>494</v>
       </c>
@@ -27043,7 +27087,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A496">
         <v>495</v>
       </c>
@@ -27084,7 +27128,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A497">
         <v>496</v>
       </c>
@@ -27122,7 +27166,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A498">
         <v>497</v>
       </c>
@@ -27160,7 +27204,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A499">
         <v>498</v>
       </c>
@@ -27198,7 +27242,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A500">
         <v>499</v>
       </c>
@@ -27236,7 +27280,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A501">
         <v>500</v>
       </c>
@@ -27274,7 +27318,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A502">
         <v>501</v>
       </c>
@@ -27312,7 +27356,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A503">
         <v>502</v>
       </c>
@@ -27350,7 +27394,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A504">
         <v>503</v>
       </c>
@@ -27388,7 +27432,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A505">
         <v>504</v>
       </c>
@@ -27426,7 +27470,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A506">
         <v>505</v>
       </c>
@@ -27464,7 +27508,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A507">
         <v>506</v>
       </c>
@@ -27502,7 +27546,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A508">
         <v>507</v>
       </c>
@@ -27540,7 +27584,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A509">
         <v>508</v>
       </c>
@@ -27578,7 +27622,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A510">
         <v>509</v>
       </c>
@@ -27616,7 +27660,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A511">
         <v>510</v>
       </c>
@@ -27654,7 +27698,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A512">
         <v>511</v>
       </c>
@@ -27692,7 +27736,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A513">
         <v>512</v>
       </c>
@@ -27730,7 +27774,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A514">
         <v>513</v>
       </c>
@@ -27771,7 +27815,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A515">
         <v>514</v>
       </c>
@@ -27809,7 +27853,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A516">
         <v>515</v>
       </c>
@@ -27847,7 +27891,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A517">
         <v>516</v>
       </c>
@@ -27885,7 +27929,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518">
         <v>517</v>
       </c>
@@ -27923,7 +27967,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519">
         <v>518</v>
       </c>
@@ -27961,7 +28005,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A520">
         <v>519</v>
       </c>
@@ -27999,7 +28043,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A521">
         <v>520</v>
       </c>
@@ -28037,7 +28081,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A522">
         <v>521</v>
       </c>
@@ -28075,7 +28119,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A523">
         <v>522</v>
       </c>
@@ -28113,7 +28157,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A524">
         <v>523</v>
       </c>
@@ -28151,7 +28195,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A525">
         <v>524</v>
       </c>
@@ -28189,7 +28233,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A526">
         <v>525</v>
       </c>
@@ -28227,7 +28271,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A527">
         <v>526</v>
       </c>
@@ -28265,7 +28309,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A528">
         <v>527</v>
       </c>
@@ -28303,7 +28347,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A529">
         <v>528</v>
       </c>
@@ -28341,7 +28385,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A530">
         <v>529</v>
       </c>
@@ -28379,7 +28423,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A531">
         <v>530</v>
       </c>
@@ -28417,7 +28461,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A532">
         <v>531</v>
       </c>
@@ -28455,7 +28499,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A533">
         <v>532</v>
       </c>
@@ -28493,7 +28537,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A534">
         <v>533</v>
       </c>
@@ -28531,7 +28575,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A535">
         <v>534</v>
       </c>
@@ -28569,7 +28613,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A536">
         <v>535</v>
       </c>
@@ -28607,7 +28651,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A537">
         <v>536</v>
       </c>
@@ -28645,7 +28689,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A538">
         <v>537</v>
       </c>
@@ -28683,7 +28727,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A539">
         <v>538</v>
       </c>
@@ -28721,7 +28765,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A540">
         <v>539</v>
       </c>
@@ -28759,7 +28803,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A541">
         <v>540</v>
       </c>
@@ -28797,7 +28841,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A542">
         <v>541</v>
       </c>
@@ -28835,7 +28879,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A543">
         <v>542</v>
       </c>
@@ -28873,7 +28917,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A544">
         <v>543</v>
       </c>
@@ -28911,7 +28955,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A545">
         <v>544</v>
       </c>
@@ -28949,7 +28993,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A546">
         <v>545</v>
       </c>
@@ -28987,7 +29031,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A547">
         <v>546</v>
       </c>
@@ -29025,7 +29069,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A548">
         <v>547</v>
       </c>
@@ -29063,7 +29107,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A549">
         <v>548</v>
       </c>
@@ -29101,7 +29145,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A550">
         <v>549</v>
       </c>
@@ -29139,7 +29183,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A551">
         <v>550</v>
       </c>
@@ -29177,7 +29221,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A552">
         <v>551</v>
       </c>
@@ -29215,7 +29259,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A553">
         <v>552</v>
       </c>
@@ -29253,7 +29297,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A554">
         <v>553</v>
       </c>
@@ -29291,7 +29335,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A555">
         <v>554</v>
       </c>
@@ -29329,7 +29373,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A556">
         <v>555</v>
       </c>
@@ -29367,7 +29411,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A557">
         <v>556</v>
       </c>
@@ -29405,7 +29449,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A558">
         <v>557</v>
       </c>
@@ -29443,7 +29487,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A559">
         <v>558</v>
       </c>
@@ -29481,7 +29525,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A560">
         <v>559</v>
       </c>
@@ -29519,7 +29563,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A561">
         <v>560</v>
       </c>
@@ -29557,7 +29601,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A562">
         <v>561</v>
       </c>
@@ -29595,7 +29639,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A563">
         <v>562</v>
       </c>
@@ -29633,7 +29677,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A564">
         <v>563</v>
       </c>
@@ -29671,7 +29715,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A565">
         <v>564</v>
       </c>
@@ -29709,7 +29753,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A566">
         <v>565</v>
       </c>
@@ -29747,7 +29791,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A567">
         <v>566</v>
       </c>
@@ -29785,7 +29829,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A568">
         <v>567</v>
       </c>
@@ -29823,7 +29867,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A569">
         <v>568</v>
       </c>
@@ -29861,7 +29905,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A570">
         <v>569</v>
       </c>
@@ -29899,7 +29943,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A571">
         <v>570</v>
       </c>
@@ -29937,7 +29981,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A572">
         <v>571</v>
       </c>
@@ -29975,7 +30019,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A573">
         <v>572</v>
       </c>
@@ -30013,7 +30057,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A574">
         <v>573</v>
       </c>
@@ -30051,7 +30095,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A575">
         <v>574</v>
       </c>
@@ -30089,7 +30133,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A576">
         <v>575</v>
       </c>
@@ -30127,7 +30171,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A577">
         <v>576</v>
       </c>
@@ -30165,7 +30209,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A578">
         <v>577</v>
       </c>
@@ -30203,7 +30247,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A579">
         <v>578</v>
       </c>
@@ -30241,7 +30285,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A580">
         <v>579</v>
       </c>
@@ -30279,7 +30323,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A581">
         <v>580</v>
       </c>
@@ -30317,7 +30361,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A582">
         <v>581</v>
       </c>
@@ -30355,7 +30399,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A583">
         <v>582</v>
       </c>
@@ -30393,7 +30437,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A584">
         <v>583</v>
       </c>
@@ -30431,7 +30475,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A585">
         <v>584</v>
       </c>
@@ -30469,7 +30513,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A586">
         <v>585</v>
       </c>
@@ -30507,7 +30551,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A587">
         <v>586</v>
       </c>
@@ -30545,7 +30589,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A588">
         <v>587</v>
       </c>
@@ -30583,7 +30627,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A589">
         <v>588</v>
       </c>
@@ -30621,7 +30665,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A590">
         <v>589</v>
       </c>
@@ -30659,7 +30703,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A591">
         <v>590</v>
       </c>
@@ -30697,7 +30741,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A592">
         <v>591</v>
       </c>
@@ -30741,7 +30785,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A593">
         <v>592</v>
       </c>
@@ -30785,7 +30829,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A594">
         <v>593</v>
       </c>
@@ -30829,7 +30873,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A595">
         <v>594</v>
       </c>
@@ -30873,7 +30917,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A596">
         <v>595</v>
       </c>
@@ -30917,7 +30961,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A597">
         <v>596</v>
       </c>
@@ -30961,7 +31005,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A598">
         <v>597</v>
       </c>
@@ -31005,7 +31049,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A599">
         <v>598</v>
       </c>
@@ -31049,7 +31093,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A600">
         <v>599</v>
       </c>
@@ -31093,7 +31137,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A601">
         <v>600</v>
       </c>
@@ -31134,7 +31178,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A602">
         <v>601</v>
       </c>
@@ -31178,7 +31222,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A603">
         <v>602</v>
       </c>
@@ -31222,7 +31266,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A604">
         <v>603</v>
       </c>
@@ -31266,7 +31310,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A605">
         <v>604</v>
       </c>
@@ -31310,7 +31354,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A606">
         <v>605</v>
       </c>
@@ -31354,7 +31398,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A607">
         <v>606</v>
       </c>
@@ -31398,7 +31442,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A608">
         <v>607</v>
       </c>
@@ -31442,7 +31486,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A609">
         <v>608</v>
       </c>
@@ -31486,7 +31530,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A610">
         <v>609</v>
       </c>
@@ -31527,7 +31571,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A611">
         <v>610</v>
       </c>
@@ -31568,7 +31612,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A612">
         <v>611</v>
       </c>
@@ -31609,7 +31653,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A613">
         <v>612</v>
       </c>
@@ -31647,7 +31691,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A614">
         <v>613</v>
       </c>
@@ -31688,7 +31732,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A615">
         <v>614</v>
       </c>
@@ -31732,7 +31776,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A616">
         <v>615</v>
       </c>
@@ -31776,7 +31820,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A617">
         <v>616</v>
       </c>
@@ -31820,7 +31864,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A618">
         <v>617</v>
       </c>
@@ -31858,7 +31902,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A619">
         <v>618</v>
       </c>
@@ -31899,7 +31943,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A620">
         <v>619</v>
       </c>
@@ -31940,7 +31984,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A621">
         <v>620</v>
       </c>
@@ -31981,7 +32025,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A622">
         <v>621</v>
       </c>
@@ -32025,7 +32069,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A623">
         <v>622</v>
       </c>
@@ -32069,7 +32113,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A624">
         <v>623</v>
       </c>
@@ -32113,7 +32157,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A625">
         <v>624</v>
       </c>
@@ -32157,7 +32201,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A626">
         <v>625</v>
       </c>
@@ -32201,7 +32245,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A627">
         <v>626</v>
       </c>
@@ -32242,7 +32286,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A628">
         <v>627</v>
       </c>
@@ -32286,7 +32330,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A629">
         <v>628</v>
       </c>
@@ -32327,7 +32371,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A630">
         <v>629</v>
       </c>
@@ -32368,7 +32412,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A631">
         <v>630</v>
       </c>
@@ -32409,7 +32453,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A632">
         <v>631</v>
       </c>
@@ -32447,7 +32491,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A633">
         <v>632</v>
       </c>
@@ -32488,7 +32532,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A634">
         <v>633</v>
       </c>
@@ -32529,7 +32573,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A635">
         <v>634</v>
       </c>
@@ -32570,7 +32614,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A636">
         <v>635</v>
       </c>
@@ -32611,7 +32655,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A637">
         <v>636</v>
       </c>
@@ -32652,7 +32696,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A638">
         <v>637</v>
       </c>
@@ -32693,7 +32737,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A639">
         <v>638</v>
       </c>
@@ -32734,7 +32778,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A640">
         <v>639</v>
       </c>
@@ -32775,7 +32819,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A641">
         <v>640</v>
       </c>
@@ -32819,7 +32863,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A642">
         <v>641</v>
       </c>
@@ -32860,7 +32904,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A643">
         <v>642</v>
       </c>
@@ -32901,7 +32945,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A644">
         <v>643</v>
       </c>
@@ -32942,7 +32986,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A645">
         <v>644</v>
       </c>
@@ -32983,7 +33027,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A646">
         <v>645</v>
       </c>
@@ -33024,7 +33068,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A647">
         <v>646</v>
       </c>
@@ -33065,7 +33109,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A648">
         <v>647</v>
       </c>
@@ -33106,7 +33150,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A649">
         <v>648</v>
       </c>
@@ -33147,7 +33191,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A650">
         <v>649</v>
       </c>
@@ -33188,7 +33232,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A651">
         <v>650</v>
       </c>
@@ -33229,7 +33273,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A652">
         <v>651</v>
       </c>
@@ -33270,7 +33314,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A653">
         <v>652</v>
       </c>
@@ -33311,7 +33355,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A654">
         <v>653</v>
       </c>
@@ -33352,7 +33396,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A655">
         <v>654</v>
       </c>
@@ -33393,7 +33437,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A656">
         <v>655</v>
       </c>
@@ -33434,7 +33478,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="657" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A657">
         <v>656</v>
       </c>
@@ -33475,7 +33519,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="658" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A658">
         <v>657</v>
       </c>
@@ -33516,7 +33560,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="659" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A659">
         <v>658</v>
       </c>
@@ -33557,7 +33601,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="660" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A660">
         <v>659</v>
       </c>
@@ -33598,7 +33642,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="661" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A661">
         <v>660</v>
       </c>
@@ -33639,7 +33683,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="662" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A662">
         <v>661</v>
       </c>
@@ -33680,7 +33724,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="663" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A663">
         <v>662</v>
       </c>
@@ -33721,7 +33765,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="664" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A664">
         <v>663</v>
       </c>
@@ -33762,7 +33806,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="665" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A665">
         <v>664</v>
       </c>
@@ -33803,7 +33847,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="666" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A666">
         <v>665</v>
       </c>
@@ -33835,7 +33879,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A667">
         <v>666</v>
       </c>
@@ -33867,7 +33911,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A668">
         <v>667</v>
       </c>
@@ -33899,7 +33943,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A669">
         <v>668</v>
       </c>
@@ -33931,7 +33975,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A670">
         <v>669</v>
       </c>
@@ -33972,7 +34016,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="671" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A671">
         <v>670</v>
       </c>
@@ -34013,7 +34057,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="672" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A672">
         <v>671</v>
       </c>
@@ -34054,7 +34098,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A673">
         <v>672</v>
       </c>
@@ -34095,7 +34139,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A674">
         <v>673</v>
       </c>
@@ -34136,7 +34180,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A675">
         <v>674</v>
       </c>
@@ -34180,7 +34224,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A676">
         <v>675</v>
       </c>
@@ -34224,7 +34268,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A677">
         <v>676</v>
       </c>
@@ -34265,7 +34309,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A678">
         <v>677</v>
       </c>
@@ -34306,7 +34350,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A679">
         <v>678</v>
       </c>
@@ -34347,7 +34391,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A680">
         <v>679</v>
       </c>
@@ -34388,7 +34432,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A681">
         <v>680</v>
       </c>
@@ -34429,7 +34473,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A682">
         <v>681</v>
       </c>
@@ -34470,7 +34514,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A683">
         <v>682</v>
       </c>
@@ -34511,7 +34555,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A684">
         <v>683</v>
       </c>
@@ -34552,7 +34596,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A685">
         <v>684</v>
       </c>
@@ -34593,7 +34637,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A686">
         <v>685</v>
       </c>
@@ -34634,7 +34678,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A687">
         <v>686</v>
       </c>
@@ -34675,7 +34719,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A688">
         <v>687</v>
       </c>
@@ -34716,7 +34760,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A689">
         <v>688</v>
       </c>
@@ -34757,7 +34801,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A690">
         <v>689</v>
       </c>
@@ -34798,7 +34842,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A691">
         <v>690</v>
       </c>
@@ -34839,7 +34883,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A692">
         <v>691</v>
       </c>
@@ -34880,7 +34924,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A693">
         <v>692</v>
       </c>
@@ -34921,7 +34965,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A694">
         <v>693</v>
       </c>
@@ -34962,7 +35006,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A695">
         <v>694</v>
       </c>
@@ -35006,7 +35050,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A696">
         <v>695</v>
       </c>
@@ -35050,7 +35094,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A697">
         <v>696</v>
       </c>
@@ -35094,7 +35138,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A698">
         <v>697</v>
       </c>
@@ -35138,7 +35182,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A699">
         <v>698</v>
       </c>
@@ -35182,7 +35226,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A700">
         <v>699</v>
       </c>
@@ -35226,7 +35270,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A701">
         <v>700</v>
       </c>
@@ -35270,7 +35314,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A702">
         <v>701</v>
       </c>
@@ -35314,7 +35358,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A703">
         <v>702</v>
       </c>
@@ -35355,7 +35399,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A704">
         <v>703</v>
       </c>
@@ -35399,7 +35443,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A705">
         <v>704</v>
       </c>
@@ -35440,15 +35484,15 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A706">
         <v>705</v>
       </c>
       <c r="B706" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C706" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D706" s="6" t="s">
         <v>856</v>
@@ -35484,15 +35528,15 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A707">
         <v>706</v>
       </c>
       <c r="B707" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C707" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D707" s="6" t="s">
         <v>856</v>
@@ -35528,15 +35572,15 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A708">
         <v>707</v>
       </c>
       <c r="B708" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C708" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D708" s="6" t="s">
         <v>856</v>
@@ -35572,15 +35616,15 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A709">
         <v>708</v>
       </c>
       <c r="B709" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C709" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D709" s="6" t="s">
         <v>1105</v>
@@ -35619,15 +35663,15 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A710">
         <v>709</v>
       </c>
       <c r="B710" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D710" s="6" t="s">
         <v>1105</v>
@@ -35663,15 +35707,15 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A711">
         <v>710</v>
       </c>
       <c r="B711" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C711" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D711" s="6" t="s">
         <v>1106</v>
@@ -35707,15 +35751,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A712">
         <v>711</v>
       </c>
       <c r="B712" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C712" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D712" s="6" t="s">
         <v>1106</v>
@@ -35748,15 +35792,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A713">
         <v>712</v>
       </c>
       <c r="B713" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C713" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D713" s="6" t="s">
         <v>1106</v>
@@ -35789,15 +35833,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A714">
         <v>713</v>
       </c>
       <c r="B714" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D714" s="6" t="s">
         <v>1106</v>
@@ -35830,15 +35874,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A715">
         <v>714</v>
       </c>
       <c r="B715" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C715" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D715" s="6" t="s">
         <v>1106</v>
@@ -35871,15 +35915,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A716">
         <v>715</v>
       </c>
       <c r="B716" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C716" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D716" s="6" t="s">
         <v>1106</v>
@@ -35912,15 +35956,15 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A717">
         <v>716</v>
       </c>
       <c r="B717" s="6" t="s">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="C717" s="6" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D717" s="6" t="s">
         <v>1106</v>
@@ -35953,7 +35997,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A718">
         <v>717</v>
       </c>
@@ -35994,7 +36038,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A719">
         <v>718</v>
       </c>
@@ -36035,7 +36079,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A720">
         <v>719</v>
       </c>
@@ -36076,7 +36120,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A721">
         <v>720</v>
       </c>
@@ -36117,7 +36161,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="722" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A722">
         <v>721</v>
       </c>
@@ -36158,7 +36202,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A723">
         <v>722</v>
       </c>
@@ -36199,7 +36243,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A724">
         <v>723</v>
       </c>
@@ -36240,7 +36284,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="725" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A725">
         <v>724</v>
       </c>
@@ -36281,7 +36325,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="726" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A726">
         <v>725</v>
       </c>
@@ -36322,7 +36366,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A727">
         <v>726</v>
       </c>
@@ -36363,7 +36407,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A728">
         <v>727</v>
       </c>
@@ -36404,7 +36448,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A729">
         <v>728</v>
       </c>
@@ -36445,7 +36489,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="730" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A730">
         <v>729</v>
       </c>
@@ -36486,7 +36530,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A731">
         <v>730</v>
       </c>
@@ -36527,7 +36571,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A732">
         <v>731</v>
       </c>
@@ -36568,7 +36612,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="733" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A733">
         <v>732</v>
       </c>
@@ -36609,7 +36653,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="734" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A734">
         <v>733</v>
       </c>
@@ -36650,7 +36694,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="735" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A735">
         <v>734</v>
       </c>
@@ -36691,7 +36735,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A736">
         <v>735</v>
       </c>
@@ -36732,7 +36776,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A737">
         <v>736</v>
       </c>
@@ -36773,7 +36817,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A738">
         <v>737</v>
       </c>
@@ -36814,7 +36858,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A739">
         <v>738</v>
       </c>
@@ -36855,7 +36899,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A740">
         <v>739</v>
       </c>
@@ -36896,7 +36940,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A741">
         <v>740</v>
       </c>
@@ -36937,7 +36981,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="742" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A742">
         <v>741</v>
       </c>
@@ -36978,7 +37022,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="743" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A743">
         <v>742</v>
       </c>
@@ -37019,7 +37063,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A744">
         <v>743</v>
       </c>
@@ -37060,7 +37104,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="745" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A745">
         <v>744</v>
       </c>
@@ -37101,7 +37145,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A746">
         <v>745</v>
       </c>
@@ -37142,7 +37186,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A747">
         <v>746</v>
       </c>
@@ -37183,7 +37227,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="748" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A748">
         <v>747</v>
       </c>
@@ -37224,7 +37268,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A749">
         <v>748</v>
       </c>
@@ -37265,7 +37309,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A750">
         <v>749</v>
       </c>
@@ -37306,7 +37350,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A751">
         <v>750</v>
       </c>
@@ -37347,7 +37391,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A752">
         <v>751</v>
       </c>
@@ -37388,7 +37432,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="753" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A753">
         <v>752</v>
       </c>
@@ -37429,7 +37473,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="754" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A754">
         <v>753</v>
       </c>
@@ -37470,7 +37514,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="755" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A755">
         <v>754</v>
       </c>
@@ -37511,7 +37555,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="756" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A756">
         <v>755</v>
       </c>
@@ -37552,7 +37596,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="757" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A757">
         <v>756</v>
       </c>
@@ -37593,7 +37637,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="758" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A758">
         <v>757</v>
       </c>
@@ -37634,7 +37678,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="759" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A759">
         <v>758</v>
       </c>
@@ -37675,7 +37719,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="760" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A760">
         <v>759</v>
       </c>
@@ -37716,7 +37760,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="761" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A761">
         <v>760</v>
       </c>
@@ -37760,7 +37804,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="762" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A762">
         <v>761</v>
       </c>
@@ -37804,7 +37848,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="763" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A763">
         <v>762</v>
       </c>
@@ -37848,7 +37892,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="764" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A764">
         <v>763</v>
       </c>
@@ -37892,7 +37936,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="765" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A765">
         <v>764</v>
       </c>
@@ -37936,7 +37980,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="766" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A766">
         <v>765</v>
       </c>
@@ -37980,7 +38024,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="767" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A767">
         <v>766</v>
       </c>
@@ -38024,7 +38068,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="768" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A768">
         <v>767</v>
       </c>
@@ -38068,7 +38112,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="769" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A769">
         <v>768</v>
       </c>
@@ -38112,7 +38156,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="770" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A770">
         <v>769</v>
       </c>
@@ -38156,7 +38200,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="771" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A771">
         <v>770</v>
       </c>
@@ -38200,7 +38244,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="772" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A772">
         <v>771</v>
       </c>
@@ -38244,7 +38288,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="773" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A773">
         <v>772</v>
       </c>
@@ -38288,7 +38332,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="774" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A774">
         <v>773</v>
       </c>
@@ -38332,7 +38376,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="775" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A775">
         <v>774</v>
       </c>
@@ -38376,7 +38420,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="776" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A776">
         <v>775</v>
       </c>
@@ -38420,7 +38464,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="777" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A777">
         <v>776</v>
       </c>
@@ -38464,7 +38508,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="778" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A778">
         <v>777</v>
       </c>
@@ -38505,7 +38549,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="779" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A779">
         <v>778</v>
       </c>
@@ -38546,7 +38590,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="780" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A780">
         <v>779</v>
       </c>
@@ -38587,7 +38631,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="781" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A781">
         <v>780</v>
       </c>
@@ -38628,7 +38672,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="782" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A782">
         <v>781</v>
       </c>
@@ -38669,7 +38713,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="783" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A783">
         <v>782</v>
       </c>
@@ -38710,7 +38754,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="784" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A784">
         <v>783</v>
       </c>
@@ -38751,7 +38795,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="785" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A785">
         <v>784</v>
       </c>
@@ -38792,7 +38836,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="786" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A786">
         <v>785</v>
       </c>
@@ -38833,7 +38877,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="787" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A787">
         <v>786</v>
       </c>
@@ -38874,7 +38918,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="788" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A788">
         <v>787</v>
       </c>
@@ -38915,7 +38959,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="789" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A789">
         <v>788</v>
       </c>
@@ -38956,7 +39000,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="790" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A790">
         <v>789</v>
       </c>
@@ -38997,7 +39041,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="791" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A791">
         <v>790</v>
       </c>
@@ -39038,7 +39082,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="792" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A792">
         <v>791</v>
       </c>
@@ -39079,7 +39123,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="793" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A793">
         <v>792</v>
       </c>
@@ -39120,7 +39164,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="794" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A794">
         <v>793</v>
       </c>
@@ -39164,7 +39208,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="795" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A795">
         <v>794</v>
       </c>
@@ -39205,7 +39249,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="796" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A796">
         <v>795</v>
       </c>
@@ -39246,7 +39290,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="797" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A797">
         <v>796</v>
       </c>
@@ -39287,7 +39331,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="798" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A798">
         <v>797</v>
       </c>
@@ -39328,7 +39372,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="799" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A799">
         <v>798</v>
       </c>
@@ -39369,7 +39413,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="800" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A800">
         <v>799</v>
       </c>
@@ -39410,7 +39454,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="801" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A801">
         <v>800</v>
       </c>
@@ -39451,7 +39495,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="802" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A802">
         <v>801</v>
       </c>
@@ -39492,7 +39536,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="803" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A803">
         <v>802</v>
       </c>
@@ -39533,7 +39577,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="804" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A804">
         <v>803</v>
       </c>
@@ -39574,7 +39618,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="805" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A805">
         <v>804</v>
       </c>
@@ -39615,7 +39659,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="806" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A806">
         <v>805</v>
       </c>
@@ -39656,7 +39700,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="807" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A807">
         <v>806</v>
       </c>
@@ -39697,7 +39741,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="808" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A808">
         <v>807</v>
       </c>
@@ -39738,7 +39782,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="809" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A809">
         <v>808</v>
       </c>
@@ -39779,7 +39823,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="810" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A810">
         <v>809</v>
       </c>
@@ -39820,7 +39864,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="811" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A811">
         <v>810</v>
       </c>
@@ -39861,7 +39905,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="812" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A812">
         <v>811</v>
       </c>
@@ -39902,7 +39946,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="813" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A813">
         <v>812</v>
       </c>
@@ -39943,7 +39987,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="814" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A814">
         <v>813</v>
       </c>
@@ -39984,7 +40028,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="815" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A815">
         <v>814</v>
       </c>
@@ -40025,7 +40069,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="816" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A816">
         <v>815</v>
       </c>
@@ -40066,7 +40110,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="817" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A817">
         <v>816</v>
       </c>
@@ -40107,7 +40151,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="818" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A818">
         <v>817</v>
       </c>
@@ -40148,7 +40192,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="819" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A819">
         <v>818</v>
       </c>
@@ -40189,7 +40233,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="820" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A820">
         <v>819</v>
       </c>
@@ -40230,7 +40274,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="821" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A821">
         <v>820</v>
       </c>
@@ -40271,7 +40315,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="822" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A822">
         <v>821</v>
       </c>
@@ -40312,7 +40356,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="823" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A823">
         <v>822</v>
       </c>
@@ -40353,7 +40397,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="824" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A824">
         <v>823</v>
       </c>
@@ -40394,7 +40438,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="825" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A825">
         <v>824</v>
       </c>
@@ -40435,7 +40479,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="826" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A826">
         <v>825</v>
       </c>
@@ -40476,7 +40520,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="827" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A827">
         <v>826</v>
       </c>
@@ -40517,7 +40561,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="828" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A828">
         <v>827</v>
       </c>
@@ -40558,7 +40602,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="829" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A829">
         <v>828</v>
       </c>
@@ -40599,7 +40643,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="830" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A830">
         <v>829</v>
       </c>
@@ -40640,7 +40684,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="831" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A831">
         <v>830</v>
       </c>
@@ -40681,7 +40725,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="832" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A832">
         <v>831</v>
       </c>
@@ -40722,7 +40766,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A833">
         <v>832</v>
       </c>
@@ -40763,7 +40807,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A834">
         <v>833</v>
       </c>
@@ -40804,7 +40848,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A835">
         <v>834</v>
       </c>
@@ -40848,7 +40892,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A836">
         <v>835</v>
       </c>
@@ -40892,7 +40936,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A837">
         <v>836</v>
       </c>
@@ -40936,7 +40980,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A838">
         <v>837</v>
       </c>
@@ -40980,7 +41024,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A839">
         <v>838</v>
       </c>
@@ -41024,7 +41068,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A840">
         <v>839</v>
       </c>
@@ -41068,7 +41112,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="841" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A841">
         <v>840</v>
       </c>
@@ -41112,7 +41156,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="842" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A842">
         <v>841</v>
       </c>
@@ -41156,7 +41200,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="843" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A843">
         <v>842</v>
       </c>
@@ -41197,7 +41241,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="844" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A844">
         <v>843</v>
       </c>
@@ -41238,7 +41282,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A845">
         <v>844</v>
       </c>
@@ -41279,7 +41323,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A846">
         <v>845</v>
       </c>
@@ -41320,7 +41364,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A847">
         <v>846</v>
       </c>
@@ -41361,7 +41405,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A848">
         <v>847</v>
       </c>
@@ -41402,7 +41446,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A849">
         <v>848</v>
       </c>
@@ -41443,7 +41487,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="850" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A850">
         <v>849</v>
       </c>
@@ -41484,7 +41528,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="851" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A851">
         <v>850</v>
       </c>
@@ -41525,7 +41569,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="852" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A852">
         <v>851</v>
       </c>
@@ -41566,7 +41610,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="853" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A853">
         <v>852</v>
       </c>
@@ -41604,7 +41648,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="854" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A854">
         <v>853</v>
       </c>
@@ -41640,6 +41684,102 @@
       </c>
       <c r="N854" s="6" t="s">
         <v>2033</v>
+      </c>
+    </row>
+    <row r="855" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B855" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C855" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="E855" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F855" s="9" t="s">
+        <v>2331</v>
+      </c>
+      <c r="H855" s="6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I855" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="J855" s="6" t="s">
+        <v>2335</v>
+      </c>
+      <c r="L855" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="M855" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="O855" s="10" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="856" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B856" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C856" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="E856" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F856" s="9" t="s">
+        <v>2332</v>
+      </c>
+      <c r="H856" s="6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I856" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="J856" s="6" t="s">
+        <v>2336</v>
+      </c>
+      <c r="L856" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="M856" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="O856" s="10" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="857" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B857" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C857" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="E857" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F857" s="9" t="s">
+        <v>2333</v>
+      </c>
+      <c r="H857" s="6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I857" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="J857" s="6" t="s">
+        <v>2337</v>
+      </c>
+      <c r="L857" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="M857" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="O857" s="10" t="s">
+        <v>2338</v>
       </c>
     </row>
   </sheetData>
@@ -41654,9 +41794,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0177C972-1D74-9245-AC41-04BB1478BDD0}">
   <dimension ref="B2:J118"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -41685,7 +41825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>129</v>
       </c>
@@ -41711,7 +41851,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>129</v>
       </c>
@@ -41737,7 +41877,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>129</v>
       </c>
@@ -41763,7 +41903,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>129</v>
       </c>
@@ -41789,7 +41929,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>129</v>
       </c>
@@ -41815,7 +41955,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>129</v>
       </c>
@@ -41841,7 +41981,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>129</v>
       </c>
@@ -41867,7 +42007,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -41893,7 +42033,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>129</v>
       </c>
@@ -41919,7 +42059,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>129</v>
       </c>
@@ -41945,7 +42085,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -41971,7 +42111,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>129</v>
       </c>
@@ -41997,7 +42137,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>129</v>
       </c>
@@ -42023,7 +42163,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>129</v>
       </c>
@@ -42049,7 +42189,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>129</v>
       </c>
@@ -42075,7 +42215,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>129</v>
       </c>
@@ -42101,7 +42241,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>129</v>
       </c>
@@ -42127,7 +42267,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>129</v>
       </c>
@@ -42153,7 +42293,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>129</v>
       </c>
@@ -42179,7 +42319,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>129</v>
       </c>
@@ -42205,7 +42345,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>129</v>
       </c>
@@ -42231,7 +42371,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>129</v>
       </c>
@@ -42257,7 +42397,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>129</v>
       </c>
@@ -42283,7 +42423,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>129</v>
       </c>
@@ -42309,7 +42449,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>129</v>
       </c>
@@ -42335,7 +42475,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>129</v>
       </c>
@@ -42361,7 +42501,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>129</v>
       </c>
@@ -42387,7 +42527,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>129</v>
       </c>
@@ -42413,7 +42553,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>129</v>
       </c>
@@ -42439,7 +42579,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>129</v>
       </c>
@@ -42465,7 +42605,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>129</v>
       </c>
@@ -42491,7 +42631,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>129</v>
       </c>
@@ -42517,7 +42657,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>129</v>
       </c>
@@ -42543,7 +42683,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>129</v>
       </c>
@@ -42569,7 +42709,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>129</v>
       </c>
@@ -42595,7 +42735,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>129</v>
       </c>
@@ -42621,7 +42761,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>129</v>
       </c>
@@ -42647,7 +42787,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>129</v>
       </c>
@@ -42673,7 +42813,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>129</v>
       </c>
@@ -42699,7 +42839,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>129</v>
       </c>
@@ -42725,7 +42865,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>129</v>
       </c>
@@ -42751,7 +42891,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>129</v>
       </c>
@@ -42777,7 +42917,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>129</v>
       </c>
@@ -42803,7 +42943,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>129</v>
       </c>
@@ -42829,7 +42969,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>129</v>
       </c>
@@ -42855,7 +42995,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>129</v>
       </c>
@@ -42881,7 +43021,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>129</v>
       </c>
@@ -42907,7 +43047,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>129</v>
       </c>
@@ -42933,7 +43073,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>129</v>
       </c>
@@ -42959,7 +43099,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>129</v>
       </c>
@@ -42985,7 +43125,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>129</v>
       </c>
@@ -43011,7 +43151,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>129</v>
       </c>
@@ -43037,7 +43177,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>129</v>
       </c>
@@ -43063,7 +43203,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>129</v>
       </c>
@@ -43090,7 +43230,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>129</v>
       </c>
@@ -43117,7 +43257,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>129</v>
       </c>
@@ -43144,7 +43284,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>129</v>
       </c>
@@ -43171,7 +43311,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>129</v>
       </c>
@@ -43198,7 +43338,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>129</v>
       </c>
@@ -43225,7 +43365,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>129</v>
       </c>
@@ -43252,7 +43392,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>129</v>
       </c>
@@ -43279,7 +43419,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>129</v>
       </c>
@@ -43306,7 +43446,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>129</v>
       </c>
@@ -43333,7 +43473,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>129</v>
       </c>
@@ -43360,7 +43500,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>129</v>
       </c>
@@ -43387,7 +43527,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>129</v>
       </c>
@@ -43414,7 +43554,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>129</v>
       </c>
@@ -43441,7 +43581,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>129</v>
       </c>
@@ -43468,7 +43608,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>129</v>
       </c>
@@ -43495,7 +43635,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>129</v>
       </c>
@@ -43522,7 +43662,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>129</v>
       </c>
@@ -43549,7 +43689,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>129</v>
       </c>
@@ -43576,7 +43716,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>129</v>
       </c>
@@ -43603,7 +43743,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>129</v>
       </c>
@@ -43630,7 +43770,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>129</v>
       </c>
@@ -43657,7 +43797,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>129</v>
       </c>
@@ -43684,7 +43824,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>129</v>
       </c>
@@ -43711,7 +43851,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>129</v>
       </c>
@@ -43738,7 +43878,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>129</v>
       </c>
@@ -43765,7 +43905,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>129</v>
       </c>
@@ -43792,7 +43932,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>129</v>
       </c>
@@ -43819,7 +43959,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>129</v>
       </c>
@@ -43846,7 +43986,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>129</v>
       </c>
@@ -43873,7 +44013,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>129</v>
       </c>
@@ -43900,7 +44040,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>129</v>
       </c>
@@ -43927,7 +44067,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>129</v>
       </c>
@@ -43954,7 +44094,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>129</v>
       </c>
@@ -43981,7 +44121,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>129</v>
       </c>
@@ -44008,7 +44148,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>129</v>
       </c>
@@ -44035,7 +44175,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>129</v>
       </c>
@@ -44062,7 +44202,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>129</v>
       </c>
@@ -44089,7 +44229,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>129</v>
       </c>
@@ -44116,7 +44256,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>129</v>
       </c>
@@ -44143,7 +44283,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>129</v>
       </c>
@@ -44170,7 +44310,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>129</v>
       </c>
@@ -44197,7 +44337,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>129</v>
       </c>
@@ -44224,7 +44364,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>129</v>
       </c>
@@ -44251,7 +44391,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>129</v>
       </c>
@@ -44277,7 +44417,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>129</v>
       </c>
@@ -44303,7 +44443,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>129</v>
       </c>
@@ -44329,7 +44469,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>129</v>
       </c>
@@ -44355,7 +44495,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>129</v>
       </c>
@@ -44381,7 +44521,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>129</v>
       </c>
@@ -44407,7 +44547,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>129</v>
       </c>
@@ -44433,7 +44573,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>129</v>
       </c>
@@ -44459,7 +44599,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>129</v>
       </c>
@@ -44485,7 +44625,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>129</v>
       </c>
@@ -44511,7 +44651,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>129</v>
       </c>
@@ -44537,7 +44677,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>129</v>
       </c>
@@ -44563,7 +44703,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>129</v>
       </c>
@@ -44589,7 +44729,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>129</v>
       </c>
@@ -44615,7 +44755,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>129</v>
       </c>
@@ -44641,7 +44781,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>129</v>
       </c>
@@ -44667,7 +44807,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>129</v>
       </c>
@@ -44693,7 +44833,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>129</v>
       </c>
@@ -44719,7 +44859,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>129</v>
       </c>
